--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,51 +447,95 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1790808573942_ktuq</v>
+        <v>sale_1790839031379</v>
       </c>
       <c r="B2" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C2" t="str">
-        <v>03182642966</v>
+        <v>+92 340 7317084</v>
       </c>
       <c r="D2" t="str">
-        <v>Ali Ahmed</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F2" t="str">
         <v>Shared</v>
       </c>
       <c r="G2" t="str">
-        <v>Abd114@kuromee.com</v>
+        <v>Nord9@kuromee.com</v>
       </c>
       <c r="H2" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="K2" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-10-30</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-09-30T22:49:33.942Z</v>
+        <v>2026-10-01T07:17:11.379Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>sale_1790838846301</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C3" t="str">
+        <v>3085352533</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G3" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>800</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-11-29</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2 Devices</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-10-01T07:14:06.302Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,95 +447,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1790839031379</v>
+        <v>sale_1790891345201_z6tu</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C2" t="str">
-        <v>+92 340 7317084</v>
+        <v>dssds</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F2" t="str">
         <v>Shared</v>
       </c>
       <c r="G2" t="str">
-        <v>Nord9@kuromee.com</v>
+        <v>Sgsg</v>
       </c>
       <c r="H2" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K2" t="str">
         <v>Paid</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-10-01T07:17:11.379Z</v>
+        <v>2026-10-01T21:49:05.201Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sale_1790838846301</v>
+        <v>sale_1790839031379</v>
       </c>
       <c r="B3" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C3" t="str">
-        <v>3085352533</v>
+        <v>+92 340 7317084</v>
       </c>
       <c r="D3" t="str">
         <v/>
       </c>
       <c r="E3" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Nord9@kuromee.com</v>
+      </c>
+      <c r="H3" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>500</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-10-01T07:17:11.379Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>sale_1790838846301</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>3085352533</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
         <v>Surfshark</v>
       </c>
-      <c r="F3" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="F4" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G4" t="str">
         <v>abd149@kuromee.com</v>
       </c>
-      <c r="H3" t="str">
+      <c r="H4" t="str">
         <v>2 Months (60 Days)</v>
       </c>
-      <c r="I3">
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="J3">
+      <c r="J4">
         <v>800</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K4" t="str">
         <v>Pending</v>
       </c>
-      <c r="L3" t="str">
+      <c r="L4" t="str">
         <v>2026-11-29</v>
       </c>
-      <c r="M3" t="str">
+      <c r="M4" t="str">
         <v>2 Devices</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N4" t="str">
         <v>2026-10-01T07:14:06.302Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,139 +447,95 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1790891345201_z6tu</v>
+        <v>sale_1790839031379</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-01</v>
       </c>
       <c r="C2" t="str">
-        <v>dssds</v>
+        <v>+92 340 7317084</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F2" t="str">
         <v>Shared</v>
       </c>
       <c r="G2" t="str">
-        <v>Sgsg</v>
+        <v>Nord9@kuromee.com</v>
       </c>
       <c r="H2" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="K2" t="str">
         <v>Paid</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-10-01T21:49:05.201Z</v>
+        <v>2026-10-01T07:17:11.379Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sale_1790839031379</v>
+        <v>sale_1790838846301</v>
       </c>
       <c r="B3" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C3" t="str">
-        <v>+92 340 7317084</v>
+        <v>3085352533</v>
       </c>
       <c r="D3" t="str">
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F3" t="str">
         <v>Shared</v>
       </c>
       <c r="G3" t="str">
-        <v>Nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H3" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="K3" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2 Devices</v>
       </c>
       <c r="N3" t="str">
-        <v>2026-10-01T07:17:11.379Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>sale_1790838846301</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-10-01</v>
-      </c>
-      <c r="C4" t="str">
-        <v>3085352533</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="G4" t="str">
-        <v>abd149@kuromee.com</v>
-      </c>
-      <c r="H4" t="str">
-        <v>2 Months (60 Days)</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>800</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-11-29</v>
-      </c>
-      <c r="M4" t="str">
-        <v>2 Devices</v>
-      </c>
-      <c r="N4" t="str">
         <v>2026-10-01T07:14:06.302Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,57 +447,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1790839031379</v>
+        <v>sale_1790889578017</v>
       </c>
       <c r="B2" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C2" t="str">
-        <v>+92 340 7317084</v>
+        <v>03000000000</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F2" t="str">
         <v>Shared</v>
       </c>
       <c r="G2" t="str">
-        <v>Nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H2" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K2" t="str">
         <v>Paid</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-10-01T07:17:11.379Z</v>
+        <v>2026-10-01T20:59:38.017Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sale_1790838846301</v>
+        <v>sale_1790888324786</v>
       </c>
       <c r="B3" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C3" t="str">
-        <v>3085352533</v>
+        <v>3424112890 - 232013</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -512,37 +512,785 @@
         <v>abd149@kuromee.com</v>
       </c>
       <c r="H3" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>250</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-10-01T20:58:44.786Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>sale_1790871288858</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>+92 336 6331621</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G4" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H4" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1200</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-10-01T16:14:48.858Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>sale_1790871264002</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C5" t="str">
+        <v>+98 901 603 6081</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G5" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H5" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>500</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-10-01T16:14:24.002Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>sale_1790868862060</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>+92 341 9010662</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G6" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H6" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v>2026-10-01T15:34:22.075Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>sale_1790864924575</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C7" t="str">
+        <v>+92 313 6762957</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G7" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H7" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>500</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L7" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v>2026-10-01T14:28:44.576Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>sale_1790864890520</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C8" t="str">
+        <v>3166729551</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G8" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H8" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <v>600</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L8" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v>2026-10-01T14:28:10.520Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>sale_1790862744178</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C9" t="str">
+        <v>+92 317 0295905</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G9" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H9" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <v>600</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v>2026-10-01T13:52:24.178Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>sale_1790861118501</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C10" t="str">
+        <v>+92 344 4643148</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G10" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H10" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>500</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v>2026-10-01T13:25:18.501Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>sale_1790853314445</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+92 302 7283125</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G11" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H11" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>750</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L11" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M11" t="str">
+        <v>vukdsas@apricity.tech  masuk123</v>
+      </c>
+      <c r="N11" t="str">
+        <v>2026-10-01T11:15:14.445Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>sale_1790852538710</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C12" t="str">
+        <v>+92 325 1501138</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G12" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1000</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L12" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v>2026-10-01T11:02:18.710Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>sale_1790852373016</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C13" t="str">
+        <v>+92 301 7890066</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G13" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1500</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v>2026-10-01T10:59:33.016Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>sale_1790850006978</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C14" t="str">
+        <v>+92 342 4112890-534389</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G14" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>200</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L14" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v>2026-10-01T10:20:06.978Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>sale_1790849948623</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C15" t="str">
+        <v>+92 349 6363398</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G15" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H15" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>250</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L15" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v>2026-10-01T10:19:08.625Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>sale_1790844774858</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C16" t="str">
+        <v>03035587360</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Not applicable</v>
+      </c>
+      <c r="H16" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I16">
+        <v>18</v>
+      </c>
+      <c r="J16">
+        <v>500</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L16" t="str">
+        <v>2028-03-23</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v>2026-10-01T08:52:54.860Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>sale_1790841917101</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C17" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G17" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H17" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17">
+        <v>500</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L17" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v>2026-10-01T08:05:17.101Z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>sale_1790890880426_oulk</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C18" t="str">
+        <v>3336677666</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G18" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H18" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>250</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L18" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v>2026-10-01T21:41:20.426Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>sale_1790839031379</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C19" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Nord9@kuromee.com</v>
+      </c>
+      <c r="H19" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <v>500</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L19" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v>2026-10-01T07:17:11.379Z</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>sale_1790838846301</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C20" t="str">
+        <v>3085352533</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G20" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H20" t="str">
         <v>2 Months (60 Days)</v>
       </c>
-      <c r="I3">
+      <c r="I20">
         <v>2</v>
       </c>
-      <c r="J3">
+      <c r="J20">
         <v>800</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K20" t="str">
         <v>Pending</v>
       </c>
-      <c r="L3" t="str">
+      <c r="L20" t="str">
         <v>2026-11-29</v>
       </c>
-      <c r="M3" t="str">
+      <c r="M20" t="str">
         <v>2 Devices</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N20" t="str">
         <v>2026-10-01T07:14:06.302Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -584,9 +1332,69 @@
         <v>2026-09-30T23:28:01.227Z</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>exp_1790889252470</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Surfshark/Nord Paid</v>
+      </c>
+      <c r="E3">
+        <v>1600</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-10-01T21:14:12.470Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>exp_1790888895390</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Capcut padmahastuti3@akunku.site|masuk123</v>
+      </c>
+      <c r="E4">
+        <v>350</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-10-01T21:08:15.390Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>exp_1790865001001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Capcut Account For Luxury online Store   vukdsas@apricity.tech:masuk123</v>
+      </c>
+      <c r="E5">
+        <v>350</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-10-01T14:30:01.001Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,57 +447,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1790889578017</v>
+        <v>sale_1790839031379</v>
       </c>
       <c r="B2" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C2" t="str">
-        <v>03000000000</v>
+        <v>+92 340 7317084</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F2" t="str">
         <v>Shared</v>
       </c>
       <c r="G2" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>Nord9@kuromee.com</v>
       </c>
       <c r="H2" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K2" t="str">
         <v>Paid</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-11-29</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-10-01T20:59:38.017Z</v>
+        <v>2026-10-01T07:17:11.379Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sale_1790888324786</v>
+        <v>sale_1790838846301</v>
       </c>
       <c r="B3" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C3" t="str">
-        <v>3424112890 - 232013</v>
+        <v>3085352533</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -512,48 +512,48 @@
         <v>abd149@kuromee.com</v>
       </c>
       <c r="H3" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="K3" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2 Devices</v>
       </c>
       <c r="N3" t="str">
-        <v>2026-10-01T20:58:44.786Z</v>
+        <v>2026-10-01T07:14:06.302Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>sale_1790871288858</v>
+        <v>sale_1790890878620</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C4" t="str">
-        <v>+92 336 6331621</v>
+        <v>3336677666</v>
       </c>
       <c r="D4" t="str">
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F4" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G4" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H4" t="str">
         <v>1 Month (30 Days)</v>
@@ -562,86 +562,86 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="K4" t="str">
         <v>Paid</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>2026-10-01T16:14:48.858Z</v>
+        <v>2026-10-01T21:41:18.621Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>sale_1790871264002</v>
+        <v>sale_1790889330982</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C5" t="str">
-        <v>+98 901 603 6081</v>
+        <v>+92 333 7180888</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F5" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G5" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H5" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K5" t="str">
         <v>Paid</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>2026-10-01T16:14:24.002Z</v>
+        <v>2026-10-01T21:15:30.982Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>sale_1790868862060</v>
+        <v>sale_1790889206450</v>
       </c>
       <c r="B6" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C6" t="str">
-        <v>+92 341 9010662</v>
+        <v>447348556756 - 2 Devices</v>
       </c>
       <c r="D6" t="str">
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F6" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G6" t="str">
-        <v>NA</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H6" t="str">
         <v>1 Month (30 Days)</v>
@@ -650,10 +650,10 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K6" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L6" t="str">
         <v>2026-10-30</v>
@@ -662,206 +662,206 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>2026-10-01T15:34:22.075Z</v>
+        <v>2026-10-01T21:13:26.450Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>sale_1790864924575</v>
+        <v>sale_1790889149110</v>
       </c>
       <c r="B7" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C7" t="str">
-        <v>+92 313 6762957</v>
+        <v>3716928959</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F7" t="str">
         <v>Shared</v>
       </c>
       <c r="G7" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H7" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K7" t="str">
         <v>Paid</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M7" t="str">
         <v/>
       </c>
       <c r="N7" t="str">
-        <v>2026-10-01T14:28:44.576Z</v>
+        <v>2026-10-01T21:12:29.110Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>sale_1790864890520</v>
+        <v>sale_1790889019841</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C8" t="str">
-        <v>3166729551</v>
+        <v>+92 324 3715759</v>
       </c>
       <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F8" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G8" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H8" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="K8" t="str">
         <v>Paid</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M8" t="str">
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>2026-10-01T14:28:10.520Z</v>
+        <v>2026-10-01T21:10:19.841Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>sale_1790862744178</v>
+        <v>sale_1790888980587</v>
       </c>
       <c r="B9" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C9" t="str">
-        <v>+92 317 0295905</v>
+        <v>+92 337 8569003</v>
       </c>
       <c r="D9" t="str">
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Nord</v>
+        <v>CapCut</v>
       </c>
       <c r="F9" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G9" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>padmahastuti3@akunku.site|masuk123</v>
       </c>
       <c r="H9" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="K9" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M9" t="str">
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>2026-10-01T13:52:24.178Z</v>
+        <v>2026-10-01T21:09:40.587Z</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>sale_1790861118501</v>
+        <v>sale_1790888790593</v>
       </c>
       <c r="B10" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C10" t="str">
-        <v>+92 344 4643148</v>
+        <v>+92 318 8934627</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F10" t="str">
         <v>Shared</v>
       </c>
       <c r="G10" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H10" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="K10" t="str">
         <v>Paid</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M10" t="str">
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>2026-10-01T13:25:18.501Z</v>
+        <v>2026-10-01T21:06:30.593Z</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>sale_1790853314445</v>
+        <v>sale_1790888748366</v>
       </c>
       <c r="B11" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C11" t="str">
-        <v>+92 302 7283125</v>
+        <v>3121600439</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>CapCut</v>
+        <v>Surfshark</v>
       </c>
       <c r="F11" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G11" t="str">
-        <v>NA</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H11" t="str">
         <v>1 Month (30 Days)</v>
@@ -870,42 +870,42 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K11" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L11" t="str">
         <v>2026-10-30</v>
       </c>
       <c r="M11" t="str">
-        <v>vukdsas@apricity.tech  masuk123</v>
+        <v/>
       </c>
       <c r="N11" t="str">
-        <v>2026-10-01T11:15:14.445Z</v>
+        <v>2026-10-01T21:05:48.366Z</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>sale_1790852538710</v>
+        <v>sale_1790888549930</v>
       </c>
       <c r="B12" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C12" t="str">
-        <v>+92 325 1501138</v>
+        <v>3148646368</v>
       </c>
       <c r="D12" t="str">
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F12" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G12" t="str">
-        <v>N/A</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H12" t="str">
         <v>1 Month (30 Days)</v>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="K12" t="str">
         <v>Paid</v>
@@ -926,62 +926,62 @@
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>2026-10-01T11:02:18.710Z</v>
+        <v>2026-10-01T21:02:29.930Z</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>sale_1790852373016</v>
+        <v>sale_1790888489800</v>
       </c>
       <c r="B13" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C13" t="str">
-        <v>+92 301 7890066</v>
+        <v>3043943233 - 2 devices</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F13" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G13" t="str">
-        <v>N/A</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H13" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="K13" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-10-30</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Payment 5 Oct</v>
       </c>
       <c r="N13" t="str">
-        <v>2026-10-01T10:59:33.016Z</v>
+        <v>2026-10-01T21:01:29.800Z</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>sale_1790850006978</v>
+        <v>sale_1790888426010</v>
       </c>
       <c r="B14" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C14" t="str">
-        <v>+92 342 4112890-534389</v>
+        <v>3125698180</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -996,36 +996,36 @@
         <v>abd149@kuromee.com</v>
       </c>
       <c r="H14" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K14" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>Payment Sunday 4 Oct</v>
       </c>
       <c r="N14" t="str">
-        <v>2026-10-01T10:20:06.978Z</v>
+        <v>2026-10-01T21:00:26.011Z</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>sale_1790849948623</v>
+        <v>sale_1790888378017</v>
       </c>
       <c r="B15" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C15" t="str">
-        <v>+92 349 6363398</v>
+        <v>3208546164</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -1040,250 +1040,690 @@
         <v>abd149@kuromee.com</v>
       </c>
       <c r="H15" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K15" t="str">
         <v>Paid</v>
       </c>
       <c r="L15" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>2026-10-01T10:19:08.625Z</v>
+        <v>2026-10-01T20:59:38.017Z</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>sale_1790844774858</v>
+        <v>sale_1790888324786</v>
       </c>
       <c r="B16" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C16" t="str">
-        <v>03035587360</v>
+        <v>3424112890 - 232013</v>
       </c>
       <c r="D16" t="str">
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Gemini Pro</v>
+        <v>Surfshark</v>
       </c>
       <c r="F16" t="str">
         <v>Shared</v>
       </c>
       <c r="G16" t="str">
-        <v>Not applicable</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H16" t="str">
-        <v>18 Months (540 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I16">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K16" t="str">
         <v>Paid</v>
       </c>
       <c r="L16" t="str">
-        <v>2028-03-23</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>2026-10-01T08:52:54.860Z</v>
+        <v>2026-10-01T20:58:44.786Z</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>sale_1790841917101</v>
+        <v>sale_1790871288858</v>
       </c>
       <c r="B17" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C17" t="str">
-        <v>+92 340 7317084</v>
+        <v>+92 336 6331621</v>
       </c>
       <c r="D17" t="str">
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F17" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G17" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H17" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="K17" t="str">
         <v>Paid</v>
       </c>
       <c r="L17" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>2026-10-01T08:05:17.101Z</v>
+        <v>2026-10-01T16:14:48.858Z</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>sale_1790890880426_oulk</v>
+        <v>sale_1790871264002</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-01</v>
       </c>
       <c r="C18" t="str">
-        <v>3336677666</v>
+        <v>+98 901 603 6081</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F18" t="str">
         <v>Shared</v>
       </c>
       <c r="G18" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>nord9@kuromee.com</v>
       </c>
       <c r="H18" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="K18" t="str">
         <v>Paid</v>
       </c>
       <c r="L18" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>2026-10-01T21:41:20.426Z</v>
+        <v>2026-10-01T16:14:24.002Z</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>sale_1790839031379</v>
+        <v>sale_1790868862060</v>
       </c>
       <c r="B19" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C19" t="str">
-        <v>+92 340 7317084</v>
+        <v>+92 341 9010662</v>
       </c>
       <c r="D19" t="str">
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F19" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G19" t="str">
-        <v>Nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H19" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K19" t="str">
         <v>Paid</v>
       </c>
       <c r="L19" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>2026-10-01T07:17:11.379Z</v>
+        <v>2026-10-01T15:34:22.075Z</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>sale_1790838846301</v>
+        <v>sale_1790864924575</v>
       </c>
       <c r="B20" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C20" t="str">
-        <v>3085352533</v>
+        <v>+92 313 6762957</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G20" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H20" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>500</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L20" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v>2026-10-01T14:28:44.576Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>sale_1790864890520</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C21" t="str">
+        <v>3166729551</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
         <v>Surfshark</v>
       </c>
-      <c r="F20" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="G20" t="str">
+      <c r="F21" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G21" t="str">
         <v>abd149@kuromee.com</v>
       </c>
-      <c r="H20" t="str">
-        <v>2 Months (60 Days)</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="J20">
-        <v>800</v>
-      </c>
-      <c r="K20" t="str">
+      <c r="H21" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <v>600</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L21" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v>2026-10-01T14:28:10.520Z</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>sale_1790862744178</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C22" t="str">
+        <v>+92 317 0295905</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G22" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H22" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>600</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L22" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v>2026-10-01T13:52:24.178Z</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>sale_1790861118501</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C23" t="str">
+        <v>+92 344 4643148</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G23" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H23" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23">
+        <v>500</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L23" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v>2026-10-01T13:25:18.501Z</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>sale_1790853314445</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C24" t="str">
+        <v>+92 302 7283125</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G24" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H24" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>750</v>
+      </c>
+      <c r="K24" t="str">
         <v>Pending</v>
       </c>
-      <c r="L20" t="str">
-        <v>2026-11-29</v>
-      </c>
-      <c r="M20" t="str">
-        <v>2 Devices</v>
-      </c>
-      <c r="N20" t="str">
-        <v>2026-10-01T07:14:06.302Z</v>
+      <c r="L24" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M24" t="str">
+        <v>vukdsas@apricity.tech  masuk123</v>
+      </c>
+      <c r="N24" t="str">
+        <v>2026-10-01T11:15:14.445Z</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>sale_1790852538710</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C25" t="str">
+        <v>+92 325 1501138</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G25" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H25" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1000</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L25" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v>2026-10-01T11:02:18.710Z</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>sale_1790852373016</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C26" t="str">
+        <v>+92 301 7890066</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G26" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H26" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1500</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L26" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v>2026-10-01T10:59:33.016Z</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>sale_1790850006978</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C27" t="str">
+        <v>+92 342 4112890-534389</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G27" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H27" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>200</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L27" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v>2026-10-01T10:20:06.978Z</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>sale_1790849948623</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C28" t="str">
+        <v>+92 349 6363398</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G28" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H28" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>250</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L28" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v>2026-10-01T10:19:08.625Z</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>sale_1790844774858</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C29" t="str">
+        <v>03035587360</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Not applicable</v>
+      </c>
+      <c r="H29" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I29">
+        <v>18</v>
+      </c>
+      <c r="J29">
+        <v>500</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L29" t="str">
+        <v>2028-03-23</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v>2026-10-01T08:52:54.860Z</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>sale_1790841917101</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C30" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G30" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H30" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <v>500</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L30" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v>2026-10-01T08:05:17.101Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N30"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,57 +447,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1790839031379</v>
+        <v>sale_1790934819273</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C2" t="str">
-        <v>+92 340 7317084</v>
+        <v>3362088885</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F2" t="str">
         <v>Shared</v>
       </c>
       <c r="G2" t="str">
-        <v>Nord9@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H2" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K2" t="str">
         <v>Paid</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-10-01T07:17:11.379Z</v>
+        <v>2026-10-02T09:53:39.274Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sale_1790838846301</v>
+        <v>sale_1790934132194</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C3" t="str">
-        <v>3085352533</v>
+        <v>3171626906</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -509,39 +509,39 @@
         <v>Shared</v>
       </c>
       <c r="G3" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H3" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="K3" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-11-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M3" t="str">
-        <v>2 Devices</v>
+        <v/>
       </c>
       <c r="N3" t="str">
-        <v>2026-10-01T07:14:06.302Z</v>
+        <v>2026-10-02T09:42:12.194Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>sale_1790890878620</v>
+        <v>sale_1790929984076</v>
       </c>
       <c r="B4" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C4" t="str">
-        <v>3336677666</v>
+        <v>3425091286</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -574,18 +574,18 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>2026-10-01T21:41:18.621Z</v>
+        <v>2026-10-02T08:33:04.076Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>sale_1790889330982</v>
+        <v>sale_1790928896570</v>
       </c>
       <c r="B5" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C5" t="str">
-        <v>+92 333 7180888</v>
+        <v>+92 335 9333443</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -594,7 +594,7 @@
         <v>Muse AI</v>
       </c>
       <c r="F5" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G5" t="str">
         <v>NA</v>
@@ -606,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="K5" t="str">
         <v>Paid</v>
@@ -618,18 +618,18 @@
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>2026-10-01T21:15:30.982Z</v>
+        <v>2026-10-02T08:14:56.570Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>sale_1790889206450</v>
+        <v>sale_1790927823366</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C6" t="str">
-        <v>447348556756 - 2 Devices</v>
+        <v>3424112890 - 178132</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -641,7 +641,7 @@
         <v>Shared</v>
       </c>
       <c r="G6" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H6" t="str">
         <v>1 Month (30 Days)</v>
@@ -650,30 +650,30 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K6" t="str">
         <v>Pending</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M6" t="str">
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>2026-10-01T21:13:26.450Z</v>
+        <v>2026-10-02T07:57:03.366Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>sale_1790889149110</v>
+        <v>sale_1790927720999</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C7" t="str">
-        <v>3716928959</v>
+        <v>3355060692</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -685,95 +685,95 @@
         <v>Shared</v>
       </c>
       <c r="G7" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H7" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K7" t="str">
         <v>Paid</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-11-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M7" t="str">
         <v/>
       </c>
       <c r="N7" t="str">
-        <v>2026-10-01T21:12:29.110Z</v>
+        <v>2026-10-02T07:55:20.999Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>sale_1790889019841</v>
+        <v>sale_1790927520048</v>
       </c>
       <c r="B8" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C8" t="str">
-        <v>+92 324 3715759</v>
+        <v>3237432065</v>
       </c>
       <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F8" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G8" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H8" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="K8" t="str">
         <v>Paid</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-30</v>
       </c>
       <c r="M8" t="str">
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>2026-10-01T21:10:19.841Z</v>
+        <v>2026-10-02T07:52:00.048Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>sale_1790888980587</v>
+        <v>sale_1790927399372</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C9" t="str">
-        <v>+92 337 8569003</v>
+        <v>3226763778</v>
       </c>
       <c r="D9" t="str">
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>CapCut</v>
+        <v>Surfshark</v>
       </c>
       <c r="F9" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G9" t="str">
-        <v>padmahastuti3@akunku.site|masuk123</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H9" t="str">
         <v>1 Month (30 Days)</v>
@@ -782,42 +782,42 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K9" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M9" t="str">
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>2026-10-01T21:09:40.587Z</v>
+        <v>2026-10-02T07:49:59.372Z</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>sale_1790888790593</v>
+        <v>sale_1790927194315</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C10" t="str">
-        <v>+92 318 8934627</v>
+        <v>3087182016</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F10" t="str">
         <v>Shared</v>
       </c>
       <c r="G10" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H10" t="str">
         <v>1 Month (30 Days)</v>
@@ -826,30 +826,30 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="K10" t="str">
         <v>Paid</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M10" t="str">
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>2026-10-01T21:06:30.593Z</v>
+        <v>2026-10-02T07:46:34.315Z</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>sale_1790888748366</v>
+        <v>sale_1790926790421</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C11" t="str">
-        <v>3121600439</v>
+        <v>3424112890 - 161547</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -861,7 +861,7 @@
         <v>Shared</v>
       </c>
       <c r="G11" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H11" t="str">
         <v>1 Month (30 Days)</v>
@@ -870,30 +870,30 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K11" t="str">
         <v>Paid</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M11" t="str">
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>2026-10-01T21:05:48.366Z</v>
+        <v>2026-10-02T07:39:50.422Z</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>sale_1790888549930</v>
+        <v>sale_1790890878620</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C12" t="str">
-        <v>3148646368</v>
+        <v>3336677666</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -905,7 +905,7 @@
         <v>Shared</v>
       </c>
       <c r="G12" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H12" t="str">
         <v>1 Month (30 Days)</v>
@@ -914,118 +914,118 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K12" t="str">
         <v>Paid</v>
       </c>
       <c r="L12" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M12" t="str">
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>2026-10-01T21:02:29.930Z</v>
+        <v>2026-10-01T21:41:18.621Z</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>sale_1790888489800</v>
+        <v>sale_1790889330982</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C13" t="str">
-        <v>3043943233 - 2 devices</v>
+        <v>+92 333 7180888</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F13" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G13" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H13" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>1000</v>
       </c>
       <c r="K13" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M13" t="str">
-        <v>Payment 5 Oct</v>
+        <v/>
       </c>
       <c r="N13" t="str">
-        <v>2026-10-01T21:01:29.800Z</v>
+        <v>2026-10-01T21:15:30.982Z</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>sale_1790888426010</v>
+        <v>sale_1790889019841</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C14" t="str">
-        <v>3125698180</v>
+        <v>+92 324 3715759</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F14" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G14" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H14" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="K14" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-11-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M14" t="str">
-        <v>Payment Sunday 4 Oct</v>
+        <v/>
       </c>
       <c r="N14" t="str">
-        <v>2026-10-01T21:00:26.011Z</v>
+        <v>2026-10-01T21:10:19.841Z</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>sale_1790888378017</v>
+        <v>sale_1790889206450</v>
       </c>
       <c r="B15" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C15" t="str">
-        <v>3208546164</v>
+        <v>447348556756 - 2 Devices</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -1040,36 +1040,36 @@
         <v>abd149@kuromee.com</v>
       </c>
       <c r="H15" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K15" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L15" t="str">
-        <v>2026-11-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>2026-10-01T20:59:38.017Z</v>
+        <v>2026-10-01T21:13:26.450Z</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>sale_1790888324786</v>
+        <v>sale_1790889149110</v>
       </c>
       <c r="B16" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C16" t="str">
-        <v>3424112890 - 232013</v>
+        <v>3716928959</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -1084,48 +1084,48 @@
         <v>abd149@kuromee.com</v>
       </c>
       <c r="H16" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K16" t="str">
         <v>Paid</v>
       </c>
       <c r="L16" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>2026-10-01T20:58:44.786Z</v>
+        <v>2026-10-01T21:12:29.110Z</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>sale_1790871288858</v>
+        <v>sale_1790888980587</v>
       </c>
       <c r="B17" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C17" t="str">
-        <v>+92 336 6331621</v>
+        <v>+92 337 8569003</v>
       </c>
       <c r="D17" t="str">
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Muse AI</v>
+        <v>CapCut</v>
       </c>
       <c r="F17" t="str">
         <v>Private</v>
       </c>
       <c r="G17" t="str">
-        <v>NA</v>
+        <v>padmahastuti3@akunku.site|masuk123</v>
       </c>
       <c r="H17" t="str">
         <v>1 Month (30 Days)</v>
@@ -1134,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="K17" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L17" t="str">
         <v>2026-10-30</v>
@@ -1146,74 +1146,74 @@
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>2026-10-01T16:14:48.858Z</v>
+        <v>2026-10-01T21:09:40.587Z</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>sale_1790871264002</v>
+        <v>sale_1790888790593</v>
       </c>
       <c r="B18" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C18" t="str">
-        <v>+98 901 603 6081</v>
+        <v>+92 318 8934627</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F18" t="str">
         <v>Shared</v>
       </c>
       <c r="G18" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H18" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="K18" t="str">
         <v>Paid</v>
       </c>
       <c r="L18" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>2026-10-01T16:14:24.002Z</v>
+        <v>2026-10-01T21:06:30.593Z</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>sale_1790868862060</v>
+        <v>sale_1790888748366</v>
       </c>
       <c r="B19" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C19" t="str">
-        <v>+92 341 9010662</v>
+        <v>3121600439</v>
       </c>
       <c r="D19" t="str">
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F19" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G19" t="str">
-        <v>NA</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H19" t="str">
         <v>1 Month (30 Days)</v>
@@ -1222,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K19" t="str">
         <v>Paid</v>
@@ -1234,62 +1234,62 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>2026-10-01T15:34:22.075Z</v>
+        <v>2026-10-01T21:05:48.366Z</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>sale_1790864924575</v>
+        <v>sale_1790888549930</v>
       </c>
       <c r="B20" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C20" t="str">
-        <v>+92 313 6762957</v>
+        <v>3148646368</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F20" t="str">
         <v>Shared</v>
       </c>
       <c r="G20" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H20" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K20" t="str">
         <v>Paid</v>
       </c>
       <c r="L20" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>2026-10-01T14:28:44.576Z</v>
+        <v>2026-10-01T21:02:29.930Z</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>sale_1790864890520</v>
+        <v>sale_1790888489800</v>
       </c>
       <c r="B21" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C21" t="str">
-        <v>3166729551</v>
+        <v>3043943233 - 2 devices</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -1310,130 +1310,130 @@
         <v>3</v>
       </c>
       <c r="J21">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="K21" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L21" t="str">
         <v>2026-12-29</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Payment 5 Oct</v>
       </c>
       <c r="N21" t="str">
-        <v>2026-10-01T14:28:10.520Z</v>
+        <v>2026-10-01T21:01:29.800Z</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>sale_1790862744178</v>
+        <v>sale_1790888426010</v>
       </c>
       <c r="B22" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C22" t="str">
-        <v>+92 317 0295905</v>
+        <v>3125698180</v>
       </c>
       <c r="D22" t="str">
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F22" t="str">
         <v>Shared</v>
       </c>
       <c r="G22" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H22" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="K22" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L22" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>Payment Sunday 4 Oct</v>
       </c>
       <c r="N22" t="str">
-        <v>2026-10-01T13:52:24.178Z</v>
+        <v>2026-10-01T21:00:26.011Z</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>sale_1790861118501</v>
+        <v>sale_1790888378017</v>
       </c>
       <c r="B23" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C23" t="str">
-        <v>+92 344 4643148</v>
+        <v>3208546164</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F23" t="str">
         <v>Shared</v>
       </c>
       <c r="G23" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H23" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K23" t="str">
         <v>Paid</v>
       </c>
       <c r="L23" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>2026-10-01T13:25:18.501Z</v>
+        <v>2026-10-01T20:59:38.017Z</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>sale_1790853314445</v>
+        <v>sale_1790888324786</v>
       </c>
       <c r="B24" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C24" t="str">
-        <v>+92 302 7283125</v>
+        <v>3424112890 - 232013</v>
       </c>
       <c r="D24" t="str">
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>CapCut</v>
+        <v>Surfshark</v>
       </c>
       <c r="F24" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G24" t="str">
-        <v>NA</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H24" t="str">
         <v>1 Month (30 Days)</v>
@@ -1442,30 +1442,30 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K24" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L24" t="str">
         <v>2026-10-30</v>
       </c>
       <c r="M24" t="str">
-        <v>vukdsas@apricity.tech  masuk123</v>
+        <v/>
       </c>
       <c r="N24" t="str">
-        <v>2026-10-01T11:15:14.445Z</v>
+        <v>2026-10-01T20:58:44.786Z</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>sale_1790852538710</v>
+        <v>sale_1790871288858</v>
       </c>
       <c r="B25" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C25" t="str">
-        <v>+92 325 1501138</v>
+        <v>+92 336 6331621</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -1477,7 +1477,7 @@
         <v>Private</v>
       </c>
       <c r="G25" t="str">
-        <v>N/A</v>
+        <v>NA</v>
       </c>
       <c r="H25" t="str">
         <v>1 Month (30 Days)</v>
@@ -1486,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="K25" t="str">
         <v>Paid</v>
@@ -1498,74 +1498,74 @@
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>2026-10-01T11:02:18.710Z</v>
+        <v>2026-10-01T16:14:48.858Z</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>sale_1790852373016</v>
+        <v>sale_1790871264002</v>
       </c>
       <c r="B26" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C26" t="str">
-        <v>+92 301 7890066</v>
+        <v>+98 901 603 6081</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Muse AI</v>
+        <v>Nord</v>
       </c>
       <c r="F26" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G26" t="str">
-        <v>N/A</v>
+        <v>nord9@kuromee.com</v>
       </c>
       <c r="H26" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="K26" t="str">
         <v>Paid</v>
       </c>
       <c r="L26" t="str">
-        <v>2026-10-30</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>2026-10-01T10:59:33.016Z</v>
+        <v>2026-10-01T16:14:24.002Z</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>sale_1790850006978</v>
+        <v>sale_1790868862060</v>
       </c>
       <c r="B27" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C27" t="str">
-        <v>+92 342 4112890-534389</v>
+        <v>+92 341 9010662</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F27" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G27" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H27" t="str">
         <v>1 Month (30 Days)</v>
@@ -1574,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="K27" t="str">
         <v>Paid</v>
@@ -1586,106 +1586,106 @@
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>2026-10-01T10:20:06.978Z</v>
+        <v>2026-10-01T15:34:22.075Z</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>sale_1790849948623</v>
+        <v>sale_1790864924575</v>
       </c>
       <c r="B28" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C28" t="str">
-        <v>+92 349 6363398</v>
+        <v>+92 313 6762957</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F28" t="str">
         <v>Shared</v>
       </c>
       <c r="G28" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>nord9@kuromee.com</v>
       </c>
       <c r="H28" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="K28" t="str">
         <v>Paid</v>
       </c>
       <c r="L28" t="str">
-        <v>2026-10-30</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
-        <v>2026-10-01T10:19:08.625Z</v>
+        <v>2026-10-01T14:28:44.576Z</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>sale_1790844774858</v>
+        <v>sale_1790864890520</v>
       </c>
       <c r="B29" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C29" t="str">
-        <v>03035587360</v>
+        <v>3166729551</v>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Gemini Pro</v>
+        <v>Surfshark</v>
       </c>
       <c r="F29" t="str">
         <v>Shared</v>
       </c>
       <c r="G29" t="str">
-        <v>Not applicable</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H29" t="str">
-        <v>18 Months (540 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I29">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J29">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K29" t="str">
         <v>Paid</v>
       </c>
       <c r="L29" t="str">
-        <v>2028-03-23</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>2026-10-01T08:52:54.860Z</v>
+        <v>2026-10-01T14:28:10.520Z</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>sale_1790841917101</v>
+        <v>sale_1790862744178</v>
       </c>
       <c r="B30" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C30" t="str">
-        <v>+92 340 7317084</v>
+        <v>+92 317 0295905</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>3</v>
       </c>
       <c r="J30">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K30" t="str">
         <v>Paid</v>
@@ -1718,12 +1718,452 @@
         <v/>
       </c>
       <c r="N30" t="str">
+        <v>2026-10-01T13:52:24.178Z</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>sale_1790861118501</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C31" t="str">
+        <v>+92 344 4643148</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G31" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H31" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>500</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L31" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v>2026-10-01T13:25:18.501Z</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>sale_1790853314445</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C32" t="str">
+        <v>+92 302 7283125</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G32" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H32" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>750</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L32" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M32" t="str">
+        <v>vukdsas@apricity.tech  masuk123</v>
+      </c>
+      <c r="N32" t="str">
+        <v>2026-10-01T11:15:14.445Z</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>sale_1790852538710</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C33" t="str">
+        <v>+92 325 1501138</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H33" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1000</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L33" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v>2026-10-01T11:02:18.710Z</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>sale_1790852373016</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C34" t="str">
+        <v>+92 301 7890066</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H34" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>1500</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L34" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v>2026-10-01T10:59:33.016Z</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>sale_1790850006978</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C35" t="str">
+        <v>+92 342 4112890-534389</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G35" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H35" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>200</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L35" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v>2026-10-01T10:20:06.978Z</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>sale_1790849948623</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C36" t="str">
+        <v>+92 349 6363398</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G36" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H36" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>250</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L36" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v>2026-10-01T10:19:08.625Z</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>sale_1790844774858</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C37" t="str">
+        <v>03035587360</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Not applicable</v>
+      </c>
+      <c r="H37" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I37">
+        <v>18</v>
+      </c>
+      <c r="J37">
+        <v>500</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L37" t="str">
+        <v>2028-03-23</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v>2026-10-01T08:52:54.860Z</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>sale_1790841917101</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C38" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G38" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H38" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>500</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L38" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
         <v>2026-10-01T08:05:17.101Z</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>sale_1790839031379</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C39" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Nord9@kuromee.com</v>
+      </c>
+      <c r="H39" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>500</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L39" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v>2026-10-01T07:17:11.379Z</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>sale_1790838846301</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C40" t="str">
+        <v>3085352533</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G40" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H40" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40">
+        <v>800</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L40" t="str">
+        <v>2026-11-29</v>
+      </c>
+      <c r="M40" t="str">
+        <v>2 Devices</v>
+      </c>
+      <c r="N40" t="str">
+        <v>2026-10-01T07:14:06.302Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N40"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,57 +447,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1790934819273</v>
+        <v>sale_1790972901458</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C2" t="str">
-        <v>3362088885</v>
+        <v>+92 333 3707266</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F2" t="str">
         <v>Shared</v>
       </c>
       <c r="G2" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>nord9@kuromee.com</v>
       </c>
       <c r="H2" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="K2" t="str">
         <v>Paid</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-31</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-10-02T09:53:39.274Z</v>
+        <v>2026-10-02T20:28:21.458Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sale_1790934132194</v>
+        <v>sale_1790971693632</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C3" t="str">
-        <v>3171626906</v>
+        <v>3038522190</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -512,36 +512,36 @@
         <v>abd150@kuromee.com</v>
       </c>
       <c r="H3" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K3" t="str">
         <v>Paid</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-01</v>
       </c>
       <c r="M3" t="str">
         <v/>
       </c>
       <c r="N3" t="str">
-        <v>2026-10-02T09:42:12.194Z</v>
+        <v>2026-10-02T20:08:13.632Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>sale_1790929984076</v>
+        <v>sale_1790967903952</v>
       </c>
       <c r="B4" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C4" t="str">
-        <v>3425091286</v>
+        <v>3452401920</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -556,48 +556,48 @@
         <v>abd150@kuromee.com</v>
       </c>
       <c r="H4" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K4" t="str">
         <v>Paid</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-30</v>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>2026-10-02T08:33:04.076Z</v>
+        <v>2026-10-02T19:05:03.952Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>sale_1790928896570</v>
+        <v>sale_1790966446338</v>
       </c>
       <c r="B5" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C5" t="str">
-        <v>+92 335 9333443</v>
+        <v>3162936885</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F5" t="str">
         <v>Shared</v>
       </c>
       <c r="G5" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H5" t="str">
         <v>1 Month (30 Days)</v>
@@ -606,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="K5" t="str">
         <v>Paid</v>
@@ -618,18 +618,18 @@
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>2026-10-02T08:14:56.570Z</v>
+        <v>2026-10-02T18:40:46.338Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>sale_1790927823366</v>
+        <v>sale_1790964840039</v>
       </c>
       <c r="B6" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C6" t="str">
-        <v>3424112890 - 178132</v>
+        <v>3068258151</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -650,10 +650,10 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K6" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L6" t="str">
         <v>2026-10-31</v>
@@ -662,30 +662,30 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>2026-10-02T07:57:03.366Z</v>
+        <v>2026-10-02T18:14:00.039Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>sale_1790927720999</v>
+        <v>sale_1790964482569</v>
       </c>
       <c r="B7" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C7" t="str">
-        <v>3355060692</v>
+        <v>+92 334 7132394</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F7" t="str">
         <v>Shared</v>
       </c>
       <c r="G7" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H7" t="str">
         <v>1 Month (30 Days)</v>
@@ -694,7 +694,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K7" t="str">
         <v>Paid</v>
@@ -706,62 +706,62 @@
         <v/>
       </c>
       <c r="N7" t="str">
-        <v>2026-10-02T07:55:20.999Z</v>
+        <v>2026-10-02T18:08:02.570Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>sale_1790927520048</v>
+        <v>sale_1790964455099</v>
       </c>
       <c r="B8" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C8" t="str">
-        <v>3237432065</v>
+        <v>+92 318 8934627</v>
       </c>
       <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F8" t="str">
         <v>Shared</v>
       </c>
       <c r="G8" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H8" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="K8" t="str">
         <v>Paid</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-11-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M8" t="str">
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>2026-10-02T07:52:00.048Z</v>
+        <v>2026-10-02T18:07:35.099Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>sale_1790927399372</v>
+        <v>sale_1790955121286</v>
       </c>
       <c r="B9" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C9" t="str">
-        <v>3226763778</v>
+        <v>3424112890 - 810813</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -782,10 +782,10 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K9" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L9" t="str">
         <v>2026-10-31</v>
@@ -794,30 +794,30 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>2026-10-02T07:49:59.372Z</v>
+        <v>2026-10-02T15:32:01.286Z</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>sale_1790927194315</v>
+        <v>sale_1790954315594</v>
       </c>
       <c r="B10" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C10" t="str">
-        <v>3087182016</v>
+        <v>+92 339 8895511</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F10" t="str">
         <v>Shared</v>
       </c>
       <c r="G10" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H10" t="str">
         <v>1 Month (30 Days)</v>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>250</v>
+        <v>1200</v>
       </c>
       <c r="K10" t="str">
         <v>Paid</v>
@@ -838,118 +838,118 @@
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>2026-10-02T07:46:34.315Z</v>
+        <v>2026-10-02T15:18:35.594Z</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>sale_1790926790421</v>
+        <v>sale_1790946519871</v>
       </c>
       <c r="B11" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C11" t="str">
-        <v>3424112890 - 161547</v>
+        <v>+92 337 4695990</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F11" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G11" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H11" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>200</v>
+        <v>1300</v>
       </c>
       <c r="K11" t="str">
         <v>Paid</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-30</v>
       </c>
       <c r="M11" t="str">
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>2026-10-02T07:39:50.422Z</v>
+        <v>2026-10-02T13:08:39.871Z</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>sale_1790890878620</v>
+        <v>sale_1790946456992</v>
       </c>
       <c r="B12" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C12" t="str">
-        <v>3336677666</v>
+        <v>+92 310 8747472</v>
       </c>
       <c r="D12" t="str">
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F12" t="str">
         <v>Shared</v>
       </c>
       <c r="G12" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>nor8@kuromee.com</v>
       </c>
       <c r="H12" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>6 Months (180 Days)</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="K12" t="str">
         <v>Paid</v>
       </c>
       <c r="L12" t="str">
-        <v>2026-10-31</v>
+        <v>2027-03-30</v>
       </c>
       <c r="M12" t="str">
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>2026-10-01T21:41:18.621Z</v>
+        <v>2026-10-02T13:07:36.993Z</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>sale_1790889330982</v>
+        <v>sale_1790941037212</v>
       </c>
       <c r="B13" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C13" t="str">
-        <v>+92 333 7180888</v>
+        <v>30474552522</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F13" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G13" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H13" t="str">
         <v>1 Month (30 Days)</v>
@@ -958,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K13" t="str">
         <v>Paid</v>
@@ -970,74 +970,74 @@
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>2026-10-01T21:15:30.982Z</v>
+        <v>2026-10-02T11:37:17.212Z</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>sale_1790889019841</v>
+        <v>sale_1790940354053</v>
       </c>
       <c r="B14" t="str">
         <v>2026-10-02</v>
       </c>
       <c r="C14" t="str">
-        <v>+92 324 3715759</v>
+        <v>+92 333 5598645</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F14" t="str">
         <v>Private</v>
       </c>
       <c r="G14" t="str">
-        <v>NA</v>
+        <v>alissaturner822@gmail.com</v>
       </c>
       <c r="H14" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="K14" t="str">
         <v>Paid</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-30</v>
       </c>
       <c r="M14" t="str">
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>2026-10-01T21:10:19.841Z</v>
+        <v>2026-10-02T11:25:54.053Z</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>sale_1790889206450</v>
+        <v>sale_1790939431495</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C15" t="str">
-        <v>447348556756 - 2 Devices</v>
+        <v>+92 301 2553778</v>
       </c>
       <c r="D15" t="str">
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F15" t="str">
         <v>Shared</v>
       </c>
       <c r="G15" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H15" t="str">
         <v>1 Month (30 Days)</v>
@@ -1046,30 +1046,30 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="K15" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L15" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>2026-10-01T21:13:26.450Z</v>
+        <v>2026-10-02T11:10:31.495Z</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>sale_1790889149110</v>
+        <v>sale_1790936221232</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C16" t="str">
-        <v>3716928959</v>
+        <v>3362088885</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -1081,51 +1081,51 @@
         <v>Shared</v>
       </c>
       <c r="G16" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H16" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K16" t="str">
         <v>Paid</v>
       </c>
       <c r="L16" t="str">
-        <v>2026-11-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>2026-10-01T21:12:29.110Z</v>
+        <v>2026-10-02T10:17:01.232Z</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>sale_1790888980587</v>
+        <v>sale_1790934819273</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C17" t="str">
-        <v>+92 337 8569003</v>
+        <v>3362088885</v>
       </c>
       <c r="D17" t="str">
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>CapCut</v>
+        <v>Surfshark</v>
       </c>
       <c r="F17" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G17" t="str">
-        <v>padmahastuti3@akunku.site|masuk123</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H17" t="str">
         <v>1 Month (30 Days)</v>
@@ -1134,42 +1134,42 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K17" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L17" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>2026-10-01T21:09:40.587Z</v>
+        <v>2026-10-02T09:53:39.274Z</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>sale_1790888790593</v>
+        <v>sale_1790934132194</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C18" t="str">
-        <v>+92 318 8934627</v>
+        <v>3171626906</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F18" t="str">
         <v>Shared</v>
       </c>
       <c r="G18" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H18" t="str">
         <v>1 Month (30 Days)</v>
@@ -1178,30 +1178,30 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="K18" t="str">
         <v>Paid</v>
       </c>
       <c r="L18" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>2026-10-01T21:06:30.593Z</v>
+        <v>2026-10-02T09:42:12.194Z</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>sale_1790888748366</v>
+        <v>sale_1790929984076</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C19" t="str">
-        <v>3121600439</v>
+        <v>3425091286</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -1213,7 +1213,7 @@
         <v>Shared</v>
       </c>
       <c r="G19" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H19" t="str">
         <v>1 Month (30 Days)</v>
@@ -1228,36 +1228,36 @@
         <v>Paid</v>
       </c>
       <c r="L19" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>2026-10-01T21:05:48.366Z</v>
+        <v>2026-10-02T08:33:04.076Z</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>sale_1790888549930</v>
+        <v>sale_1790928896570</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C20" t="str">
-        <v>3148646368</v>
+        <v>+92 335 9333443</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F20" t="str">
         <v>Shared</v>
       </c>
       <c r="G20" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H20" t="str">
         <v>1 Month (30 Days)</v>
@@ -1266,30 +1266,30 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="K20" t="str">
         <v>Paid</v>
       </c>
       <c r="L20" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>2026-10-01T21:02:29.930Z</v>
+        <v>2026-10-02T08:14:56.570Z</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>sale_1790888489800</v>
+        <v>sale_1790927823366</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C21" t="str">
-        <v>3043943233 - 2 devices</v>
+        <v>3424112890 - 178132</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -1301,39 +1301,39 @@
         <v>Shared</v>
       </c>
       <c r="G21" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H21" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="K21" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L21" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M21" t="str">
-        <v>Payment 5 Oct</v>
+        <v/>
       </c>
       <c r="N21" t="str">
-        <v>2026-10-01T21:01:29.800Z</v>
+        <v>2026-10-02T07:57:03.366Z</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>sale_1790888426010</v>
+        <v>sale_1790927720999</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C22" t="str">
-        <v>3125698180</v>
+        <v>3355060692</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -1345,39 +1345,39 @@
         <v>Shared</v>
       </c>
       <c r="G22" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H22" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K22" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L22" t="str">
-        <v>2026-11-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M22" t="str">
-        <v>Payment Sunday 4 Oct</v>
+        <v/>
       </c>
       <c r="N22" t="str">
-        <v>2026-10-01T21:00:26.011Z</v>
+        <v>2026-10-02T07:55:20.999Z</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>sale_1790888378017</v>
+        <v>sale_1790927520048</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C23" t="str">
-        <v>3208546164</v>
+        <v>3237432065</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Shared</v>
       </c>
       <c r="G23" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H23" t="str">
         <v>2 Months (60 Days)</v>
@@ -1404,24 +1404,24 @@
         <v>Paid</v>
       </c>
       <c r="L23" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-30</v>
       </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>2026-10-01T20:59:38.017Z</v>
+        <v>2026-10-02T07:52:00.048Z</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>sale_1790888324786</v>
+        <v>sale_1790927399372</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C24" t="str">
-        <v>3424112890 - 232013</v>
+        <v>3226763778</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>Shared</v>
       </c>
       <c r="G24" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H24" t="str">
         <v>1 Month (30 Days)</v>
@@ -1448,36 +1448,36 @@
         <v>Paid</v>
       </c>
       <c r="L24" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>2026-10-01T20:58:44.786Z</v>
+        <v>2026-10-02T07:49:59.372Z</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>sale_1790871288858</v>
+        <v>sale_1790927194315</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C25" t="str">
-        <v>+92 336 6331621</v>
+        <v>3087182016</v>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F25" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G25" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H25" t="str">
         <v>1 Month (30 Days)</v>
@@ -1486,86 +1486,86 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="K25" t="str">
         <v>Paid</v>
       </c>
       <c r="L25" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>2026-10-01T16:14:48.858Z</v>
+        <v>2026-10-02T07:46:34.315Z</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>sale_1790871264002</v>
+        <v>sale_1790926790421</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C26" t="str">
-        <v>+98 901 603 6081</v>
+        <v>3424112890 - 161547</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F26" t="str">
         <v>Shared</v>
       </c>
       <c r="G26" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H26" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K26" t="str">
         <v>Paid</v>
       </c>
       <c r="L26" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>2026-10-01T16:14:24.002Z</v>
+        <v>2026-10-02T07:39:50.422Z</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>sale_1790868862060</v>
+        <v>sale_1790890878620</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C27" t="str">
-        <v>+92 341 9010662</v>
+        <v>3336677666</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F27" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G27" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H27" t="str">
         <v>1 Month (30 Days)</v>
@@ -1574,206 +1574,206 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K27" t="str">
         <v>Paid</v>
       </c>
       <c r="L27" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>2026-10-01T15:34:22.075Z</v>
+        <v>2026-10-01T21:41:18.621Z</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>sale_1790864924575</v>
+        <v>sale_1790889330982</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C28" t="str">
-        <v>+92 313 6762957</v>
+        <v>+92 333 7180888</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F28" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G28" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H28" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K28" t="str">
         <v>Paid</v>
       </c>
       <c r="L28" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
-        <v>2026-10-01T14:28:44.576Z</v>
+        <v>2026-10-01T21:15:30.982Z</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>sale_1790864890520</v>
+        <v>sale_1790889019841</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C29" t="str">
-        <v>3166729551</v>
+        <v>+92 324 3715759</v>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F29" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G29" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H29" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="K29" t="str">
         <v>Paid</v>
       </c>
       <c r="L29" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>2026-10-01T14:28:10.520Z</v>
+        <v>2026-10-01T21:10:19.841Z</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>sale_1790862744178</v>
+        <v>sale_1790889206450</v>
       </c>
       <c r="B30" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C30" t="str">
-        <v>+92 317 0295905</v>
+        <v>447348556756 - 2 Devices</v>
       </c>
       <c r="D30" t="str">
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F30" t="str">
         <v>Shared</v>
       </c>
       <c r="G30" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H30" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K30" t="str">
         <v>Paid</v>
       </c>
       <c r="L30" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M30" t="str">
         <v/>
       </c>
       <c r="N30" t="str">
-        <v>2026-10-01T13:52:24.178Z</v>
+        <v>2026-10-01T21:13:26.450Z</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>sale_1790861118501</v>
+        <v>sale_1790889149110</v>
       </c>
       <c r="B31" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C31" t="str">
-        <v>+92 344 4643148</v>
+        <v>3716928959</v>
       </c>
       <c r="D31" t="str">
         <v/>
       </c>
       <c r="E31" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F31" t="str">
         <v>Shared</v>
       </c>
       <c r="G31" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H31" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K31" t="str">
         <v>Paid</v>
       </c>
       <c r="L31" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M31" t="str">
         <v/>
       </c>
       <c r="N31" t="str">
-        <v>2026-10-01T13:25:18.501Z</v>
+        <v>2026-10-01T21:12:29.110Z</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>sale_1790853314445</v>
+        <v>sale_1790888980587</v>
       </c>
       <c r="B32" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C32" t="str">
-        <v>+92 302 7283125</v>
+        <v>+92 337 8569003</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -1785,7 +1785,7 @@
         <v>Private</v>
       </c>
       <c r="G32" t="str">
-        <v>NA</v>
+        <v>padmahastuti3@akunku.site|masuk123</v>
       </c>
       <c r="H32" t="str">
         <v>1 Month (30 Days)</v>
@@ -1803,21 +1803,21 @@
         <v>2026-10-30</v>
       </c>
       <c r="M32" t="str">
-        <v>vukdsas@apricity.tech  masuk123</v>
+        <v/>
       </c>
       <c r="N32" t="str">
-        <v>2026-10-01T11:15:14.445Z</v>
+        <v>2026-10-01T21:09:40.587Z</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>sale_1790852538710</v>
+        <v>sale_1790888790593</v>
       </c>
       <c r="B33" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C33" t="str">
-        <v>+92 325 1501138</v>
+        <v>+92 318 8934627</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1826,10 +1826,10 @@
         <v>Muse AI</v>
       </c>
       <c r="F33" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G33" t="str">
-        <v>N/A</v>
+        <v>NA</v>
       </c>
       <c r="H33" t="str">
         <v>1 Month (30 Days)</v>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="K33" t="str">
         <v>Paid</v>
@@ -1850,30 +1850,30 @@
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>2026-10-01T11:02:18.710Z</v>
+        <v>2026-10-01T21:06:30.593Z</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>sale_1790852373016</v>
+        <v>sale_1790888748366</v>
       </c>
       <c r="B34" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C34" t="str">
-        <v>+92 301 7890066</v>
+        <v>3121600439</v>
       </c>
       <c r="D34" t="str">
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F34" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G34" t="str">
-        <v>N/A</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H34" t="str">
         <v>1 Month (30 Days)</v>
@@ -1882,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="K34" t="str">
         <v>Paid</v>
@@ -1894,18 +1894,18 @@
         <v/>
       </c>
       <c r="N34" t="str">
-        <v>2026-10-01T10:59:33.016Z</v>
+        <v>2026-10-01T21:05:48.366Z</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>sale_1790850006978</v>
+        <v>sale_1790888549930</v>
       </c>
       <c r="B35" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C35" t="str">
-        <v>+92 342 4112890-534389</v>
+        <v>3148646368</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -1938,18 +1938,18 @@
         <v/>
       </c>
       <c r="N35" t="str">
-        <v>2026-10-01T10:20:06.978Z</v>
+        <v>2026-10-01T21:02:29.930Z</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>sale_1790849948623</v>
+        <v>sale_1790888489800</v>
       </c>
       <c r="B36" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C36" t="str">
-        <v>+92 349 6363398</v>
+        <v>3043943233 - 2 devices</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -1964,213 +1964,873 @@
         <v>abd149@kuromee.com</v>
       </c>
       <c r="H36" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K36" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L36" t="str">
-        <v>2026-10-30</v>
+        <v>2026-12-29</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>Payment 5 Oct</v>
       </c>
       <c r="N36" t="str">
-        <v>2026-10-01T10:19:08.625Z</v>
+        <v>2026-10-01T21:01:29.800Z</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>sale_1790844774858</v>
+        <v>sale_1790888426010</v>
       </c>
       <c r="B37" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C37" t="str">
-        <v>03035587360</v>
+        <v>3125698180</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>Gemini Pro</v>
+        <v>Surfshark</v>
       </c>
       <c r="F37" t="str">
         <v>Shared</v>
       </c>
       <c r="G37" t="str">
-        <v>Not applicable</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H37" t="str">
-        <v>18 Months (540 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I37">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K37" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L37" t="str">
-        <v>2028-03-23</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>Payment Sunday 4 Oct</v>
       </c>
       <c r="N37" t="str">
-        <v>2026-10-01T08:52:54.860Z</v>
+        <v>2026-10-01T21:00:26.011Z</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>sale_1790841917101</v>
+        <v>sale_1790888378017</v>
       </c>
       <c r="B38" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C38" t="str">
-        <v>+92 340 7317084</v>
+        <v>3208546164</v>
       </c>
       <c r="D38" t="str">
         <v/>
       </c>
       <c r="E38" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F38" t="str">
         <v>Shared</v>
       </c>
       <c r="G38" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H38" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K38" t="str">
         <v>Paid</v>
       </c>
       <c r="L38" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-29</v>
       </c>
       <c r="M38" t="str">
         <v/>
       </c>
       <c r="N38" t="str">
-        <v>2026-10-01T08:05:17.101Z</v>
+        <v>2026-10-01T20:59:38.017Z</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>sale_1790839031379</v>
+        <v>sale_1790888324786</v>
       </c>
       <c r="B39" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C39" t="str">
-        <v>+92 340 7317084</v>
+        <v>3424112890 - 232013</v>
       </c>
       <c r="D39" t="str">
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F39" t="str">
         <v>Shared</v>
       </c>
       <c r="G39" t="str">
-        <v>Nord9@kuromee.com</v>
+        <v>abd149@kuromee.com</v>
       </c>
       <c r="H39" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K39" t="str">
         <v>Paid</v>
       </c>
       <c r="L39" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="M39" t="str">
         <v/>
       </c>
       <c r="N39" t="str">
-        <v>2026-10-01T07:17:11.379Z</v>
+        <v>2026-10-01T20:58:44.786Z</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>sale_1790838846301</v>
+        <v>sale_1790871288858</v>
       </c>
       <c r="B40" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C40" t="str">
+        <v>+92 336 6331621</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G40" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H40" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>1200</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L40" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v>2026-10-01T16:14:48.858Z</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>sale_1790871264002</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C41" t="str">
+        <v>+98 901 603 6081</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G41" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H41" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>500</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L41" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v>2026-10-01T16:14:24.002Z</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>sale_1790868862060</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C42" t="str">
+        <v>+92 341 9010662</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G42" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H42" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>1000</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L42" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v>2026-10-01T15:34:22.075Z</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>sale_1790864924575</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C43" t="str">
+        <v>+92 313 6762957</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G43" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H43" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I43">
+        <v>3</v>
+      </c>
+      <c r="J43">
+        <v>500</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L43" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v>2026-10-01T14:28:44.576Z</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>sale_1790864890520</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C44" t="str">
+        <v>3166729551</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G44" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H44" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>600</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L44" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v>2026-10-01T14:28:10.520Z</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>sale_1790862744178</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C45" t="str">
+        <v>+92 317 0295905</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G45" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H45" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45">
+        <v>600</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L45" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v>2026-10-01T13:52:24.178Z</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>sale_1790861118501</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C46" t="str">
+        <v>+92 344 4643148</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G46" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H46" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>500</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L46" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v>2026-10-01T13:25:18.501Z</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>sale_1790853314445</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C47" t="str">
+        <v>+92 302 7283125</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G47" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H47" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>750</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L47" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M47" t="str">
+        <v>vukdsas@apricity.tech  masuk123</v>
+      </c>
+      <c r="N47" t="str">
+        <v>2026-10-01T11:15:14.445Z</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>sale_1790852538710</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C48" t="str">
+        <v>+92 325 1501138</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G48" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H48" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>1000</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L48" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v>2026-10-01T11:02:18.710Z</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>sale_1790852373016</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C49" t="str">
+        <v>+92 301 7890066</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G49" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H49" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>1500</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L49" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v>2026-10-01T10:59:33.016Z</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>sale_1790850006978</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C50" t="str">
+        <v>+92 342 4112890-534389</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G50" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H50" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>200</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L50" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v>2026-10-01T10:20:06.978Z</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>sale_1790849948623</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C51" t="str">
+        <v>+92 349 6363398</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G51" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H51" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>250</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L51" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v>2026-10-01T10:19:08.625Z</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>sale_1790844774858</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C52" t="str">
+        <v>03035587360</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Not applicable</v>
+      </c>
+      <c r="H52" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I52">
+        <v>18</v>
+      </c>
+      <c r="J52">
+        <v>500</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L52" t="str">
+        <v>2028-03-23</v>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v>2026-10-01T08:52:54.860Z</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>sale_1790841917101</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C53" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G53" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H53" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I53">
+        <v>3</v>
+      </c>
+      <c r="J53">
+        <v>500</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L53" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v>2026-10-01T08:05:17.101Z</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>sale_1790839031379</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C54" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Nord9@kuromee.com</v>
+      </c>
+      <c r="H54" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I54">
+        <v>3</v>
+      </c>
+      <c r="J54">
+        <v>500</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L54" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v>2026-10-01T07:17:11.379Z</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>sale_1790838846301</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C55" t="str">
         <v>3085352533</v>
       </c>
-      <c r="D40" t="str">
-        <v/>
-      </c>
-      <c r="E40" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="F40" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="G40" t="str">
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G55" t="str">
         <v>abd149@kuromee.com</v>
       </c>
-      <c r="H40" t="str">
+      <c r="H55" t="str">
         <v>2 Months (60 Days)</v>
       </c>
-      <c r="I40">
+      <c r="I55">
         <v>2</v>
       </c>
-      <c r="J40">
+      <c r="J55">
         <v>800</v>
       </c>
-      <c r="K40" t="str">
+      <c r="K55" t="str">
         <v>Pending</v>
       </c>
-      <c r="L40" t="str">
+      <c r="L55" t="str">
         <v>2026-11-29</v>
       </c>
-      <c r="M40" t="str">
+      <c r="M55" t="str">
         <v>2 Devices</v>
       </c>
-      <c r="N40" t="str">
+      <c r="N55" t="str">
         <v>2026-10-01T07:14:06.302Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N55"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2194,47 +2854,47 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>exp_1790810881227_1bq9</v>
+        <v>exp_1790946533413</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C2" t="str">
-        <v>Meta Ads</v>
+        <v>Vendor Purchasing</v>
       </c>
       <c r="D2" t="str">
-        <v>Meta Ads Campaign</v>
+        <v>Nord purchasing</v>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-09-30T23:28:01.227Z</v>
+        <v>2026-10-02T13:08:53.414Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>exp_1790889252470</v>
+        <v>exp_1790940392222</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C3" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D3" t="str">
-        <v>Surfshark/Nord Paid</v>
+        <v>alissaturner822@gmail.com   Surfshark Private Payment</v>
       </c>
       <c r="E3">
-        <v>1600</v>
+        <v>750</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-10-01T21:14:12.470Z</v>
+        <v>2026-10-02T11:26:32.222Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>exp_1790888895390</v>
+        <v>exp_1790889252470</v>
       </c>
       <c r="B4" t="str">
         <v>2026-10-01</v>
@@ -2243,18 +2903,18 @@
         <v>Vendor Purchasing</v>
       </c>
       <c r="D4" t="str">
-        <v>Capcut padmahastuti3@akunku.site|masuk123</v>
+        <v>Surfshark/Nord Paid</v>
       </c>
       <c r="E4">
-        <v>350</v>
+        <v>1600</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-10-01T21:08:15.390Z</v>
+        <v>2026-10-01T21:14:12.470Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>exp_1790865001001</v>
+        <v>exp_1790888895390</v>
       </c>
       <c r="B5" t="str">
         <v>2026-10-01</v>
@@ -2263,18 +2923,58 @@
         <v>Vendor Purchasing</v>
       </c>
       <c r="D5" t="str">
-        <v>Capcut Account For Luxury online Store   vukdsas@apricity.tech:masuk123</v>
+        <v>Capcut padmahastuti3@akunku.site|masuk123</v>
       </c>
       <c r="E5">
         <v>350</v>
       </c>
       <c r="F5" t="str">
+        <v>2026-10-01T21:08:15.390Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>exp_1790865001001</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Capcut Account For Luxury online Store   vukdsas@apricity.tech:masuk123</v>
+      </c>
+      <c r="E6">
+        <v>350</v>
+      </c>
+      <c r="F6" t="str">
         <v>2026-10-01T14:30:01.001Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>exp_1790810881227_1bq9</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Meta Ads</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Meta Ads Campaign</v>
+      </c>
+      <c r="E7">
+        <v>500</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-09-30T23:28:01.227Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -2981,7 +2981,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3289,9 +3289,26 @@
         <v>500</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Test Product</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="str">
+        <v>1M</v>
+      </c>
+      <c r="E19">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -2981,7 +2981,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3289,26 +3289,9 @@
         <v>500</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Test Product</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="str">
-        <v>1M</v>
-      </c>
-      <c r="E19">
-        <v>100</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -5,7 +5,6 @@
   <sheets>
     <sheet name="Sales" sheetId="1" r:id="rId1"/>
     <sheet name="Expenses" sheetId="2" r:id="rId2"/>
-    <sheet name="Products" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N89"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,189 +446,189 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1790972901458</v>
+        <v>sale_1791205614503</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C2" t="str">
-        <v>+92 333 3707266</v>
+        <v>+92 344 9282193</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F2" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G2" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H2" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K2" t="str">
         <v>Paid</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-12-31</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-10-02T20:28:21.458Z</v>
+        <v>2026-10-05T13:06:54.503Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sale_1790971693632</v>
+        <v>sale_1791205520863</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C3" t="str">
-        <v>3038522190</v>
+        <v>+92 336 2088885</v>
       </c>
       <c r="D3" t="str">
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>Surfshark</v>
+        <v>CapCut</v>
       </c>
       <c r="F3" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G3" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>baktionopradana64@akunku.site  masuk123  qaoyxh@apricity.tech  masuk123</v>
       </c>
       <c r="H3" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="K3" t="str">
         <v>Paid</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-12-01</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2 Capcut</v>
       </c>
       <c r="N3" t="str">
-        <v>2026-10-02T20:08:13.632Z</v>
+        <v>2026-10-05T13:05:20.863Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>sale_1790967903952</v>
+        <v>sale_1791205472496</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C4" t="str">
-        <v>3452401920</v>
+        <v>+92 300 2689698</v>
       </c>
       <c r="D4" t="str">
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F4" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G4" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H4" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="K4" t="str">
         <v>Paid</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-11-30</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>2026-10-02T19:05:03.952Z</v>
+        <v>2026-10-05T13:04:32.497Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>sale_1790966446338</v>
+        <v>sale_1791193680484</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C5" t="str">
-        <v>3162936885</v>
+        <v>+92 341 5984031</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F5" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G5" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H5" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="K5" t="str">
         <v>Paid</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>2026-10-02T18:40:46.338Z</v>
+        <v>2026-10-05T09:48:00.484Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>sale_1790964840039</v>
+        <v>sale_1791191267464</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C6" t="str">
-        <v>3068258151</v>
+        <v>3317376555</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -641,7 +640,7 @@
         <v>Shared</v>
       </c>
       <c r="G6" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H6" t="str">
         <v>1 Month (30 Days)</v>
@@ -656,80 +655,80 @@
         <v>Paid</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M6" t="str">
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>2026-10-02T18:14:00.039Z</v>
+        <v>2026-10-05T09:07:47.464Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>sale_1790964482569</v>
+        <v>sale_1791187749963</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C7" t="str">
-        <v>+92 334 7132394</v>
+        <v>+92 326 4813460</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Muse AI</v>
+        <v>Nord</v>
       </c>
       <c r="F7" t="str">
         <v>Shared</v>
       </c>
       <c r="G7" t="str">
-        <v>NA</v>
+        <v>nord10@kuromee.com</v>
       </c>
       <c r="H7" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="K7" t="str">
         <v>Paid</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-10-31</v>
+        <v>2027-01-02</v>
       </c>
       <c r="M7" t="str">
         <v/>
       </c>
       <c r="N7" t="str">
-        <v>2026-10-02T18:08:02.570Z</v>
+        <v>2026-10-05T08:09:09.963Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>sale_1790964455099</v>
+        <v>sale_1791187520074</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C8" t="str">
-        <v>+92 318 8934627</v>
+        <v>3005130980</v>
       </c>
       <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F8" t="str">
         <v>Shared</v>
       </c>
       <c r="G8" t="str">
-        <v>NA</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H8" t="str">
         <v>1 Month (30 Days)</v>
@@ -738,30 +737,30 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K8" t="str">
         <v>Paid</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M8" t="str">
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>2026-10-02T18:07:35.099Z</v>
+        <v>2026-10-05T08:05:20.074Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>sale_1790955121286</v>
+        <v>sale_1791187470511</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C9" t="str">
-        <v>3424112890 - 810813</v>
+        <v>3443570380</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -773,7 +772,7 @@
         <v>Shared</v>
       </c>
       <c r="G9" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H9" t="str">
         <v>1 Month (30 Days)</v>
@@ -788,74 +787,74 @@
         <v>Pending</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M9" t="str">
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>2026-10-02T15:32:01.286Z</v>
+        <v>2026-10-05T08:04:30.511Z</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>sale_1790954315594</v>
+        <v>sale_1791187181909</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C10" t="str">
-        <v>+92 339 8895511</v>
+        <v>+92 319 5466691</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Muse AI</v>
+        <v>Gemini Pro</v>
       </c>
       <c r="F10" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G10" t="str">
         <v>NA</v>
       </c>
       <c r="H10" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>18 Months (540 Days)</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J10">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="K10" t="str">
         <v>Paid</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-10-31</v>
+        <v>2028-03-27</v>
       </c>
       <c r="M10" t="str">
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>2026-10-02T15:18:35.594Z</v>
+        <v>2026-10-05T07:59:41.909Z</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>sale_1790946519871</v>
+        <v>sale_1791184673171</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C11" t="str">
-        <v>+92 337 4695990</v>
+        <v>+92 303 5733146</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F11" t="str">
         <v>Private</v>
@@ -864,80 +863,80 @@
         <v>NA</v>
       </c>
       <c r="H11" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="K11" t="str">
         <v>Paid</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-12-30</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M11" t="str">
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>2026-10-02T13:08:39.871Z</v>
+        <v>2026-10-05T07:17:53.172Z</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>sale_1790946456992</v>
+        <v>sale_1791183478163</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C12" t="str">
-        <v>+92 310 8747472</v>
+        <v>3425091286</v>
       </c>
       <c r="D12" t="str">
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F12" t="str">
         <v>Shared</v>
       </c>
       <c r="G12" t="str">
-        <v>nor8@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H12" t="str">
-        <v>6 Months (180 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="K12" t="str">
         <v>Paid</v>
       </c>
       <c r="L12" t="str">
-        <v>2027-03-30</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M12" t="str">
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>2026-10-02T13:07:36.993Z</v>
+        <v>2026-10-05T06:57:58.163Z</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>sale_1790941037212</v>
+        <v>sale_1791183466887</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C13" t="str">
-        <v>30474552522</v>
+        <v>3199182226</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -949,7 +948,7 @@
         <v>Shared</v>
       </c>
       <c r="G13" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H13" t="str">
         <v>1 Month (30 Days)</v>
@@ -964,156 +963,156 @@
         <v>Paid</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M13" t="str">
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>2026-10-02T11:37:17.212Z</v>
+        <v>2026-10-05T06:57:46.887Z</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>sale_1790940354053</v>
+        <v>sale_1791153252198</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C14" t="str">
-        <v>+92 333 5598645</v>
+        <v>+92 326 7000168</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F14" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G14" t="str">
-        <v>alissaturner822@gmail.com</v>
+        <v>nord9@kuromee.com</v>
       </c>
       <c r="H14" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="K14" t="str">
         <v>Paid</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-11-30</v>
+        <v>2027-01-02</v>
       </c>
       <c r="M14" t="str">
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>2026-10-02T11:25:54.053Z</v>
+        <v>2026-10-04T22:34:12.198Z</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>sale_1790939431495</v>
+        <v>sale_1791138731891</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C15" t="str">
-        <v>+92 301 2553778</v>
+        <v>+92 309 6116899</v>
       </c>
       <c r="D15" t="str">
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Muse AI</v>
+        <v>Gemini Pro</v>
       </c>
       <c r="F15" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G15" t="str">
         <v>NA</v>
       </c>
       <c r="H15" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>18 Months (540 Days)</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J15">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="K15" t="str">
         <v>Paid</v>
       </c>
       <c r="L15" t="str">
-        <v>2026-10-31</v>
+        <v>2028-03-26</v>
       </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>2026-10-02T11:10:31.495Z</v>
+        <v>2026-10-04T18:32:11.892Z</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>sale_1790936221232</v>
+        <v>sale_1791137994648</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C16" t="str">
-        <v>3362088885</v>
+        <v>+92 302 4827701</v>
       </c>
       <c r="D16" t="str">
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Surfshark</v>
+        <v>Gemini Pro</v>
       </c>
       <c r="F16" t="str">
         <v>Shared</v>
       </c>
       <c r="G16" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H16" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>18 Months (540 Days)</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J16">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="K16" t="str">
         <v>Paid</v>
       </c>
       <c r="L16" t="str">
-        <v>2026-10-31</v>
+        <v>2028-03-26</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>2026-10-02T10:17:01.232Z</v>
+        <v>2026-10-04T18:19:54.648Z</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>sale_1790934819273</v>
+        <v>sale_1791136834025</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C17" t="str">
-        <v>3362088885</v>
+        <v>3126811828</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -1125,7 +1124,7 @@
         <v>Shared</v>
       </c>
       <c r="G17" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H17" t="str">
         <v>1 Month (30 Days)</v>
@@ -1140,156 +1139,156 @@
         <v>Paid</v>
       </c>
       <c r="L17" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-02</v>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>2026-10-02T09:53:39.274Z</v>
+        <v>2026-10-04T18:00:34.025Z</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>sale_1790934132194</v>
+        <v>sale_1791136775857</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C18" t="str">
-        <v>3171626906</v>
+        <v>+92 311 7274561</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F18" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G18" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>n</v>
       </c>
       <c r="H18" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="J18">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K18" t="str">
         <v>Paid</v>
       </c>
       <c r="L18" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-02</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>2026-10-02T09:42:12.194Z</v>
+        <v>2026-10-04T17:59:35.857Z</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>sale_1790929984076</v>
+        <v>sale_1791136760132</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C19" t="str">
-        <v>3425091286</v>
+        <v>+92 308 5413116</v>
       </c>
       <c r="D19" t="str">
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F19" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G19" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H19" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K19" t="str">
         <v>Paid</v>
       </c>
       <c r="L19" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-02</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>2026-10-02T08:33:04.076Z</v>
+        <v>2026-10-04T17:59:20.132Z</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>sale_1790928896570</v>
+        <v>sale_1791134215437</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C20" t="str">
-        <v>+92 335 9333443</v>
+        <v>3157839993</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F20" t="str">
         <v>Shared</v>
       </c>
       <c r="G20" t="str">
-        <v>NA</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H20" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>12 Months (360 Days)</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J20">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="K20" t="str">
         <v>Paid</v>
       </c>
       <c r="L20" t="str">
-        <v>2026-10-31</v>
+        <v>2027-09-28</v>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>2026-10-02T08:14:56.570Z</v>
+        <v>2026-10-04T17:16:55.437Z</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>sale_1790927823366</v>
+        <v>sale_1791106255456</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C21" t="str">
-        <v>3424112890 - 178132</v>
+        <v>971558178928</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -1301,39 +1300,39 @@
         <v>Shared</v>
       </c>
       <c r="G21" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H21" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="K21" t="str">
         <v>Paid</v>
       </c>
       <c r="L21" t="str">
-        <v>2026-10-31</v>
+        <v>2027-01-01</v>
       </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>2026-10-02T07:57:03.366Z</v>
+        <v>2026-10-04T09:30:55.457Z</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>sale_1790927720999</v>
+        <v>sale_1791103826297</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C22" t="str">
-        <v>3355060692</v>
+        <v>3006831690</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -1345,39 +1344,39 @@
         <v>Shared</v>
       </c>
       <c r="G22" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H22" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>12 Months (360 Days)</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J22">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K22" t="str">
         <v>Paid</v>
       </c>
       <c r="L22" t="str">
-        <v>2026-10-31</v>
+        <v>2027-09-28</v>
       </c>
       <c r="M22" t="str">
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>2026-10-02T07:55:20.999Z</v>
+        <v>2026-10-04T08:50:26.297Z</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>sale_1790927520048</v>
+        <v>sale_1791102228323</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C23" t="str">
-        <v>3237432065</v>
+        <v>3047732450</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -1389,39 +1388,39 @@
         <v>Shared</v>
       </c>
       <c r="G23" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H23" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>12 Months (360 Days)</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J23">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="K23" t="str">
         <v>Paid</v>
       </c>
       <c r="L23" t="str">
-        <v>2026-11-30</v>
+        <v>2027-09-28</v>
       </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>2026-10-02T07:52:00.048Z</v>
+        <v>2026-10-04T08:23:48.324Z</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>sale_1790927399372</v>
+        <v>sale_1791099523357</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C24" t="str">
-        <v>3226763778</v>
+        <v>3081503007</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -1448,24 +1447,24 @@
         <v>Paid</v>
       </c>
       <c r="L24" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-02</v>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>2026-10-02T07:49:59.372Z</v>
+        <v>2026-10-04T07:38:43.357Z</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>sale_1790927194315</v>
+        <v>sale_1791098261508</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C25" t="str">
-        <v>3087182016</v>
+        <v>3007034330</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -1480,124 +1479,124 @@
         <v>abd150@kuromee.com</v>
       </c>
       <c r="H25" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K25" t="str">
         <v>Paid</v>
       </c>
       <c r="L25" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-02</v>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>2026-10-02T07:46:34.315Z</v>
+        <v>2026-10-04T07:17:41.508Z</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>sale_1790926790421</v>
+        <v>sale_1791064529531</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C26" t="str">
-        <v>3424112890 - 161547</v>
+        <v>+92 302 7283125</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F26" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G26" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H26" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I26">
         <v>1</v>
       </c>
       <c r="J26">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="K26" t="str">
         <v>Paid</v>
       </c>
       <c r="L26" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-01</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>2026-10-02T07:39:50.422Z</v>
+        <v>2026-10-03T21:55:29.531Z</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>sale_1790890878620</v>
+        <v>sale_1791064497321</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C27" t="str">
-        <v>3336677666</v>
+        <v>+92 300 6831690</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F27" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G27" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H27" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I27">
         <v>1</v>
       </c>
       <c r="J27">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K27" t="str">
         <v>Paid</v>
       </c>
       <c r="L27" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-01</v>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>2026-10-01T21:41:18.621Z</v>
+        <v>2026-10-03T21:54:57.321Z</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>sale_1790889330982</v>
+        <v>sale_1791037027100</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C28" t="str">
-        <v>+92 333 7180888</v>
+        <v>+92 309 3030483</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1612,80 +1611,80 @@
         <v>NA</v>
       </c>
       <c r="H28" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I28">
         <v>1</v>
       </c>
       <c r="J28">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="K28" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L28" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-01</v>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
-        <v>2026-10-01T21:15:30.982Z</v>
+        <v>2026-10-03T14:17:07.100Z</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>sale_1790889019841</v>
+        <v>sale_1791036095236</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C29" t="str">
-        <v>+92 324 3715759</v>
+        <v>3413317078</v>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F29" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G29" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H29" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="K29" t="str">
         <v>Paid</v>
       </c>
       <c r="L29" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-01</v>
       </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>2026-10-01T21:10:19.841Z</v>
+        <v>2026-10-03T14:01:35.236Z</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>sale_1790889206450</v>
+        <v>sale_1791035943610</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C30" t="str">
-        <v>447348556756 - 2 Devices</v>
+        <v>3158206979</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1697,7 +1696,7 @@
         <v>Shared</v>
       </c>
       <c r="G30" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H30" t="str">
         <v>1 Month (30 Days)</v>
@@ -1706,30 +1705,30 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K30" t="str">
         <v>Paid</v>
       </c>
       <c r="L30" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-01</v>
       </c>
       <c r="M30" t="str">
         <v/>
       </c>
       <c r="N30" t="str">
-        <v>2026-10-01T21:13:26.450Z</v>
+        <v>2026-10-03T13:59:03.610Z</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>sale_1790889149110</v>
+        <v>sale_1791035347968</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C31" t="str">
-        <v>3716928959</v>
+        <v>3091259797</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1741,227 +1740,227 @@
         <v>Shared</v>
       </c>
       <c r="G31" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H31" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K31" t="str">
         <v>Paid</v>
       </c>
       <c r="L31" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-01</v>
       </c>
       <c r="M31" t="str">
         <v/>
       </c>
       <c r="N31" t="str">
-        <v>2026-10-01T21:12:29.110Z</v>
+        <v>2026-10-03T13:49:07.968Z</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>sale_1790888980587</v>
+        <v>sale_1791035307158</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C32" t="str">
-        <v>+92 337 8569003</v>
+        <v>3241266815</v>
       </c>
       <c r="D32" t="str">
         <v/>
       </c>
       <c r="E32" t="str">
-        <v>CapCut</v>
+        <v>Surfshark</v>
       </c>
       <c r="F32" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G32" t="str">
-        <v>padmahastuti3@akunku.site|masuk123</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H32" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="K32" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L32" t="str">
-        <v>2026-10-30</v>
+        <v>2026-12-31</v>
       </c>
       <c r="M32" t="str">
         <v/>
       </c>
       <c r="N32" t="str">
-        <v>2026-10-01T21:09:40.587Z</v>
+        <v>2026-10-03T13:48:27.158Z</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>sale_1790888790593</v>
+        <v>sale_1791035284989</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C33" t="str">
-        <v>+92 318 8934627</v>
+        <v>+92 314 7659690</v>
       </c>
       <c r="D33" t="str">
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>Muse AI</v>
+        <v>CapCut</v>
       </c>
       <c r="F33" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G33" t="str">
-        <v>NA</v>
+        <v>jinawidamanik6@ccpro.id|masuk123</v>
       </c>
       <c r="H33" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="J33">
-        <v>1200</v>
+        <v>550</v>
       </c>
       <c r="K33" t="str">
         <v>Paid</v>
       </c>
       <c r="L33" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-01</v>
       </c>
       <c r="M33" t="str">
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>2026-10-01T21:06:30.593Z</v>
+        <v>2026-10-03T13:48:04.990Z</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>sale_1790888748366</v>
+        <v>sale_1791028064145</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C34" t="str">
-        <v>3121600439</v>
+        <v>+92 342 9665704</v>
       </c>
       <c r="D34" t="str">
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>Surfshark</v>
+        <v>CapCut</v>
       </c>
       <c r="F34" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G34" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H34" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="K34" t="str">
         <v>Paid</v>
       </c>
       <c r="L34" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-01</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>arthurwestbrook00q61@klingaii.com Capcut#1122</v>
       </c>
       <c r="N34" t="str">
-        <v>2026-10-01T21:05:48.366Z</v>
+        <v>2026-10-03T11:47:44.145Z</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>sale_1790888549930</v>
+        <v>sale_1791024242646</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C35" t="str">
-        <v>3148646368</v>
+        <v>+92 319 5466691</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F35" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G35" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H35" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
       <c r="J35">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="K35" t="str">
         <v>Paid</v>
       </c>
       <c r="L35" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-01</v>
       </c>
       <c r="M35" t="str">
         <v/>
       </c>
       <c r="N35" t="str">
-        <v>2026-10-01T21:02:29.930Z</v>
+        <v>2026-10-03T10:44:02.646Z</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>sale_1790888489800</v>
+        <v>sale_1790972901458</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C36" t="str">
-        <v>3043943233 - 2 devices</v>
+        <v>+92 333 3707266</v>
       </c>
       <c r="D36" t="str">
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F36" t="str">
         <v>Shared</v>
       </c>
       <c r="G36" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>nord9@kuromee.com</v>
       </c>
       <c r="H36" t="str">
         <v>3 Months (90 Days)</v>
@@ -1970,30 +1969,30 @@
         <v>3</v>
       </c>
       <c r="J36">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K36" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L36" t="str">
-        <v>2026-12-29</v>
+        <v>2026-12-31</v>
       </c>
       <c r="M36" t="str">
-        <v>Payment 5 Oct</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>2026-10-01T21:01:29.800Z</v>
+        <v>2026-10-02T20:28:21.458Z</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>sale_1790888426010</v>
+        <v>sale_1790971693632</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C37" t="str">
-        <v>3125698180</v>
+        <v>3038522190</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -2005,7 +2004,7 @@
         <v>Shared</v>
       </c>
       <c r="G37" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H37" t="str">
         <v>2 Months (60 Days)</v>
@@ -2017,27 +2016,27 @@
         <v>400</v>
       </c>
       <c r="K37" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L37" t="str">
-        <v>2026-11-29</v>
+        <v>2026-12-01</v>
       </c>
       <c r="M37" t="str">
-        <v>Payment Sunday 4 Oct</v>
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v>2026-10-01T21:00:26.011Z</v>
+        <v>2026-10-02T20:08:13.632Z</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>sale_1790888378017</v>
+        <v>sale_1790967903952</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C38" t="str">
-        <v>3208546164</v>
+        <v>3452401920</v>
       </c>
       <c r="D38" t="str">
         <v/>
@@ -2049,7 +2048,7 @@
         <v>Shared</v>
       </c>
       <c r="G38" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H38" t="str">
         <v>2 Months (60 Days)</v>
@@ -2064,24 +2063,24 @@
         <v>Paid</v>
       </c>
       <c r="L38" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-30</v>
       </c>
       <c r="M38" t="str">
         <v/>
       </c>
       <c r="N38" t="str">
-        <v>2026-10-01T20:59:38.017Z</v>
+        <v>2026-10-02T19:05:03.952Z</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>sale_1790888324786</v>
+        <v>sale_1790966446338</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C39" t="str">
-        <v>3424112890 - 232013</v>
+        <v>3162936885</v>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -2093,7 +2092,7 @@
         <v>Shared</v>
       </c>
       <c r="G39" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H39" t="str">
         <v>1 Month (30 Days)</v>
@@ -2108,36 +2107,36 @@
         <v>Paid</v>
       </c>
       <c r="L39" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M39" t="str">
         <v/>
       </c>
       <c r="N39" t="str">
-        <v>2026-10-01T20:58:44.786Z</v>
+        <v>2026-10-02T18:40:46.338Z</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>sale_1790871288858</v>
+        <v>sale_1790964840039</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C40" t="str">
-        <v>+92 336 6331621</v>
+        <v>3068258151</v>
       </c>
       <c r="D40" t="str">
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F40" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G40" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H40" t="str">
         <v>1 Month (30 Days)</v>
@@ -2146,74 +2145,74 @@
         <v>1</v>
       </c>
       <c r="J40">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="K40" t="str">
         <v>Paid</v>
       </c>
       <c r="L40" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M40" t="str">
         <v/>
       </c>
       <c r="N40" t="str">
-        <v>2026-10-01T16:14:48.858Z</v>
+        <v>2026-10-02T18:14:00.039Z</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>sale_1790871264002</v>
+        <v>sale_1790964482569</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C41" t="str">
-        <v>+98 901 603 6081</v>
+        <v>+92 334 7132394</v>
       </c>
       <c r="D41" t="str">
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F41" t="str">
         <v>Shared</v>
       </c>
       <c r="G41" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H41" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K41" t="str">
         <v>Paid</v>
       </c>
       <c r="L41" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M41" t="str">
         <v/>
       </c>
       <c r="N41" t="str">
-        <v>2026-10-01T16:14:24.002Z</v>
+        <v>2026-10-02T18:08:02.570Z</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>sale_1790868862060</v>
+        <v>sale_1790964455099</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C42" t="str">
-        <v>+92 341 9010662</v>
+        <v>+92 318 8934627</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -2222,7 +2221,7 @@
         <v>Muse AI</v>
       </c>
       <c r="F42" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G42" t="str">
         <v>NA</v>
@@ -2240,112 +2239,112 @@
         <v>Paid</v>
       </c>
       <c r="L42" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M42" t="str">
         <v/>
       </c>
       <c r="N42" t="str">
-        <v>2026-10-01T15:34:22.075Z</v>
+        <v>2026-10-02T18:07:35.099Z</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>sale_1790864924575</v>
+        <v>sale_1790955121286</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C43" t="str">
-        <v>+92 313 6762957</v>
+        <v>3424112890 - 810813</v>
       </c>
       <c r="D43" t="str">
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F43" t="str">
         <v>Shared</v>
       </c>
       <c r="G43" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H43" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K43" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L43" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M43" t="str">
         <v/>
       </c>
       <c r="N43" t="str">
-        <v>2026-10-01T14:28:44.576Z</v>
+        <v>2026-10-02T15:32:01.286Z</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>sale_1790864890520</v>
+        <v>sale_1790954315594</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C44" t="str">
-        <v>3166729551</v>
+        <v>+92 339 8895511</v>
       </c>
       <c r="D44" t="str">
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F44" t="str">
         <v>Shared</v>
       </c>
       <c r="G44" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H44" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="K44" t="str">
         <v>Paid</v>
       </c>
       <c r="L44" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M44" t="str">
         <v/>
       </c>
       <c r="N44" t="str">
-        <v>2026-10-01T14:28:10.520Z</v>
+        <v>2026-10-02T15:18:35.594Z</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>sale_1790862744178</v>
+        <v>sale_1790946519871</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C45" t="str">
-        <v>+92 317 0295905</v>
+        <v>+92 337 4695990</v>
       </c>
       <c r="D45" t="str">
         <v/>
@@ -2354,10 +2353,10 @@
         <v>Nord</v>
       </c>
       <c r="F45" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G45" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H45" t="str">
         <v>3 Months (90 Days)</v>
@@ -2366,30 +2365,30 @@
         <v>3</v>
       </c>
       <c r="J45">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="K45" t="str">
         <v>Paid</v>
       </c>
       <c r="L45" t="str">
-        <v>2026-12-29</v>
+        <v>2026-12-30</v>
       </c>
       <c r="M45" t="str">
         <v/>
       </c>
       <c r="N45" t="str">
-        <v>2026-10-01T13:52:24.178Z</v>
+        <v>2026-10-02T13:08:39.871Z</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>sale_1790861118501</v>
+        <v>sale_1790946456992</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C46" t="str">
-        <v>+92 344 4643148</v>
+        <v>+92 310 8747472</v>
       </c>
       <c r="D46" t="str">
         <v/>
@@ -2401,51 +2400,51 @@
         <v>Shared</v>
       </c>
       <c r="G46" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>nor8@kuromee.com</v>
       </c>
       <c r="H46" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>6 Months (180 Days)</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J46">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="K46" t="str">
         <v>Paid</v>
       </c>
       <c r="L46" t="str">
-        <v>2026-12-29</v>
+        <v>2027-03-30</v>
       </c>
       <c r="M46" t="str">
         <v/>
       </c>
       <c r="N46" t="str">
-        <v>2026-10-01T13:25:18.501Z</v>
+        <v>2026-10-02T13:07:36.993Z</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>sale_1790853314445</v>
+        <v>sale_1790941037212</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C47" t="str">
-        <v>+92 302 7283125</v>
+        <v>30474552522</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>CapCut</v>
+        <v>Surfshark</v>
       </c>
       <c r="F47" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G47" t="str">
-        <v>NA</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H47" t="str">
         <v>1 Month (30 Days)</v>
@@ -2454,74 +2453,74 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K47" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L47" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M47" t="str">
-        <v>vukdsas@apricity.tech  masuk123</v>
+        <v/>
       </c>
       <c r="N47" t="str">
-        <v>2026-10-01T11:15:14.445Z</v>
+        <v>2026-10-02T11:37:17.212Z</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>sale_1790852538710</v>
+        <v>sale_1790940354053</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C48" t="str">
-        <v>+92 325 1501138</v>
+        <v>+92 333 5598645</v>
       </c>
       <c r="D48" t="str">
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F48" t="str">
         <v>Private</v>
       </c>
       <c r="G48" t="str">
-        <v>N/A</v>
+        <v>alissaturner822@gmail.com</v>
       </c>
       <c r="H48" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="K48" t="str">
         <v>Paid</v>
       </c>
       <c r="L48" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-30</v>
       </c>
       <c r="M48" t="str">
         <v/>
       </c>
       <c r="N48" t="str">
-        <v>2026-10-01T11:02:18.710Z</v>
+        <v>2026-10-02T11:25:54.053Z</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>sale_1790852373016</v>
+        <v>sale_1790939431495</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C49" t="str">
-        <v>+92 301 7890066</v>
+        <v>+92 301 2553778</v>
       </c>
       <c r="D49" t="str">
         <v/>
@@ -2530,10 +2529,10 @@
         <v>Muse AI</v>
       </c>
       <c r="F49" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G49" t="str">
-        <v>N/A</v>
+        <v>NA</v>
       </c>
       <c r="H49" t="str">
         <v>1 Month (30 Days)</v>
@@ -2542,30 +2541,30 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="K49" t="str">
         <v>Paid</v>
       </c>
       <c r="L49" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M49" t="str">
         <v/>
       </c>
       <c r="N49" t="str">
-        <v>2026-10-01T10:59:33.016Z</v>
+        <v>2026-10-02T11:10:31.495Z</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>sale_1790850006978</v>
+        <v>sale_1790936221232</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C50" t="str">
-        <v>+92 342 4112890-534389</v>
+        <v>3362088885</v>
       </c>
       <c r="D50" t="str">
         <v/>
@@ -2577,7 +2576,7 @@
         <v>Shared</v>
       </c>
       <c r="G50" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H50" t="str">
         <v>1 Month (30 Days)</v>
@@ -2586,30 +2585,30 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K50" t="str">
         <v>Paid</v>
       </c>
       <c r="L50" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M50" t="str">
         <v/>
       </c>
       <c r="N50" t="str">
-        <v>2026-10-01T10:20:06.978Z</v>
+        <v>2026-10-02T10:17:01.232Z</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>sale_1790849948623</v>
+        <v>sale_1790934821042_1qpo</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C51" t="str">
-        <v>+92 349 6363398</v>
+        <v>3362088885</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -2621,7 +2620,7 @@
         <v>Shared</v>
       </c>
       <c r="G51" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H51" t="str">
         <v>1 Month (30 Days)</v>
@@ -2636,201 +2635,1697 @@
         <v>Paid</v>
       </c>
       <c r="L51" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M51" t="str">
         <v/>
       </c>
       <c r="N51" t="str">
-        <v>2026-10-01T10:19:08.625Z</v>
+        <v>2026-10-02T09:53:41.042Z</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>sale_1790844774858</v>
+        <v>sale_1790934819273</v>
       </c>
       <c r="B52" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C52" t="str">
-        <v>03035587360</v>
+        <v>3362088885</v>
       </c>
       <c r="D52" t="str">
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>Gemini Pro</v>
+        <v>Surfshark</v>
       </c>
       <c r="F52" t="str">
         <v>Shared</v>
       </c>
       <c r="G52" t="str">
-        <v>Not applicable</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H52" t="str">
-        <v>18 Months (540 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I52">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K52" t="str">
         <v>Paid</v>
       </c>
       <c r="L52" t="str">
-        <v>2028-03-23</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M52" t="str">
         <v/>
       </c>
       <c r="N52" t="str">
-        <v>2026-10-01T08:52:54.860Z</v>
+        <v>2026-10-02T09:53:39.274Z</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>sale_1790841917101</v>
+        <v>sale_1790934132194</v>
       </c>
       <c r="B53" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C53" t="str">
-        <v>+92 340 7317084</v>
+        <v>3171626906</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F53" t="str">
         <v>Shared</v>
       </c>
       <c r="G53" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H53" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K53" t="str">
         <v>Paid</v>
       </c>
       <c r="L53" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M53" t="str">
         <v/>
       </c>
       <c r="N53" t="str">
-        <v>2026-10-01T08:05:17.101Z</v>
+        <v>2026-10-02T09:42:12.194Z</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>sale_1790839031379</v>
+        <v>sale_1790929984076</v>
       </c>
       <c r="B54" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C54" t="str">
-        <v>+92 340 7317084</v>
+        <v>3425091286</v>
       </c>
       <c r="D54" t="str">
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F54" t="str">
         <v>Shared</v>
       </c>
       <c r="G54" t="str">
-        <v>Nord9@kuromee.com</v>
+        <v>abd150@kuromee.com</v>
       </c>
       <c r="H54" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J54">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K54" t="str">
         <v>Paid</v>
       </c>
       <c r="L54" t="str">
-        <v>2026-12-29</v>
+        <v>2026-10-31</v>
       </c>
       <c r="M54" t="str">
         <v/>
       </c>
       <c r="N54" t="str">
-        <v>2026-10-01T07:17:11.379Z</v>
+        <v>2026-10-02T08:33:04.076Z</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>sale_1790838846301</v>
+        <v>sale_1790928896570</v>
       </c>
       <c r="B55" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C55" t="str">
+        <v>+92 335 9333443</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G55" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H55" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L55" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v>2026-10-02T08:14:56.570Z</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>sale_1790927823366</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C56" t="str">
+        <v>3424112890 - 178132</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G56" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H56" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>200</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L56" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v>2026-10-02T07:57:03.366Z</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>sale_1790927720999</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C57" t="str">
+        <v>3355060692</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G57" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H57" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>250</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L57" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v>2026-10-02T07:55:20.999Z</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>sale_1790927520048</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C58" t="str">
+        <v>3237432065</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G58" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H58" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I58">
+        <v>2</v>
+      </c>
+      <c r="J58">
+        <v>400</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L58" t="str">
+        <v>2026-11-30</v>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v>2026-10-02T07:52:00.048Z</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>sale_1790927399372</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C59" t="str">
+        <v>3226763778</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G59" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H59" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>250</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L59" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v>2026-10-02T07:49:59.372Z</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>sale_1790927194315</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C60" t="str">
+        <v>3087182016</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G60" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H60" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>250</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L60" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v>2026-10-02T07:46:34.315Z</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>sale_1790926790421</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C61" t="str">
+        <v>3424112890 - 161547</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G61" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H61" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>200</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L61" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v>2026-10-02T07:39:50.422Z</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>sale_1790890878620</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C62" t="str">
+        <v>3336677666</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G62" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H62" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>250</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L62" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v>2026-10-01T21:41:18.621Z</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>sale_1790889330982</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C63" t="str">
+        <v>+92 333 7180888</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G63" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H63" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>1000</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L63" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v>2026-10-01T21:15:30.982Z</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>sale_1790889019841</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C64" t="str">
+        <v>+92 324 3715759</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G64" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H64" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>1000</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L64" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v>2026-10-01T21:10:19.841Z</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>sale_1790889206450</v>
+      </c>
+      <c r="B65" t="str">
         <v>2026-10-01</v>
       </c>
-      <c r="C55" t="str">
-        <v>3085352533</v>
-      </c>
-      <c r="D55" t="str">
-        <v/>
-      </c>
-      <c r="E55" t="str">
+      <c r="C65" t="str">
+        <v>447348556756 - 2 Devices</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
         <v>Surfshark</v>
       </c>
-      <c r="F55" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="G55" t="str">
+      <c r="F65" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G65" t="str">
         <v>abd149@kuromee.com</v>
       </c>
-      <c r="H55" t="str">
+      <c r="H65" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>500</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L65" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v>2026-10-01T21:13:26.450Z</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>sale_1790889149110</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C66" t="str">
+        <v>3716928959</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G66" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H66" t="str">
         <v>2 Months (60 Days)</v>
       </c>
-      <c r="I55">
+      <c r="I66">
         <v>2</v>
       </c>
-      <c r="J55">
-        <v>800</v>
-      </c>
-      <c r="K55" t="str">
+      <c r="J66">
+        <v>400</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L66" t="str">
+        <v>2026-11-29</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v>2026-10-01T21:12:29.110Z</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>sale_1790888980587</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C67" t="str">
+        <v>+92 337 8569003</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G67" t="str">
+        <v>padmahastuti3@akunku.site|masuk123</v>
+      </c>
+      <c r="H67" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>750</v>
+      </c>
+      <c r="K67" t="str">
         <v>Pending</v>
       </c>
-      <c r="L55" t="str">
+      <c r="L67" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v>2026-10-01T21:09:40.587Z</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sale_1790888790593</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C68" t="str">
+        <v>+92 318 8934627</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G68" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H68" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>1200</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L68" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v>2026-10-01T21:06:30.593Z</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>sale_1790888748366</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C69" t="str">
+        <v>3121600439</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G69" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H69" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <v>250</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L69" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v>2026-10-01T21:05:48.366Z</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>sale_1790888549930</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C70" t="str">
+        <v>3148646368</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G70" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H70" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>200</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L70" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v>2026-10-01T21:02:29.930Z</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>sale_1790888489800</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C71" t="str">
+        <v>3043943233 - 2 devices</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G71" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H71" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I71">
+        <v>3</v>
+      </c>
+      <c r="J71">
+        <v>1000</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L71" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Payment 5 Oct</v>
+      </c>
+      <c r="N71" t="str">
+        <v>2026-10-01T21:01:29.800Z</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>sale_1790888426010</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C72" t="str">
+        <v>3125698180</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G72" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H72" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+      <c r="J72">
+        <v>400</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L72" t="str">
         <v>2026-11-29</v>
       </c>
-      <c r="M55" t="str">
-        <v>2 Devices</v>
-      </c>
-      <c r="N55" t="str">
-        <v>2026-10-01T07:14:06.302Z</v>
+      <c r="M72" t="str">
+        <v>Payment Sunday 4 Oct</v>
+      </c>
+      <c r="N72" t="str">
+        <v>2026-10-01T21:00:26.011Z</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>sale_1790888378017</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C73" t="str">
+        <v>3208546164</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G73" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H73" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73">
+        <v>400</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L73" t="str">
+        <v>2026-11-29</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v>2026-10-01T20:59:38.017Z</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>sale_1790888324786</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C74" t="str">
+        <v>3424112890 - 232013</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G74" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H74" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>250</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L74" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v>2026-10-01T20:58:44.786Z</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>sale_1790871288858</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C75" t="str">
+        <v>+92 336 6331621</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G75" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H75" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <v>1200</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L75" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v>2026-10-01T16:14:48.858Z</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>sale_1790871264002</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C76" t="str">
+        <v>+98 901 603 6081</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G76" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H76" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I76">
+        <v>3</v>
+      </c>
+      <c r="J76">
+        <v>500</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L76" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v>2026-10-01T16:14:24.002Z</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>sale_1790868862060</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C77" t="str">
+        <v>+92 341 9010662</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G77" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H77" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1000</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L77" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v>2026-10-01T15:34:22.075Z</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sale_1790864924575</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C78" t="str">
+        <v>+92 313 6762957</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G78" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H78" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I78">
+        <v>3</v>
+      </c>
+      <c r="J78">
+        <v>500</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L78" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v>2026-10-01T14:28:44.576Z</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>sale_1790864890520</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C79" t="str">
+        <v>3166729551</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G79" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H79" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
+      </c>
+      <c r="J79">
+        <v>600</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L79" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v>2026-10-01T14:28:10.520Z</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sale_1790862744178</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C80" t="str">
+        <v>+92 317 0295905</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G80" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H80" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I80">
+        <v>3</v>
+      </c>
+      <c r="J80">
+        <v>600</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L80" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v>2026-10-01T13:52:24.178Z</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>sale_1790861118501</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C81" t="str">
+        <v>+92 344 4643148</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G81" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H81" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I81">
+        <v>3</v>
+      </c>
+      <c r="J81">
+        <v>500</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L81" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v>2026-10-01T13:25:18.501Z</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>sale_1790853314445</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C82" t="str">
+        <v>+92 302 7283125</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G82" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H82" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>750</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L82" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M82" t="str">
+        <v>vukdsas@apricity.tech  masuk123</v>
+      </c>
+      <c r="N82" t="str">
+        <v>2026-10-01T11:15:14.445Z</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>sale_1790852538710</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C83" t="str">
+        <v>+92 325 1501138</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H83" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>1000</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L83" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v>2026-10-01T11:02:18.710Z</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>sale_1790852373016</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C84" t="str">
+        <v>+92 301 7890066</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H84" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>1500</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L84" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v>2026-10-01T10:59:33.016Z</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>sale_1790850006978</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C85" t="str">
+        <v>+92 342 4112890-534389</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G85" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H85" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>200</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L85" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v>2026-10-01T10:20:06.978Z</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sale_1790849948623</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C86" t="str">
+        <v>+92 349 6363398</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G86" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H86" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <v>250</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L86" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v>2026-10-01T10:19:08.625Z</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>sale_1790844774858</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C87" t="str">
+        <v>03035587360</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G87" t="str">
+        <v>Not applicable</v>
+      </c>
+      <c r="H87" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I87">
+        <v>18</v>
+      </c>
+      <c r="J87">
+        <v>500</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L87" t="str">
+        <v>2028-03-23</v>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v>2026-10-01T08:52:54.860Z</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>sale_1790841917101</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C88" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G88" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H88" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I88">
+        <v>3</v>
+      </c>
+      <c r="J88">
+        <v>500</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L88" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v>2026-10-01T08:05:17.101Z</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>sale_1790839031379</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C89" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G89" t="str">
+        <v>Nord9@kuromee.com</v>
+      </c>
+      <c r="H89" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I89">
+        <v>3</v>
+      </c>
+      <c r="J89">
+        <v>500</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L89" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v>2026-10-01T07:17:11.379Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N89"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2854,444 +4349,187 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>exp_1790946533413</v>
+        <v>exp_1791205545999</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C2" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D2" t="str">
-        <v>Nord purchasing</v>
+        <v>baktionopradana64@akunku.site|masuk123 qaoyxh@apricity.tech:masuk123</v>
       </c>
       <c r="E2">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-10-02T13:08:53.414Z</v>
+        <v>2026-10-05T13:05:45.999Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>exp_1790940392222</v>
+        <v>exp_1791035398823</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C3" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D3" t="str">
-        <v>alissaturner822@gmail.com   Surfshark Private Payment</v>
+        <v>arthurwestbrook00q61@klingaii.com Capcut#1122</v>
       </c>
       <c r="E3">
-        <v>750</v>
+        <v>380</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-10-02T11:26:32.222Z</v>
+        <v>2026-10-03T13:49:58.823Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>exp_1790889252470</v>
+        <v>exp_1791035383336</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C4" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D4" t="str">
-        <v>Surfshark/Nord Paid</v>
+        <v>jinawidamanik6@ccpro.id|masuk123</v>
       </c>
       <c r="E4">
-        <v>1600</v>
+        <v>350</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-10-01T21:14:12.470Z</v>
+        <v>2026-10-03T13:49:43.337Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>exp_1790888895390</v>
+        <v>exp_1791018590950</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C5" t="str">
-        <v>Vendor Purchasing</v>
+        <v>Meta Ads</v>
       </c>
       <c r="D5" t="str">
-        <v>Capcut padmahastuti3@akunku.site|masuk123</v>
+        <v>Meta Ads</v>
       </c>
       <c r="E5">
-        <v>350</v>
+        <v>2000</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-10-01T21:08:15.390Z</v>
+        <v>2026-10-03T09:09:50.950Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>exp_1790865001001</v>
+        <v>exp_1790940392222</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C6" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D6" t="str">
-        <v>Capcut Account For Luxury online Store   vukdsas@apricity.tech:masuk123</v>
+        <v>alissaturner822@gmail.com   Surfshark Private Payment</v>
       </c>
       <c r="E6">
-        <v>350</v>
+        <v>750</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-10-01T14:30:01.001Z</v>
+        <v>2026-10-02T11:26:32.222Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>exp_1790810881227_1bq9</v>
+        <v>exp_1790889252470</v>
       </c>
       <c r="B7" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="C7" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Surfshark/Nord Paid</v>
+      </c>
+      <c r="E7">
+        <v>1600</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-10-01T21:14:12.470Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>exp_1790888895390</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Capcut padmahastuti3@akunku.site|masuk123</v>
+      </c>
+      <c r="E8">
+        <v>350</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-10-01T21:08:15.390Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>exp_1790865001001</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Capcut Account For Luxury online Store   vukdsas@apricity.tech:masuk123</v>
+      </c>
+      <c r="E9">
+        <v>350</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-10-01T14:30:01.001Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>exp_1790810881227_1bq9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C10" t="str">
         <v>Meta Ads</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D10" t="str">
         <v>Meta Ads Campaign</v>
       </c>
-      <c r="E7">
+      <c r="E10">
         <v>500</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F10" t="str">
         <v>2026-09-30T23:28:01.227Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Product Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Account Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Plan Duration (Months)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Plan Description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Price (Rs.)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="str">
-        <v>1 Month (30 Days)</v>
-      </c>
-      <c r="E2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2 Months (60 Days)</v>
-      </c>
-      <c r="E3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="str">
-        <v>3 Months (90 Days)</v>
-      </c>
-      <c r="E4">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5" t="str">
-        <v>6 Months (180 Days)</v>
-      </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6" t="str">
-        <v>12 Months (360 Days)</v>
-      </c>
-      <c r="E6">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Private</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2 Months (60 Days)</v>
-      </c>
-      <c r="E7">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Surfshark</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Private</v>
-      </c>
-      <c r="C8">
-        <v>12</v>
-      </c>
-      <c r="D8" t="str">
-        <v>1 Year (360 Days)</v>
-      </c>
-      <c r="E8">
-        <v>9499</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Nord</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3 Months (90 Days)</v>
-      </c>
-      <c r="E9">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Nord</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10" t="str">
-        <v>6 Months (180 Days)</v>
-      </c>
-      <c r="E10">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Nord</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C11">
-        <v>9</v>
-      </c>
-      <c r="D11" t="str">
-        <v>9 Months (270 Days)</v>
-      </c>
-      <c r="E11">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Nord</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C12">
-        <v>12</v>
-      </c>
-      <c r="D12" t="str">
-        <v>12 Months (360 Days)</v>
-      </c>
-      <c r="E12">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Nord</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Private</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13" t="str">
-        <v>3 Months (90 Days)</v>
-      </c>
-      <c r="E13">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Nord</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Private</v>
-      </c>
-      <c r="C14">
-        <v>12</v>
-      </c>
-      <c r="D14" t="str">
-        <v>12 Months (360 Days)</v>
-      </c>
-      <c r="E14">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Gemini Pro</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C15">
-        <v>18</v>
-      </c>
-      <c r="D15" t="str">
-        <v>18 Months (540 Days)</v>
-      </c>
-      <c r="E15">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>CapCut</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="str">
-        <v>1 Month (30 Days)</v>
-      </c>
-      <c r="E16">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>ChatGPT</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="str">
-        <v>1 Month (30 Days)</v>
-      </c>
-      <c r="E17">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Muse AI</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="str">
-        <v>1 Month (30 Days)</v>
-      </c>
-      <c r="E18">
-        <v>500</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Sales" sheetId="1" r:id="rId1"/>
     <sheet name="Expenses" sheetId="2" r:id="rId2"/>
+    <sheet name="Products" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -784,7 +785,7 @@
         <v>200</v>
       </c>
       <c r="K9" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L9" t="str">
         <v>2026-11-03</v>
@@ -4532,4 +4533,355 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E20"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Product Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Account Type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Plan Duration (Months)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Plan Description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Price (Rs.)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="E2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="E3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="E4">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5" t="str">
+        <v>6 Months (180 Days)</v>
+      </c>
+      <c r="E5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6" t="str">
+        <v>12 Months (360 Days)</v>
+      </c>
+      <c r="E6">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="E7">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8" t="str">
+        <v>1 Year (360 Days)</v>
+      </c>
+      <c r="E8">
+        <v>9499</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="E9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="str">
+        <v>6 Months (180 Days)</v>
+      </c>
+      <c r="E10">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="str">
+        <v>9 Months (270 Days)</v>
+      </c>
+      <c r="E11">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12" t="str">
+        <v>12 Months (360 Days)</v>
+      </c>
+      <c r="E12">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="E13">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="str">
+        <v>12 Months (360 Days)</v>
+      </c>
+      <c r="E14">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C15">
+        <v>18</v>
+      </c>
+      <c r="D15" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="E15">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="str">
+        <v>1 Month (25 Days)</v>
+      </c>
+      <c r="E16">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>ChatGPT</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="E17">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="E18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+      <c r="D19" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="E19">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="str">
+        <v>1 Month (25 Days)</v>
+      </c>
+      <c r="E20">
+        <v>550</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/data/AB_Tools_Business_Ledger.xlsx
+++ b/data/AB_Tools_Business_Ledger.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N173"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,189 +447,189 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sale_1791205614503</v>
+        <v>sale_1791744229083</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C2" t="str">
-        <v>+92 344 9282193</v>
+        <v>3340990786</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F2" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G2" t="str">
-        <v>NA</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H2" t="str">
-        <v>1 Month(s)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K2" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-11-03</v>
+        <v>2026-11-09</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>2026-10-05T13:06:54.503Z</v>
+        <v>2026-10-11T18:43:49.083Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sale_1791205520863</v>
+        <v>sale_1791742038836</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C3" t="str">
-        <v>+92 336 2088885</v>
+        <v>+92 342 8079825</v>
       </c>
       <c r="D3" t="str">
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>CapCut</v>
+        <v>Nord</v>
       </c>
       <c r="F3" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G3" t="str">
-        <v>baktionopradana64@akunku.site  masuk123  qaoyxh@apricity.tech  masuk123</v>
+        <v>nord10@kuromee.com</v>
       </c>
       <c r="H3" t="str">
-        <v>1 Month (25 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="K3" t="str">
         <v>Paid</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-11-03</v>
+        <v>2027-01-08</v>
       </c>
       <c r="M3" t="str">
-        <v>2 Capcut</v>
+        <v/>
       </c>
       <c r="N3" t="str">
-        <v>2026-10-05T13:05:20.863Z</v>
+        <v>2026-10-11T18:07:18.836Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>sale_1791205472496</v>
+        <v>sale_1791742019233</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C4" t="str">
-        <v>+92 300 2689698</v>
+        <v>447950950190</v>
       </c>
       <c r="D4" t="str">
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F4" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G4" t="str">
-        <v>NA</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H4" t="str">
-        <v>1 Month(s)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K4" t="str">
         <v>Paid</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-11-03</v>
+        <v>2026-11-09</v>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>2026-10-05T13:04:32.497Z</v>
+        <v>2026-10-11T18:06:59.233Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>sale_1791193680484</v>
+        <v>sale_1791741894442</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C5" t="str">
-        <v>+92 341 5984031</v>
+        <v>3017461956</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F5" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G5" t="str">
-        <v>NA</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H5" t="str">
-        <v>1 Month(s)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K5" t="str">
         <v>Paid</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-11-03</v>
+        <v>2026-12-09</v>
       </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>2026-10-05T09:48:00.484Z</v>
+        <v>2026-10-11T18:04:54.442Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>sale_1791191267464</v>
+        <v>sale_1791740381033</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C6" t="str">
-        <v>3317376555</v>
+        <v>3424112890 - 790651</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -641,7 +641,7 @@
         <v>Shared</v>
       </c>
       <c r="G6" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H6" t="str">
         <v>1 Month (30 Days)</v>
@@ -650,48 +650,48 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K6" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-11-03</v>
+        <v>2026-11-09</v>
       </c>
       <c r="M6" t="str">
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>2026-10-05T09:07:47.464Z</v>
+        <v>2026-10-11T17:39:41.033Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>sale_1791187749963</v>
+        <v>sale_1791663546040</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C7" t="str">
-        <v>+92 326 4813460</v>
+        <v>3483016446</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F7" t="str">
         <v>Shared</v>
       </c>
       <c r="G7" t="str">
-        <v>nord10@kuromee.com</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H7" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>400</v>
@@ -700,24 +700,24 @@
         <v>Paid</v>
       </c>
       <c r="L7" t="str">
-        <v>2027-01-02</v>
+        <v>2026-12-09</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>adnan Bhai</v>
       </c>
       <c r="N7" t="str">
-        <v>2026-10-05T08:09:09.963Z</v>
+        <v>2026-10-10T20:19:06.040Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>sale_1791187520074</v>
+        <v>sale_1791663131840</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C8" t="str">
-        <v>3005130980</v>
+        <v>3396122211</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -729,7 +729,7 @@
         <v>Shared</v>
       </c>
       <c r="G8" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H8" t="str">
         <v>1 Month (30 Days)</v>
@@ -744,24 +744,24 @@
         <v>Paid</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-11-03</v>
+        <v>2026-11-09</v>
       </c>
       <c r="M8" t="str">
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>2026-10-05T08:05:20.074Z</v>
+        <v>2026-10-10T20:12:11.840Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>sale_1791187470511</v>
+        <v>sale_1791659810737</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C9" t="str">
-        <v>3443570380</v>
+        <v>3256984754</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -773,127 +773,127 @@
         <v>Shared</v>
       </c>
       <c r="G9" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H9" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K9" t="str">
         <v>Paid</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-11-03</v>
+        <v>2026-12-09</v>
       </c>
       <c r="M9" t="str">
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>2026-10-05T08:04:30.511Z</v>
+        <v>2026-10-10T19:16:50.738Z</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>sale_1791187181909</v>
+        <v>sale_1791658951101</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C10" t="str">
-        <v>+92 319 5466691</v>
+        <v>3075478401</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Gemini Pro</v>
+        <v>Surfshark</v>
       </c>
       <c r="F10" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G10" t="str">
-        <v>NA</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H10" t="str">
-        <v>18 Months (540 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I10">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="K10" t="str">
         <v>Paid</v>
       </c>
       <c r="L10" t="str">
-        <v>2028-03-27</v>
+        <v>2026-12-09</v>
       </c>
       <c r="M10" t="str">
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>2026-10-05T07:59:41.909Z</v>
+        <v>2026-10-10T19:02:31.101Z</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>sale_1791184673171</v>
+        <v>sale_1791658343515</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C11" t="str">
-        <v>+92 303 5733146</v>
+        <v>3027248760</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F11" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G11" t="str">
-        <v>NA</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H11" t="str">
-        <v>1 Month(s)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K11" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-11-03</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M11" t="str">
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>2026-10-05T07:17:53.172Z</v>
+        <v>2026-10-10T18:52:23.515Z</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>sale_1791183478163</v>
+        <v>sale_1791642424426</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C12" t="str">
-        <v>3425091286</v>
+        <v>3271030906</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -905,7 +905,7 @@
         <v>Shared</v>
       </c>
       <c r="G12" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H12" t="str">
         <v>1 Month (30 Days)</v>
@@ -917,27 +917,27 @@
         <v>250</v>
       </c>
       <c r="K12" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L12" t="str">
-        <v>2026-11-03</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M12" t="str">
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>2026-10-05T06:57:58.163Z</v>
+        <v>2026-10-10T14:27:04.426Z</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>sale_1791183466887</v>
+        <v>sale_1791642013624</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C13" t="str">
-        <v>3199182226</v>
+        <v>3017788124</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -949,7 +949,7 @@
         <v>Shared</v>
       </c>
       <c r="G13" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H13" t="str">
         <v>1 Month (30 Days)</v>
@@ -958,162 +958,162 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K13" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-11-03</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M13" t="str">
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>2026-10-05T06:57:46.887Z</v>
+        <v>2026-10-10T14:20:13.624Z</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>sale_1791153252198</v>
+        <v>sale_1791636994682</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C14" t="str">
-        <v>+92 326 7000168</v>
+        <v>3017788124</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F14" t="str">
         <v>Shared</v>
       </c>
       <c r="G14" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H14" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K14" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L14" t="str">
-        <v>2027-01-02</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M14" t="str">
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>2026-10-04T22:34:12.198Z</v>
+        <v>2026-10-10T12:56:34.682Z</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>sale_1791138731891</v>
+        <v>sale_1791636978952</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C15" t="str">
-        <v>+92 309 6116899</v>
+        <v>3149148158</v>
       </c>
       <c r="D15" t="str">
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Gemini Pro</v>
+        <v>Surfshark</v>
       </c>
       <c r="F15" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G15" t="str">
-        <v>NA</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H15" t="str">
-        <v>18 Months (540 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I15">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K15" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L15" t="str">
-        <v>2028-03-26</v>
+        <v>2026-12-08</v>
       </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>2026-10-04T18:32:11.892Z</v>
+        <v>2026-10-10T12:56:18.953Z</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>sale_1791137994648</v>
+        <v>sale_1791635504754</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C16" t="str">
-        <v>+92 302 4827701</v>
+        <v>3129583528</v>
       </c>
       <c r="D16" t="str">
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Gemini Pro</v>
+        <v>Surfshark</v>
       </c>
       <c r="F16" t="str">
         <v>Shared</v>
       </c>
       <c r="G16" t="str">
-        <v>NA</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H16" t="str">
-        <v>18 Months (540 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I16">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="K16" t="str">
         <v>Paid</v>
       </c>
       <c r="L16" t="str">
-        <v>2028-03-26</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>2026-10-04T18:19:54.648Z</v>
+        <v>2026-10-10T12:31:44.754Z</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>sale_1791136834025</v>
+        <v>sale_1791634970672</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C17" t="str">
-        <v>3126811828</v>
+        <v>3424112890 - 758004</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -1125,7 +1125,7 @@
         <v>Shared</v>
       </c>
       <c r="G17" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H17" t="str">
         <v>1 Month (30 Days)</v>
@@ -1134,118 +1134,118 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K17" t="str">
         <v>Paid</v>
       </c>
       <c r="L17" t="str">
-        <v>2026-11-02</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>2026-10-04T18:00:34.025Z</v>
+        <v>2026-10-10T12:22:50.672Z</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>sale_1791136775857</v>
+        <v>sale_1791626849316</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C18" t="str">
-        <v>+92 311 7274561</v>
+        <v>+92 300 6831690</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Muse AI</v>
+        <v>Gemini Pro</v>
       </c>
       <c r="F18" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G18" t="str">
-        <v>n</v>
+        <v>NA</v>
       </c>
       <c r="H18" t="str">
-        <v>1 Month(s)</v>
+        <v>18 Months (540 Days)</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J18">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="K18" t="str">
         <v>Paid</v>
       </c>
       <c r="L18" t="str">
-        <v>2026-11-02</v>
+        <v>2028-04-01</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>2026-10-04T17:59:35.857Z</v>
+        <v>2026-10-10T10:07:29.316Z</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>sale_1791136760132</v>
+        <v>sale_1791626497812</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C19" t="str">
-        <v>+92 308 5413116</v>
+        <v>3463254376</v>
       </c>
       <c r="D19" t="str">
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F19" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G19" t="str">
-        <v>NA</v>
+        <v>abd154@kuromee.com</v>
       </c>
       <c r="H19" t="str">
-        <v>1 Month(s)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K19" t="str">
         <v>Paid</v>
       </c>
       <c r="L19" t="str">
-        <v>2026-11-02</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>2026-10-04T17:59:20.132Z</v>
+        <v>2026-10-10T10:01:37.812Z</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>sale_1791134215437</v>
+        <v>sale_1791624947583</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C20" t="str">
-        <v>3157839993</v>
+        <v>3014247859</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -1257,83 +1257,83 @@
         <v>Shared</v>
       </c>
       <c r="G20" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H20" t="str">
-        <v>12 Months (360 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I20">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J20">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="K20" t="str">
         <v>Paid</v>
       </c>
       <c r="L20" t="str">
-        <v>2027-09-28</v>
+        <v>2026-12-08</v>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>2026-10-04T17:16:55.437Z</v>
+        <v>2026-10-10T09:35:47.583Z</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>sale_1791106255456</v>
+        <v>sale_1791624461999</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C21" t="str">
-        <v>971558178928</v>
+        <v>+92 326 8836528</v>
       </c>
       <c r="D21" t="str">
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F21" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G21" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H21" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="K21" t="str">
         <v>Paid</v>
       </c>
       <c r="L21" t="str">
-        <v>2027-01-01</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>2026-10-04T09:30:55.457Z</v>
+        <v>2026-10-10T09:27:42.000Z</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>sale_1791103826297</v>
+        <v>sale_1791624366030</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C22" t="str">
-        <v>3006831690</v>
+        <v>3336055525</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -1345,127 +1345,127 @@
         <v>Shared</v>
       </c>
       <c r="G22" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H22" t="str">
-        <v>12 Months (360 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I22">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="K22" t="str">
         <v>Paid</v>
       </c>
       <c r="L22" t="str">
-        <v>2027-09-28</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M22" t="str">
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>2026-10-04T08:50:26.297Z</v>
+        <v>2026-10-10T09:26:06.030Z</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>sale_1791102228323</v>
+        <v>sale_1791623730616</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C23" t="str">
-        <v>3047732450</v>
+        <v>+92 326 4813460</v>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F23" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G23" t="str">
-        <v>abd151@kuromee.com</v>
+        <v>Reseller</v>
       </c>
       <c r="H23" t="str">
-        <v>12 Months (360 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I23">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="K23" t="str">
         <v>Paid</v>
       </c>
       <c r="L23" t="str">
-        <v>2027-09-28</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>3 Accounts</v>
       </c>
       <c r="N23" t="str">
-        <v>2026-10-04T08:23:48.324Z</v>
+        <v>2026-10-10T09:15:30.617Z</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>sale_1791099523357</v>
+        <v>sale_1791623395814</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C24" t="str">
-        <v>3081503007</v>
+        <v>+92 302 6591138</v>
       </c>
       <c r="D24" t="str">
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Surfshark</v>
+        <v>CapCut</v>
       </c>
       <c r="F24" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G24" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>yxddgm871@capcut.space|masuk123</v>
       </c>
       <c r="H24" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="J24">
-        <v>250</v>
+        <v>650</v>
       </c>
       <c r="K24" t="str">
         <v>Paid</v>
       </c>
       <c r="L24" t="str">
-        <v>2026-11-02</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>2026-10-04T07:38:43.357Z</v>
+        <v>2026-10-10T09:09:55.814Z</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>sale_1791098261508</v>
+        <v>sale_1791622701369</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C25" t="str">
-        <v>3007034330</v>
+        <v>3022813638</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -1477,39 +1477,39 @@
         <v>Shared</v>
       </c>
       <c r="G25" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H25" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K25" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L25" t="str">
-        <v>2026-12-02</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>2026-10-04T07:17:41.508Z</v>
+        <v>2026-10-10T08:58:21.369Z</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>sale_1791064529531</v>
+        <v>sale_1791620683247</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C26" t="str">
-        <v>+92 302 7283125</v>
+        <v>+92 347 3997831</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -1530,30 +1530,30 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="K26" t="str">
         <v>Paid</v>
       </c>
       <c r="L26" t="str">
-        <v>2026-11-01</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>2026-10-03T21:55:29.531Z</v>
+        <v>2026-10-10T08:24:43.248Z</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>sale_1791064497321</v>
+        <v>sale_1791620666007</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C27" t="str">
-        <v>+92 300 6831690</v>
+        <v>+92 370 8516473</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -1580,68 +1580,68 @@
         <v>Paid</v>
       </c>
       <c r="L27" t="str">
-        <v>2026-11-01</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>2026-10-03T21:54:57.321Z</v>
+        <v>2026-10-10T08:24:26.008Z</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>sale_1791037027100</v>
+        <v>sale_1791618008415</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C28" t="str">
-        <v>+92 309 3030483</v>
+        <v>3279076424</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F28" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G28" t="str">
-        <v>NA</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H28" t="str">
-        <v>1 Month(s)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I28">
         <v>1</v>
       </c>
       <c r="J28">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="K28" t="str">
         <v>Pending</v>
       </c>
       <c r="L28" t="str">
-        <v>2026-11-01</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
-        <v>2026-10-03T14:17:07.100Z</v>
+        <v>2026-10-10T07:40:08.415Z</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>sale_1791036095236</v>
+        <v>sale_1791617990989</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C29" t="str">
-        <v>3413317078</v>
+        <v>3087182016</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -1653,39 +1653,39 @@
         <v>Shared</v>
       </c>
       <c r="G29" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H29" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K29" t="str">
         <v>Paid</v>
       </c>
       <c r="L29" t="str">
-        <v>2026-12-01</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>2026-10-03T14:01:35.236Z</v>
+        <v>2026-10-10T07:39:50.989Z</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>sale_1791035943610</v>
+        <v>sale_1791617979938</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C30" t="str">
-        <v>3158206979</v>
+        <v>3309493280</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1697,39 +1697,39 @@
         <v>Shared</v>
       </c>
       <c r="G30" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H30" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K30" t="str">
         <v>Paid</v>
       </c>
       <c r="L30" t="str">
-        <v>2026-11-01</v>
+        <v>2026-12-08</v>
       </c>
       <c r="M30" t="str">
         <v/>
       </c>
       <c r="N30" t="str">
-        <v>2026-10-03T13:59:03.610Z</v>
+        <v>2026-10-10T07:39:39.938Z</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>sale_1791035347968</v>
+        <v>sale_1791577411191</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C31" t="str">
-        <v>3091259797</v>
+        <v>3096725851</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1741,39 +1741,39 @@
         <v>Shared</v>
       </c>
       <c r="G31" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H31" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="K31" t="str">
         <v>Paid</v>
       </c>
       <c r="L31" t="str">
-        <v>2026-11-01</v>
+        <v>2027-01-07</v>
       </c>
       <c r="M31" t="str">
         <v/>
       </c>
       <c r="N31" t="str">
-        <v>2026-10-03T13:49:07.968Z</v>
+        <v>2026-10-09T20:23:31.191Z</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>sale_1791035307158</v>
+        <v>sale_1791577395465</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C32" t="str">
-        <v>3241266815</v>
+        <v>3096725851</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -1785,89 +1785,89 @@
         <v>Shared</v>
       </c>
       <c r="G32" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H32" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K32" t="str">
         <v>Paid</v>
       </c>
       <c r="L32" t="str">
-        <v>2026-12-31</v>
+        <v>2026-11-08</v>
       </c>
       <c r="M32" t="str">
         <v/>
       </c>
       <c r="N32" t="str">
-        <v>2026-10-03T13:48:27.158Z</v>
+        <v>2026-10-09T20:23:15.465Z</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>sale_1791035284989</v>
+        <v>sale_1791570801474</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C33" t="str">
-        <v>+92 314 7659690</v>
+        <v>+92 342 9144332</v>
       </c>
       <c r="D33" t="str">
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>CapCut</v>
+        <v>Muse AI</v>
       </c>
       <c r="F33" t="str">
         <v>Private</v>
       </c>
       <c r="G33" t="str">
-        <v>jinawidamanik6@ccpro.id|masuk123</v>
+        <v>NA</v>
       </c>
       <c r="H33" t="str">
-        <v>1 Month (25 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="J33">
-        <v>550</v>
+        <v>970</v>
       </c>
       <c r="K33" t="str">
         <v>Paid</v>
       </c>
       <c r="L33" t="str">
-        <v>2026-11-01</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M33" t="str">
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>2026-10-03T13:48:04.990Z</v>
+        <v>2026-10-09T18:33:21.474Z</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>sale_1791028064145</v>
+        <v>sale_1791570762107</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C34" t="str">
-        <v>+92 342 9665704</v>
+        <v>+92 306 4379822</v>
       </c>
       <c r="D34" t="str">
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>CapCut</v>
+        <v>Muse AI</v>
       </c>
       <c r="F34" t="str">
         <v>Private</v>
@@ -1876,124 +1876,124 @@
         <v>NA</v>
       </c>
       <c r="H34" t="str">
-        <v>1 Month (25 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34">
-        <v>750</v>
+        <v>880</v>
       </c>
       <c r="K34" t="str">
         <v>Paid</v>
       </c>
       <c r="L34" t="str">
-        <v>2026-11-01</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M34" t="str">
-        <v>arthurwestbrook00q61@klingaii.com Capcut#1122</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>2026-10-03T11:47:44.145Z</v>
+        <v>2026-10-09T18:32:42.107Z</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>sale_1791024242646</v>
+        <v>sale_1791570719008</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C35" t="str">
-        <v>+92 319 5466691</v>
+        <v>3444643148</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F35" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G35" t="str">
-        <v>NA</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H35" t="str">
-        <v>1 Month(s)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="K35" t="str">
         <v>Paid</v>
       </c>
       <c r="L35" t="str">
-        <v>2026-11-01</v>
+        <v>2026-12-07</v>
       </c>
       <c r="M35" t="str">
         <v/>
       </c>
       <c r="N35" t="str">
-        <v>2026-10-03T10:44:02.646Z</v>
+        <v>2026-10-09T18:31:59.008Z</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>sale_1790972901458</v>
+        <v>sale_1791570544943</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C36" t="str">
-        <v>+92 333 3707266</v>
+        <v>3424112890 - 292472</v>
       </c>
       <c r="D36" t="str">
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F36" t="str">
         <v>Shared</v>
       </c>
       <c r="G36" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H36" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K36" t="str">
         <v>Paid</v>
       </c>
       <c r="L36" t="str">
-        <v>2026-12-31</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M36" t="str">
         <v/>
       </c>
       <c r="N36" t="str">
-        <v>2026-10-02T20:28:21.458Z</v>
+        <v>2026-10-09T18:29:04.943Z</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>sale_1790971693632</v>
+        <v>sale_1791570099419</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C37" t="str">
-        <v>3038522190</v>
+        <v>3335896409</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -2005,7 +2005,7 @@
         <v>Shared</v>
       </c>
       <c r="G37" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H37" t="str">
         <v>2 Months (60 Days)</v>
@@ -2020,24 +2020,24 @@
         <v>Paid</v>
       </c>
       <c r="L37" t="str">
-        <v>2026-12-01</v>
+        <v>2026-12-07</v>
       </c>
       <c r="M37" t="str">
         <v/>
       </c>
       <c r="N37" t="str">
-        <v>2026-10-02T20:08:13.632Z</v>
+        <v>2026-10-09T18:21:39.419Z</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>sale_1790967903952</v>
+        <v>sale_1791564656156</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C38" t="str">
-        <v>3452401920</v>
+        <v>3244585137</v>
       </c>
       <c r="D38" t="str">
         <v/>
@@ -2049,83 +2049,83 @@
         <v>Shared</v>
       </c>
       <c r="G38" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H38" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K38" t="str">
         <v>Paid</v>
       </c>
       <c r="L38" t="str">
-        <v>2026-11-30</v>
+        <v>2027-01-06</v>
       </c>
       <c r="M38" t="str">
         <v/>
       </c>
       <c r="N38" t="str">
-        <v>2026-10-02T19:05:03.952Z</v>
+        <v>2026-10-09T16:50:56.156Z</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>sale_1790966446338</v>
+        <v>sale_1791545963116</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C39" t="str">
-        <v>3162936885</v>
+        <v>+92 302 3337408</v>
       </c>
       <c r="D39" t="str">
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F39" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G39" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H39" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39">
-        <v>250</v>
+        <v>1200</v>
       </c>
       <c r="K39" t="str">
         <v>Paid</v>
       </c>
       <c r="L39" t="str">
-        <v>2026-10-31</v>
+        <v>2027-01-06</v>
       </c>
       <c r="M39" t="str">
         <v/>
       </c>
       <c r="N39" t="str">
-        <v>2026-10-02T18:40:46.338Z</v>
+        <v>2026-10-09T11:39:23.116Z</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>sale_1790964840039</v>
+        <v>sale_1791545941117</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C40" t="str">
-        <v>3068258151</v>
+        <v>3711657463</v>
       </c>
       <c r="D40" t="str">
         <v/>
@@ -2137,51 +2137,51 @@
         <v>Shared</v>
       </c>
       <c r="G40" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H40" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="K40" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L40" t="str">
-        <v>2026-10-31</v>
+        <v>2027-01-06</v>
       </c>
       <c r="M40" t="str">
         <v/>
       </c>
       <c r="N40" t="str">
-        <v>2026-10-02T18:14:00.039Z</v>
+        <v>2026-10-09T11:39:01.117Z</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>sale_1790964482569</v>
+        <v>sale_1791545916594</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C41" t="str">
-        <v>+92 334 7132394</v>
+        <v>3076774870</v>
       </c>
       <c r="D41" t="str">
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F41" t="str">
         <v>Shared</v>
       </c>
       <c r="G41" t="str">
-        <v>NA</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H41" t="str">
         <v>1 Month (30 Days)</v>
@@ -2190,30 +2190,30 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K41" t="str">
         <v>Paid</v>
       </c>
       <c r="L41" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M41" t="str">
         <v/>
       </c>
       <c r="N41" t="str">
-        <v>2026-10-02T18:08:02.570Z</v>
+        <v>2026-10-09T11:38:36.594Z</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>sale_1790964455099</v>
+        <v>sale_1791545300347</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C42" t="str">
-        <v>+92 318 8934627</v>
+        <v>+92 300 1517551</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -2222,42 +2222,42 @@
         <v>Muse AI</v>
       </c>
       <c r="F42" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G42" t="str">
         <v>NA</v>
       </c>
       <c r="H42" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I42">
         <v>1</v>
       </c>
       <c r="J42">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="K42" t="str">
         <v>Paid</v>
       </c>
       <c r="L42" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M42" t="str">
         <v/>
       </c>
       <c r="N42" t="str">
-        <v>2026-10-02T18:07:35.099Z</v>
+        <v>2026-10-09T11:28:20.348Z</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>sale_1790955121286</v>
+        <v>sale_1791545264089</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C43" t="str">
-        <v>3424112890 - 810813</v>
+        <v>3128630899</v>
       </c>
       <c r="D43" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>Shared</v>
       </c>
       <c r="G43" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H43" t="str">
         <v>1 Month (30 Days)</v>
@@ -2278,42 +2278,42 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K43" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L43" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M43" t="str">
         <v/>
       </c>
       <c r="N43" t="str">
-        <v>2026-10-02T15:32:01.286Z</v>
+        <v>2026-10-09T11:27:44.089Z</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>sale_1790954315594</v>
+        <v>sale_1791545248626</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C44" t="str">
-        <v>+92 339 8895511</v>
+        <v>3217905067</v>
       </c>
       <c r="D44" t="str">
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F44" t="str">
         <v>Shared</v>
       </c>
       <c r="G44" t="str">
-        <v>NA</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H44" t="str">
         <v>1 Month (30 Days)</v>
@@ -2322,36 +2322,36 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="K44" t="str">
         <v>Paid</v>
       </c>
       <c r="L44" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M44" t="str">
         <v/>
       </c>
       <c r="N44" t="str">
-        <v>2026-10-02T15:18:35.594Z</v>
+        <v>2026-10-09T11:27:28.626Z</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>sale_1790946519871</v>
+        <v>sale_1791541213627</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C45" t="str">
-        <v>+92 337 4695990</v>
+        <v>+92 304 1730663</v>
       </c>
       <c r="D45" t="str">
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F45" t="str">
         <v>Private</v>
@@ -2360,124 +2360,124 @@
         <v>NA</v>
       </c>
       <c r="H45" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J45">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="K45" t="str">
         <v>Paid</v>
       </c>
       <c r="L45" t="str">
-        <v>2026-12-30</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M45" t="str">
         <v/>
       </c>
       <c r="N45" t="str">
-        <v>2026-10-02T13:08:39.871Z</v>
+        <v>2026-10-09T10:20:13.627Z</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>sale_1790946456992</v>
+        <v>sale_1791541194817</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C46" t="str">
-        <v>+92 310 8747472</v>
+        <v>+92 322 4349838</v>
       </c>
       <c r="D46" t="str">
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F46" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G46" t="str">
-        <v>nor8@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H46" t="str">
-        <v>6 Months (180 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I46">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="K46" t="str">
         <v>Paid</v>
       </c>
       <c r="L46" t="str">
-        <v>2027-03-30</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M46" t="str">
         <v/>
       </c>
       <c r="N46" t="str">
-        <v>2026-10-02T13:07:36.993Z</v>
+        <v>2026-10-09T10:19:54.817Z</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>sale_1790941037212</v>
+        <v>sale_1791541126334</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C47" t="str">
-        <v>30474552522</v>
+        <v>+92 305 7502417</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F47" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G47" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H47" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I47">
         <v>1</v>
       </c>
       <c r="J47">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="K47" t="str">
         <v>Paid</v>
       </c>
       <c r="L47" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-07</v>
       </c>
       <c r="M47" t="str">
         <v/>
       </c>
       <c r="N47" t="str">
-        <v>2026-10-02T11:37:17.212Z</v>
+        <v>2026-10-09T10:18:46.334Z</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>sale_1790940354053</v>
+        <v>sale_1791541041693</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C48" t="str">
-        <v>+92 333 5598645</v>
+        <v>+92 303 0841683</v>
       </c>
       <c r="D48" t="str">
         <v/>
@@ -2486,54 +2486,54 @@
         <v>Surfshark</v>
       </c>
       <c r="F48" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G48" t="str">
-        <v>alissaturner822@gmail.com</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H48" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>12 Months (360 Days)</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J48">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="K48" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L48" t="str">
-        <v>2026-11-30</v>
+        <v>2027-10-03</v>
       </c>
       <c r="M48" t="str">
         <v/>
       </c>
       <c r="N48" t="str">
-        <v>2026-10-02T11:25:54.053Z</v>
+        <v>2026-10-09T10:17:21.694Z</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>sale_1790939431495</v>
+        <v>sale_1791485716460</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C49" t="str">
-        <v>+92 301 2553778</v>
+        <v>3319059292</v>
       </c>
       <c r="D49" t="str">
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F49" t="str">
         <v>Shared</v>
       </c>
       <c r="G49" t="str">
-        <v>NA</v>
+        <v>abd153@kuromee.com</v>
       </c>
       <c r="H49" t="str">
         <v>1 Month (30 Days)</v>
@@ -2542,74 +2542,74 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="K49" t="str">
         <v>Paid</v>
       </c>
       <c r="L49" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-06</v>
       </c>
       <c r="M49" t="str">
-        <v/>
+        <v>2 Devices</v>
       </c>
       <c r="N49" t="str">
-        <v>2026-10-02T11:10:31.495Z</v>
+        <v>2026-10-08T18:55:16.461Z</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>sale_1790936221232</v>
+        <v>sale_1791479154448</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C50" t="str">
-        <v>3362088885</v>
+        <v>+92 301 3619076</v>
       </c>
       <c r="D50" t="str">
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F50" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G50" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H50" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I50">
         <v>1</v>
       </c>
       <c r="J50">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K50" t="str">
         <v>Paid</v>
       </c>
       <c r="L50" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-06</v>
       </c>
       <c r="M50" t="str">
         <v/>
       </c>
       <c r="N50" t="str">
-        <v>2026-10-02T10:17:01.232Z</v>
+        <v>2026-10-08T17:05:54.448Z</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>sale_1790934821042_1qpo</v>
+        <v>sale_1791470236796</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C51" t="str">
-        <v>3362088885</v>
+        <v>3355917752</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -2621,127 +2621,127 @@
         <v>Shared</v>
       </c>
       <c r="G51" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H51" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K51" t="str">
         <v>Paid</v>
       </c>
       <c r="L51" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-06</v>
       </c>
       <c r="M51" t="str">
         <v/>
       </c>
       <c r="N51" t="str">
-        <v>2026-10-02T09:53:41.042Z</v>
+        <v>2026-10-08T14:37:16.796Z</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>sale_1790934819273</v>
+        <v>sale_1791467442865</v>
       </c>
       <c r="B52" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C52" t="str">
-        <v>3362088885</v>
+        <v>+92 307 1422915</v>
       </c>
       <c r="D52" t="str">
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F52" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G52" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H52" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I52">
         <v>1</v>
       </c>
       <c r="J52">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="K52" t="str">
         <v>Paid</v>
       </c>
       <c r="L52" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-06</v>
       </c>
       <c r="M52" t="str">
         <v/>
       </c>
       <c r="N52" t="str">
-        <v>2026-10-02T09:53:39.274Z</v>
+        <v>2026-10-08T13:50:42.865Z</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>sale_1790934132194</v>
+        <v>sale_1791467414950</v>
       </c>
       <c r="B53" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C53" t="str">
-        <v>3171626906</v>
+        <v>+92 314 8650015</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>Surfshark</v>
+        <v>CapCut</v>
       </c>
       <c r="F53" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G53" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>gantarhutasoit22@akunku.site masuk123</v>
       </c>
       <c r="H53" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="J53">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="K53" t="str">
         <v>Paid</v>
       </c>
       <c r="L53" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-06</v>
       </c>
       <c r="M53" t="str">
         <v/>
       </c>
       <c r="N53" t="str">
-        <v>2026-10-02T09:42:12.194Z</v>
+        <v>2026-10-08T13:50:14.951Z</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>sale_1790929984076</v>
+        <v>sale_1791448483852</v>
       </c>
       <c r="B54" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C54" t="str">
-        <v>3425091286</v>
+        <v>+92 330 9493280</v>
       </c>
       <c r="D54" t="str">
         <v/>
@@ -2753,127 +2753,127 @@
         <v>Shared</v>
       </c>
       <c r="G54" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H54" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J54">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="K54" t="str">
         <v>Paid</v>
       </c>
       <c r="L54" t="str">
-        <v>2026-10-31</v>
+        <v>2027-01-05</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>Paid but login on another acc</v>
       </c>
       <c r="N54" t="str">
-        <v>2026-10-02T08:33:04.076Z</v>
+        <v>2026-10-08T08:34:43.852Z</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>sale_1790928896570</v>
+        <v>sale_1791448297509</v>
       </c>
       <c r="B55" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C55" t="str">
-        <v>+92 335 9333443</v>
+        <v>+92 302 2525095</v>
       </c>
       <c r="D55" t="str">
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>Muse AI</v>
+        <v>Nord</v>
       </c>
       <c r="F55" t="str">
         <v>Shared</v>
       </c>
       <c r="G55" t="str">
-        <v>NA</v>
+        <v>nord10@kuromee.com</v>
       </c>
       <c r="H55" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>12 Months (360 Days)</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J55">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="K55" t="str">
         <v>Paid</v>
       </c>
       <c r="L55" t="str">
-        <v>2026-10-31</v>
+        <v>2027-10-02</v>
       </c>
       <c r="M55" t="str">
         <v/>
       </c>
       <c r="N55" t="str">
-        <v>2026-10-02T08:14:56.570Z</v>
+        <v>2026-10-08T08:31:37.509Z</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>sale_1790927823366</v>
+        <v>sale_1791448278400</v>
       </c>
       <c r="B56" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C56" t="str">
-        <v>3424112890 - 178132</v>
+        <v>+92 342 5902398</v>
       </c>
       <c r="D56" t="str">
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>Surfshark</v>
+        <v>Nord</v>
       </c>
       <c r="F56" t="str">
         <v>Shared</v>
       </c>
       <c r="G56" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>nord10@kuromee.com</v>
       </c>
       <c r="H56" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K56" t="str">
         <v>Paid</v>
       </c>
       <c r="L56" t="str">
-        <v>2026-10-31</v>
+        <v>2027-01-05</v>
       </c>
       <c r="M56" t="str">
         <v/>
       </c>
       <c r="N56" t="str">
-        <v>2026-10-02T07:57:03.366Z</v>
+        <v>2026-10-08T08:31:18.400Z</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>sale_1790927720999</v>
+        <v>sale_1791448157357</v>
       </c>
       <c r="B57" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-08</v>
       </c>
       <c r="C57" t="str">
-        <v>3355060692</v>
+        <v>3281210644</v>
       </c>
       <c r="D57" t="str">
         <v/>
@@ -2885,7 +2885,7 @@
         <v>Shared</v>
       </c>
       <c r="G57" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H57" t="str">
         <v>1 Month (30 Days)</v>
@@ -2897,27 +2897,27 @@
         <v>250</v>
       </c>
       <c r="K57" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L57" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-06</v>
       </c>
       <c r="M57" t="str">
         <v/>
       </c>
       <c r="N57" t="str">
-        <v>2026-10-02T07:55:20.999Z</v>
+        <v>2026-10-08T08:29:17.357Z</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>sale_1790927520048</v>
+        <v>sale_1791399390622</v>
       </c>
       <c r="B58" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C58" t="str">
-        <v>3237432065</v>
+        <v>447348556756</v>
       </c>
       <c r="D58" t="str">
         <v/>
@@ -2929,171 +2929,171 @@
         <v>Shared</v>
       </c>
       <c r="G58" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H58" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K58" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L58" t="str">
-        <v>2026-11-30</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M58" t="str">
         <v/>
       </c>
       <c r="N58" t="str">
-        <v>2026-10-02T07:52:00.048Z</v>
+        <v>2026-10-07T18:56:30.622Z</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>sale_1790927399372</v>
+        <v>sale_1791399362079</v>
       </c>
       <c r="B59" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C59" t="str">
-        <v>3226763778</v>
+        <v>+966 58 250 3728</v>
       </c>
       <c r="D59" t="str">
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F59" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G59" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H59" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I59">
         <v>1</v>
       </c>
       <c r="J59">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K59" t="str">
         <v>Paid</v>
       </c>
       <c r="L59" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M59" t="str">
         <v/>
       </c>
       <c r="N59" t="str">
-        <v>2026-10-02T07:49:59.372Z</v>
+        <v>2026-10-07T18:56:02.079Z</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>sale_1790927194315</v>
+        <v>sale_1791395560003</v>
       </c>
       <c r="B60" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C60" t="str">
-        <v>3087182016</v>
+        <v>+966 58 250 3728</v>
       </c>
       <c r="D60" t="str">
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F60" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G60" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H60" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I60">
         <v>1</v>
       </c>
       <c r="J60">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K60" t="str">
         <v>Paid</v>
       </c>
       <c r="L60" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M60" t="str">
         <v/>
       </c>
       <c r="N60" t="str">
-        <v>2026-10-02T07:46:34.315Z</v>
+        <v>2026-10-07T17:52:40.003Z</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>sale_1790926790421</v>
+        <v>sale_1791388345674</v>
       </c>
       <c r="B61" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C61" t="str">
-        <v>3424112890 - 161547</v>
+        <v>+92 313 6788703</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F61" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G61" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H61" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I61">
         <v>1</v>
       </c>
       <c r="J61">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="K61" t="str">
         <v>Paid</v>
       </c>
       <c r="L61" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M61" t="str">
         <v/>
       </c>
       <c r="N61" t="str">
-        <v>2026-10-02T07:39:50.422Z</v>
+        <v>2026-10-07T15:52:25.674Z</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>sale_1790890878620</v>
+        <v>sale_1791387966214</v>
       </c>
       <c r="B62" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C62" t="str">
-        <v>3336677666</v>
+        <v>3139432121</v>
       </c>
       <c r="D62" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>Shared</v>
       </c>
       <c r="G62" t="str">
-        <v>abd150@kuromee.com</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H62" t="str">
         <v>1 Month (30 Days)</v>
@@ -3120,80 +3120,80 @@
         <v>Paid</v>
       </c>
       <c r="L62" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M62" t="str">
         <v/>
       </c>
       <c r="N62" t="str">
-        <v>2026-10-01T21:41:18.621Z</v>
+        <v>2026-10-07T15:46:06.214Z</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>sale_1790889330982</v>
+        <v>sale_1791374395440</v>
       </c>
       <c r="B63" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C63" t="str">
-        <v>+92 333 7180888</v>
+        <v>3138781163</v>
       </c>
       <c r="D63" t="str">
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F63" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G63" t="str">
-        <v>NA</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H63" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="K63" t="str">
         <v>Paid</v>
       </c>
       <c r="L63" t="str">
-        <v>2026-10-31</v>
+        <v>2026-12-05</v>
       </c>
       <c r="M63" t="str">
         <v/>
       </c>
       <c r="N63" t="str">
-        <v>2026-10-01T21:15:30.982Z</v>
+        <v>2026-10-07T11:59:55.440Z</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>sale_1790889019841</v>
+        <v>sale_1791369180529</v>
       </c>
       <c r="B64" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C64" t="str">
-        <v>+92 324 3715759</v>
+        <v>3346604442</v>
       </c>
       <c r="D64" t="str">
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F64" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G64" t="str">
-        <v>NA</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H64" t="str">
         <v>1 Month (30 Days)</v>
@@ -3202,30 +3202,30 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K64" t="str">
         <v>Paid</v>
       </c>
       <c r="L64" t="str">
-        <v>2026-10-31</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M64" t="str">
         <v/>
       </c>
       <c r="N64" t="str">
-        <v>2026-10-01T21:10:19.841Z</v>
+        <v>2026-10-07T10:33:00.529Z</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>sale_1790889206450</v>
+        <v>sale_1791362365580</v>
       </c>
       <c r="B65" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C65" t="str">
-        <v>447348556756 - 2 Devices</v>
+        <v>3052407609</v>
       </c>
       <c r="D65" t="str">
         <v/>
@@ -3237,39 +3237,39 @@
         <v>Shared</v>
       </c>
       <c r="G65" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H65" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K65" t="str">
         <v>Paid</v>
       </c>
       <c r="L65" t="str">
-        <v>2026-10-30</v>
+        <v>2026-12-05</v>
       </c>
       <c r="M65" t="str">
         <v/>
       </c>
       <c r="N65" t="str">
-        <v>2026-10-01T21:13:26.450Z</v>
+        <v>2026-10-07T08:39:25.580Z</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>sale_1790889149110</v>
+        <v>sale_1791362055694</v>
       </c>
       <c r="B66" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C66" t="str">
-        <v>3716928959</v>
+        <v>3431070091</v>
       </c>
       <c r="D66" t="str">
         <v/>
@@ -3281,95 +3281,95 @@
         <v>Shared</v>
       </c>
       <c r="G66" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H66" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K66" t="str">
-        <v>Paid</v>
+        <v>Pending</v>
       </c>
       <c r="L66" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M66" t="str">
         <v/>
       </c>
       <c r="N66" t="str">
-        <v>2026-10-01T21:12:29.110Z</v>
+        <v>2026-10-07T08:34:15.694Z</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>sale_1790888980587</v>
+        <v>sale_1791361946593</v>
       </c>
       <c r="B67" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C67" t="str">
-        <v>+92 337 8569003</v>
+        <v>3078105459</v>
       </c>
       <c r="D67" t="str">
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>CapCut</v>
+        <v>Surfshark</v>
       </c>
       <c r="F67" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G67" t="str">
-        <v>padmahastuti3@akunku.site|masuk123</v>
+        <v>abd152@kuromee.com</v>
       </c>
       <c r="H67" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="K67" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L67" t="str">
-        <v>2026-10-30</v>
+        <v>2026-12-05</v>
       </c>
       <c r="M67" t="str">
         <v/>
       </c>
       <c r="N67" t="str">
-        <v>2026-10-01T21:09:40.587Z</v>
+        <v>2026-10-07T08:32:26.593Z</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sale_1790888790593</v>
+        <v>sale_1791318197323</v>
       </c>
       <c r="B68" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C68" t="str">
-        <v>+92 318 8934627</v>
+        <v>3489434943</v>
       </c>
       <c r="D68" t="str">
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F68" t="str">
         <v>Shared</v>
       </c>
       <c r="G68" t="str">
-        <v>NA</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H68" t="str">
         <v>1 Month (30 Days)</v>
@@ -3378,118 +3378,118 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="K68" t="str">
         <v>Paid</v>
       </c>
       <c r="L68" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M68" t="str">
         <v/>
       </c>
       <c r="N68" t="str">
-        <v>2026-10-01T21:06:30.593Z</v>
+        <v>2026-10-06T20:23:17.323Z</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>sale_1790888748366</v>
+        <v>sale_1791316058809</v>
       </c>
       <c r="B69" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C69" t="str">
-        <v>3121600439</v>
+        <v>+92 334 7166067</v>
       </c>
       <c r="D69" t="str">
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>Surfshark</v>
+        <v>CapCut</v>
       </c>
       <c r="F69" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G69" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>ivanusamah73@ccpro.id|masuk123</v>
       </c>
       <c r="H69" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I69">
         <v>1</v>
       </c>
       <c r="J69">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="K69" t="str">
         <v>Paid</v>
       </c>
       <c r="L69" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-05</v>
       </c>
       <c r="M69" t="str">
         <v/>
       </c>
       <c r="N69" t="str">
-        <v>2026-10-01T21:05:48.366Z</v>
+        <v>2026-10-06T19:47:38.810Z</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>sale_1790888549930</v>
+        <v>sale_1791311876244</v>
       </c>
       <c r="B70" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C70" t="str">
-        <v>3148646368</v>
+        <v>+92 301 4422789</v>
       </c>
       <c r="D70" t="str">
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>Surfshark</v>
+        <v>CapCut</v>
       </c>
       <c r="F70" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G70" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>adkwwr@apricity.tech:masuk123</v>
       </c>
       <c r="H70" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I70">
         <v>1</v>
       </c>
       <c r="J70">
-        <v>200</v>
+        <v>550</v>
       </c>
       <c r="K70" t="str">
         <v>Paid</v>
       </c>
       <c r="L70" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M70" t="str">
         <v/>
       </c>
       <c r="N70" t="str">
-        <v>2026-10-01T21:02:29.930Z</v>
+        <v>2026-10-06T18:37:56.244Z</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>sale_1790888489800</v>
+        <v>sale_1791311158245</v>
       </c>
       <c r="B71" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C71" t="str">
-        <v>3043943233 - 2 devices</v>
+        <v>3064860891</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -3501,39 +3501,39 @@
         <v>Shared</v>
       </c>
       <c r="G71" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H71" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="K71" t="str">
         <v>Pending</v>
       </c>
       <c r="L71" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M71" t="str">
-        <v>Payment 5 Oct</v>
+        <v/>
       </c>
       <c r="N71" t="str">
-        <v>2026-10-01T21:01:29.800Z</v>
+        <v>2026-10-06T18:25:58.245Z</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>sale_1790888426010</v>
+        <v>sale_1791310565383</v>
       </c>
       <c r="B72" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C72" t="str">
-        <v>3125698180</v>
+        <v>3092495714</v>
       </c>
       <c r="D72" t="str">
         <v/>
@@ -3545,7 +3545,7 @@
         <v>Shared</v>
       </c>
       <c r="G72" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H72" t="str">
         <v>2 Months (60 Days)</v>
@@ -3557,27 +3557,27 @@
         <v>400</v>
       </c>
       <c r="K72" t="str">
-        <v>Pending</v>
+        <v>Paid</v>
       </c>
       <c r="L72" t="str">
-        <v>2026-11-29</v>
+        <v>2026-12-04</v>
       </c>
       <c r="M72" t="str">
-        <v>Payment Sunday 4 Oct</v>
+        <v/>
       </c>
       <c r="N72" t="str">
-        <v>2026-10-01T21:00:26.011Z</v>
+        <v>2026-10-06T18:16:05.383Z</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>sale_1790888378017</v>
+        <v>sale_1791305700918</v>
       </c>
       <c r="B73" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C73" t="str">
-        <v>3208546164</v>
+        <v>3010160022</v>
       </c>
       <c r="D73" t="str">
         <v/>
@@ -3589,83 +3589,83 @@
         <v>Shared</v>
       </c>
       <c r="G73" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H73" t="str">
-        <v>2 Months (60 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K73" t="str">
         <v>Paid</v>
       </c>
       <c r="L73" t="str">
-        <v>2026-11-29</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M73" t="str">
         <v/>
       </c>
       <c r="N73" t="str">
-        <v>2026-10-01T20:59:38.017Z</v>
+        <v>2026-10-06T16:55:00.918Z</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>sale_1790888324786</v>
+        <v>sale_1791305595055</v>
       </c>
       <c r="B74" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C74" t="str">
-        <v>3424112890 - 232013</v>
+        <v>+971 56 568 9851</v>
       </c>
       <c r="D74" t="str">
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>Surfshark</v>
+        <v>CapCut</v>
       </c>
       <c r="F74" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G74" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>bqytxvs@apricity.tech  masuk123</v>
       </c>
       <c r="H74" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I74">
         <v>1</v>
       </c>
       <c r="J74">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="K74" t="str">
         <v>Paid</v>
       </c>
       <c r="L74" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M74" t="str">
         <v/>
       </c>
       <c r="N74" t="str">
-        <v>2026-10-01T20:58:44.786Z</v>
+        <v>2026-10-06T16:53:15.056Z</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>sale_1790871288858</v>
+        <v>sale_1791302651499</v>
       </c>
       <c r="B75" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C75" t="str">
-        <v>+92 336 6331621</v>
+        <v>+92 341 9123379</v>
       </c>
       <c r="D75" t="str">
         <v/>
@@ -3680,86 +3680,86 @@
         <v>NA</v>
       </c>
       <c r="H75" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I75">
         <v>1</v>
       </c>
       <c r="J75">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="K75" t="str">
         <v>Paid</v>
       </c>
       <c r="L75" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M75" t="str">
         <v/>
       </c>
       <c r="N75" t="str">
-        <v>2026-10-01T16:14:48.858Z</v>
+        <v>2026-10-06T16:04:11.499Z</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>sale_1790871264002</v>
+        <v>sale_1791301716905</v>
       </c>
       <c r="B76" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C76" t="str">
-        <v>+98 901 603 6081</v>
+        <v>3153158881</v>
       </c>
       <c r="D76" t="str">
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F76" t="str">
         <v>Shared</v>
       </c>
       <c r="G76" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H76" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>2 Months (60 Days)</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J76">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K76" t="str">
         <v>Paid</v>
       </c>
       <c r="L76" t="str">
-        <v>2026-12-29</v>
+        <v>2026-12-04</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>2 Devices</v>
       </c>
       <c r="N76" t="str">
-        <v>2026-10-01T16:14:24.002Z</v>
+        <v>2026-10-06T15:48:36.905Z</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>sale_1790868862060</v>
+        <v>sale_1791299832468</v>
       </c>
       <c r="B77" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C77" t="str">
-        <v>+92 341 9010662</v>
+        <v>+92 336 1042082</v>
       </c>
       <c r="D77" t="str">
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>Muse AI</v>
+        <v>CapCut</v>
       </c>
       <c r="F77" t="str">
         <v>Private</v>
@@ -3768,224 +3768,224 @@
         <v>NA</v>
       </c>
       <c r="H77" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I77">
         <v>1</v>
       </c>
       <c r="J77">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="K77" t="str">
         <v>Paid</v>
       </c>
       <c r="L77" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M77" t="str">
         <v/>
       </c>
       <c r="N77" t="str">
-        <v>2026-10-01T15:34:22.075Z</v>
+        <v>2026-10-06T15:17:12.468Z</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sale_1790864924575</v>
+        <v>sale_1791299789642</v>
       </c>
       <c r="B78" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C78" t="str">
-        <v>+92 313 6762957</v>
+        <v>3148664315</v>
       </c>
       <c r="D78" t="str">
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F78" t="str">
         <v>Shared</v>
       </c>
       <c r="G78" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H78" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K78" t="str">
         <v>Paid</v>
       </c>
       <c r="L78" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M78" t="str">
         <v/>
       </c>
       <c r="N78" t="str">
-        <v>2026-10-01T14:28:44.576Z</v>
+        <v>2026-10-06T15:16:29.642Z</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>sale_1790864890520</v>
+        <v>sale_1791298318914</v>
       </c>
       <c r="B79" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C79" t="str">
-        <v>3166729551</v>
+        <v>+92 303 6364066</v>
       </c>
       <c r="D79" t="str">
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F79" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G79" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H79" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="K79" t="str">
         <v>Paid</v>
       </c>
       <c r="L79" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M79" t="str">
         <v/>
       </c>
       <c r="N79" t="str">
-        <v>2026-10-01T14:28:10.520Z</v>
+        <v>2026-10-06T14:51:58.914Z</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sale_1790862744178</v>
+        <v>sale_1791296894614</v>
       </c>
       <c r="B80" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C80" t="str">
-        <v>+92 317 0295905</v>
+        <v>+92 304 6433408</v>
       </c>
       <c r="D80" t="str">
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F80" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G80" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H80" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="K80" t="str">
         <v>Paid</v>
       </c>
       <c r="L80" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M80" t="str">
         <v/>
       </c>
       <c r="N80" t="str">
-        <v>2026-10-01T13:52:24.178Z</v>
+        <v>2026-10-06T14:28:14.614Z</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>sale_1790861118501</v>
+        <v>sale_1791296870388</v>
       </c>
       <c r="B81" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C81" t="str">
-        <v>+92 344 4643148</v>
+        <v>3290853329</v>
       </c>
       <c r="D81" t="str">
         <v/>
       </c>
       <c r="E81" t="str">
-        <v>Nord</v>
+        <v>Surfshark</v>
       </c>
       <c r="F81" t="str">
         <v>Shared</v>
       </c>
       <c r="G81" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H81" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month (30 Days)</v>
       </c>
       <c r="I81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J81">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K81" t="str">
         <v>Paid</v>
       </c>
       <c r="L81" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M81" t="str">
         <v/>
       </c>
       <c r="N81" t="str">
-        <v>2026-10-01T13:25:18.501Z</v>
+        <v>2026-10-06T14:27:50.388Z</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>sale_1790853314445</v>
+        <v>sale_1791296265147</v>
       </c>
       <c r="B82" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C82" t="str">
-        <v>+92 302 7283125</v>
+        <v>3333496669</v>
       </c>
       <c r="D82" t="str">
         <v/>
       </c>
       <c r="E82" t="str">
-        <v>CapCut</v>
+        <v>Surfshark</v>
       </c>
       <c r="F82" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G82" t="str">
-        <v>NA</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H82" t="str">
         <v>1 Month (30 Days)</v>
@@ -3994,118 +3994,118 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="K82" t="str">
         <v>Paid</v>
       </c>
       <c r="L82" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-04</v>
       </c>
       <c r="M82" t="str">
-        <v>vukdsas@apricity.tech  masuk123</v>
+        <v/>
       </c>
       <c r="N82" t="str">
-        <v>2026-10-01T11:15:14.445Z</v>
+        <v>2026-10-06T14:17:45.147Z</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>sale_1790852538710</v>
+        <v>sale_1791284977002</v>
       </c>
       <c r="B83" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C83" t="str">
-        <v>+92 325 1501138</v>
+        <v>+92 333 1409589</v>
       </c>
       <c r="D83" t="str">
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>Muse AI</v>
+        <v>Gemini Pro</v>
       </c>
       <c r="F83" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G83" t="str">
-        <v>N/A</v>
+        <v>NA</v>
       </c>
       <c r="H83" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>18 Months (540 Days)</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J83">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="K83" t="str">
         <v>Paid</v>
       </c>
       <c r="L83" t="str">
-        <v>2026-10-30</v>
+        <v>2028-03-28</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>5x Accounts</v>
       </c>
       <c r="N83" t="str">
-        <v>2026-10-01T11:02:18.710Z</v>
+        <v>2026-10-06T11:09:37.002Z</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>sale_1790852373016</v>
+        <v>sale_1791284943104</v>
       </c>
       <c r="B84" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C84" t="str">
-        <v>+92 301 7890066</v>
+        <v>3404772060</v>
       </c>
       <c r="D84" t="str">
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>Muse AI</v>
+        <v>Surfshark</v>
       </c>
       <c r="F84" t="str">
-        <v>Private</v>
+        <v>Shared</v>
       </c>
       <c r="G84" t="str">
-        <v>N/A</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H84" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>3 Months (90 Days)</v>
       </c>
       <c r="I84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J84">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="K84" t="str">
         <v>Paid</v>
       </c>
       <c r="L84" t="str">
-        <v>2026-10-30</v>
+        <v>2027-01-03</v>
       </c>
       <c r="M84" t="str">
         <v/>
       </c>
       <c r="N84" t="str">
-        <v>2026-10-01T10:59:33.016Z</v>
+        <v>2026-10-06T11:09:03.104Z</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>sale_1790850006978</v>
+        <v>sale_1791211223866</v>
       </c>
       <c r="B85" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C85" t="str">
-        <v>+92 342 4112890-534389</v>
+        <v>3279615694</v>
       </c>
       <c r="D85" t="str">
         <v/>
@@ -4117,7 +4117,7 @@
         <v>Shared</v>
       </c>
       <c r="G85" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>abd151@kuromee.com</v>
       </c>
       <c r="H85" t="str">
         <v>1 Month (30 Days)</v>
@@ -4126,207 +4126,3903 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K85" t="str">
         <v>Paid</v>
       </c>
       <c r="L85" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M85" t="str">
         <v/>
       </c>
       <c r="N85" t="str">
-        <v>2026-10-01T10:20:06.978Z</v>
+        <v>2026-10-05T14:40:23.866Z</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sale_1790849948623</v>
+        <v>sale_1791205614503</v>
       </c>
       <c r="B86" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C86" t="str">
-        <v>+92 349 6363398</v>
+        <v>+92 344 9282193</v>
       </c>
       <c r="D86" t="str">
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>Surfshark</v>
+        <v>Muse AI</v>
       </c>
       <c r="F86" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G86" t="str">
-        <v>abd149@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H86" t="str">
-        <v>1 Month (30 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I86">
         <v>1</v>
       </c>
       <c r="J86">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="K86" t="str">
         <v>Paid</v>
       </c>
       <c r="L86" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M86" t="str">
         <v/>
       </c>
       <c r="N86" t="str">
-        <v>2026-10-01T10:19:08.625Z</v>
+        <v>2026-10-05T13:06:54.503Z</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>sale_1790844774858</v>
+        <v>sale_1791205520863</v>
       </c>
       <c r="B87" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C87" t="str">
-        <v>03035587360</v>
+        <v>+92 336 2088885</v>
       </c>
       <c r="D87" t="str">
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>Gemini Pro</v>
+        <v>CapCut</v>
       </c>
       <c r="F87" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G87" t="str">
-        <v>Not applicable</v>
+        <v>baktionopradana64@akunku.site  masuk123  qaoyxh@apricity.tech  masuk123</v>
       </c>
       <c r="H87" t="str">
-        <v>18 Months (540 Days)</v>
+        <v>1 Month (25 Days)</v>
       </c>
       <c r="I87">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J87">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="K87" t="str">
         <v>Paid</v>
       </c>
       <c r="L87" t="str">
-        <v>2028-03-23</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M87" t="str">
-        <v/>
+        <v>2 Capcut</v>
       </c>
       <c r="N87" t="str">
-        <v>2026-10-01T08:52:54.860Z</v>
+        <v>2026-10-05T13:05:20.863Z</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>sale_1790841917101</v>
+        <v>sale_1791205472496</v>
       </c>
       <c r="B88" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C88" t="str">
-        <v>+92 340 7317084</v>
+        <v>+92 300 2689698</v>
       </c>
       <c r="D88" t="str">
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>Nord</v>
+        <v>Muse AI</v>
       </c>
       <c r="F88" t="str">
-        <v>Shared</v>
+        <v>Private</v>
       </c>
       <c r="G88" t="str">
-        <v>nord9@kuromee.com</v>
+        <v>NA</v>
       </c>
       <c r="H88" t="str">
-        <v>3 Months (90 Days)</v>
+        <v>1 Month(s)</v>
       </c>
       <c r="I88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J88">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K88" t="str">
         <v>Paid</v>
       </c>
       <c r="L88" t="str">
-        <v>2026-12-29</v>
+        <v>2026-11-03</v>
       </c>
       <c r="M88" t="str">
         <v/>
       </c>
       <c r="N88" t="str">
-        <v>2026-10-01T08:05:17.101Z</v>
+        <v>2026-10-05T13:04:32.497Z</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
+        <v>sale_1791193680484</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C89" t="str">
+        <v>+92 341 5984031</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G89" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H89" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
+        <v>800</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L89" t="str">
+        <v>2026-11-03</v>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v>2026-10-05T09:48:00.484Z</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>sale_1791191267464</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C90" t="str">
+        <v>3317376555</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G90" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H90" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>250</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L90" t="str">
+        <v>2026-11-03</v>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v>2026-10-05T09:07:47.464Z</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>sale_1791187749963</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C91" t="str">
+        <v>+92 326 4813460</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G91" t="str">
+        <v>nord10@kuromee.com</v>
+      </c>
+      <c r="H91" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I91">
+        <v>3</v>
+      </c>
+      <c r="J91">
+        <v>400</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L91" t="str">
+        <v>2027-01-02</v>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v>2026-10-05T08:09:09.963Z</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>sale_1791187520074</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C92" t="str">
+        <v>3005130980</v>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G92" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H92" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>250</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L92" t="str">
+        <v>2026-11-03</v>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v>2026-10-05T08:05:20.074Z</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>sale_1791187470511</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C93" t="str">
+        <v>3443570380</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G93" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H93" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>200</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L93" t="str">
+        <v>2026-11-03</v>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v>2026-10-05T08:04:30.511Z</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>sale_1791187181909</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C94" t="str">
+        <v>+92 319 5466691</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G94" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H94" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I94">
+        <v>18</v>
+      </c>
+      <c r="J94">
+        <v>750</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L94" t="str">
+        <v>2028-03-27</v>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v>2026-10-05T07:59:41.909Z</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>sale_1791184673171</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C95" t="str">
+        <v>+92 303 5733146</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G95" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H95" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <v>1000</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L95" t="str">
+        <v>2026-11-03</v>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v>2026-10-05T07:17:53.172Z</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>sale_1791183478163</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C96" t="str">
+        <v>3425091286</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G96" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H96" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>250</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L96" t="str">
+        <v>2026-11-03</v>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v>2026-10-05T06:57:58.163Z</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sale_1791183466887</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C97" t="str">
+        <v>3199182226</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G97" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H97" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>250</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L97" t="str">
+        <v>2026-11-03</v>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v>2026-10-05T06:57:46.887Z</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>sale_1791153252198</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="C98" t="str">
+        <v>+92 326 7000168</v>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G98" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H98" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I98">
+        <v>3</v>
+      </c>
+      <c r="J98">
+        <v>500</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L98" t="str">
+        <v>2027-01-02</v>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v>2026-10-04T22:34:12.198Z</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sale_1791138731891</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C99" t="str">
+        <v>+92 309 6116899</v>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G99" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H99" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I99">
+        <v>18</v>
+      </c>
+      <c r="J99">
+        <v>500</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L99" t="str">
+        <v>2028-03-26</v>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v>2026-10-04T18:32:11.892Z</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>sale_1791137994648</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C100" t="str">
+        <v>+92 302 4827701</v>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G100" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H100" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I100">
+        <v>18</v>
+      </c>
+      <c r="J100">
+        <v>600</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L100" t="str">
+        <v>2028-03-26</v>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v>2026-10-04T18:19:54.648Z</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>sale_1791136834025</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C101" t="str">
+        <v>3126811828</v>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G101" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H101" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>250</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L101" t="str">
+        <v>2026-11-02</v>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v>2026-10-04T18:00:34.025Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>sale_1791136775857</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C102" t="str">
+        <v>+92 311 7274561</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G102" t="str">
+        <v>n</v>
+      </c>
+      <c r="H102" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>1000</v>
+      </c>
+      <c r="K102" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L102" t="str">
+        <v>2026-11-02</v>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v>2026-10-04T17:59:35.857Z</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>sale_1791136760132</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C103" t="str">
+        <v>+92 308 5413116</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G103" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H103" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <v>1000</v>
+      </c>
+      <c r="K103" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L103" t="str">
+        <v>2026-11-02</v>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v>2026-10-04T17:59:20.132Z</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>sale_1791134215437</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C104" t="str">
+        <v>3157839993</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G104" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H104" t="str">
+        <v>12 Months (360 Days)</v>
+      </c>
+      <c r="I104">
+        <v>12</v>
+      </c>
+      <c r="J104">
+        <v>1000</v>
+      </c>
+      <c r="K104" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L104" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v>2026-10-04T17:16:55.437Z</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>sale_1791106255456</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C105" t="str">
+        <v>971558178928</v>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G105" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H105" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I105">
+        <v>3</v>
+      </c>
+      <c r="J105">
+        <v>600</v>
+      </c>
+      <c r="K105" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L105" t="str">
+        <v>2027-01-01</v>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v>2026-10-04T09:30:55.457Z</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>sale_1791103826297</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C106" t="str">
+        <v>3006831690</v>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G106" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H106" t="str">
+        <v>12 Months (360 Days)</v>
+      </c>
+      <c r="I106">
+        <v>12</v>
+      </c>
+      <c r="J106">
+        <v>1500</v>
+      </c>
+      <c r="K106" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L106" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v>2026-10-04T08:50:26.297Z</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>sale_1791102228323</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C107" t="str">
+        <v>3047732450</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G107" t="str">
+        <v>abd151@kuromee.com</v>
+      </c>
+      <c r="H107" t="str">
+        <v>12 Months (360 Days)</v>
+      </c>
+      <c r="I107">
+        <v>12</v>
+      </c>
+      <c r="J107">
+        <v>1400</v>
+      </c>
+      <c r="K107" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L107" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v>2026-10-04T08:23:48.324Z</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>sale_1791099523357</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C108" t="str">
+        <v>3081503007</v>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G108" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H108" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>250</v>
+      </c>
+      <c r="K108" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L108" t="str">
+        <v>2026-11-02</v>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v>2026-10-04T07:38:43.357Z</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>sale_1791098261508</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C109" t="str">
+        <v>3007034330</v>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G109" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H109" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="J109">
+        <v>400</v>
+      </c>
+      <c r="K109" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L109" t="str">
+        <v>2026-12-02</v>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
+        <v>2026-10-04T07:17:41.508Z</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>sale_1791064529531</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C110" t="str">
+        <v>+92 302 7283125</v>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G110" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H110" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>1500</v>
+      </c>
+      <c r="K110" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L110" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
+        <v>2026-10-03T21:55:29.531Z</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>sale_1791064497321</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C111" t="str">
+        <v>+92 300 6831690</v>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G111" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H111" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>1000</v>
+      </c>
+      <c r="K111" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L111" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
+        <v>2026-10-03T21:54:57.321Z</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>sale_1791037027100</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C112" t="str">
+        <v>+92 309 3030483</v>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G112" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H112" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <v>800</v>
+      </c>
+      <c r="K112" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L112" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v>2026-10-03T14:17:07.100Z</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>sale_1791036095236</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C113" t="str">
+        <v>3413317078</v>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G113" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H113" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
+        <v>400</v>
+      </c>
+      <c r="K113" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L113" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v>2026-10-03T14:01:35.236Z</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>sale_1791035943610</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C114" t="str">
+        <v>3158206979</v>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G114" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H114" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>250</v>
+      </c>
+      <c r="K114" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L114" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v>2026-10-03T13:59:03.610Z</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>sale_1791035347968</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C115" t="str">
+        <v>3091259797</v>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G115" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H115" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>250</v>
+      </c>
+      <c r="K115" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L115" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v>2026-10-03T13:49:07.968Z</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>sale_1791035307158</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C116" t="str">
+        <v>3241266815</v>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G116" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H116" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I116">
+        <v>3</v>
+      </c>
+      <c r="J116">
+        <v>500</v>
+      </c>
+      <c r="K116" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L116" t="str">
+        <v>2026-12-31</v>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
+        <v>2026-10-03T13:48:27.158Z</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>sale_1791035284989</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C117" t="str">
+        <v>+92 314 7659690</v>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G117" t="str">
+        <v>jinawidamanik6@ccpro.id|masuk123</v>
+      </c>
+      <c r="H117" t="str">
+        <v>1 Month (25 Days)</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>550</v>
+      </c>
+      <c r="K117" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L117" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
+        <v>2026-10-03T13:48:04.990Z</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>sale_1791028064145</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C118" t="str">
+        <v>+92 342 9665704</v>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G118" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H118" t="str">
+        <v>1 Month (25 Days)</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>750</v>
+      </c>
+      <c r="K118" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L118" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="M118" t="str">
+        <v>arthurwestbrook00q61@klingaii.com Capcut#1122</v>
+      </c>
+      <c r="N118" t="str">
+        <v>2026-10-03T11:47:44.145Z</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>sale_1791024242646</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C119" t="str">
+        <v>+92 319 5466691</v>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G119" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H119" t="str">
+        <v>1 Month(s)</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>1500</v>
+      </c>
+      <c r="K119" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L119" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
+        <v>2026-10-03T10:44:02.646Z</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>sale_1790972901458</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C120" t="str">
+        <v>+92 333 3707266</v>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G120" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H120" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I120">
+        <v>3</v>
+      </c>
+      <c r="J120">
+        <v>500</v>
+      </c>
+      <c r="K120" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L120" t="str">
+        <v>2026-12-31</v>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
+        <v>2026-10-02T20:28:21.458Z</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>sale_1790971693632</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C121" t="str">
+        <v>3038522190</v>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G121" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H121" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="J121">
+        <v>400</v>
+      </c>
+      <c r="K121" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L121" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
+        <v>2026-10-02T20:08:13.632Z</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>sale_1790967903952</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C122" t="str">
+        <v>3452401920</v>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G122" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H122" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="J122">
+        <v>400</v>
+      </c>
+      <c r="K122" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L122" t="str">
+        <v>2026-11-30</v>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v>2026-10-02T19:05:03.952Z</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>sale_1790966446338</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C123" t="str">
+        <v>3162936885</v>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G123" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H123" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>250</v>
+      </c>
+      <c r="K123" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L123" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v>2026-10-02T18:40:46.338Z</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>sale_1790964840039</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C124" t="str">
+        <v>3068258151</v>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G124" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H124" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>250</v>
+      </c>
+      <c r="K124" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L124" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
+        <v>2026-10-02T18:14:00.039Z</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>sale_1790964482569</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C125" t="str">
+        <v>+92 334 7132394</v>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G125" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H125" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>1000</v>
+      </c>
+      <c r="K125" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L125" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
+        <v>2026-10-02T18:08:02.570Z</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>sale_1790964455099</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C126" t="str">
+        <v>+92 318 8934627</v>
+      </c>
+      <c r="D126" t="str">
+        <v/>
+      </c>
+      <c r="E126" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G126" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H126" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>1000</v>
+      </c>
+      <c r="K126" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L126" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
+        <v>2026-10-02T18:07:35.099Z</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>sale_1790955121286</v>
+      </c>
+      <c r="B127" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C127" t="str">
+        <v>3424112890 - 810813</v>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G127" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H127" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127">
+        <v>200</v>
+      </c>
+      <c r="K127" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L127" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
+        <v>2026-10-02T15:32:01.286Z</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sale_1790954315594</v>
+      </c>
+      <c r="B128" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C128" t="str">
+        <v>+92 339 8895511</v>
+      </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G128" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H128" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>1200</v>
+      </c>
+      <c r="K128" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L128" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v>2026-10-02T15:18:35.594Z</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>sale_1790946519871</v>
+      </c>
+      <c r="B129" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C129" t="str">
+        <v>+92 337 4695990</v>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G129" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H129" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I129">
+        <v>3</v>
+      </c>
+      <c r="J129">
+        <v>1300</v>
+      </c>
+      <c r="K129" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L129" t="str">
+        <v>2026-12-30</v>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v>2026-10-02T13:08:39.871Z</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sale_1790946456992</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C130" t="str">
+        <v>+92 310 8747472</v>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G130" t="str">
+        <v>nor8@kuromee.com</v>
+      </c>
+      <c r="H130" t="str">
+        <v>6 Months (180 Days)</v>
+      </c>
+      <c r="I130">
+        <v>6</v>
+      </c>
+      <c r="J130">
+        <v>800</v>
+      </c>
+      <c r="K130" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L130" t="str">
+        <v>2027-03-30</v>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v>2026-10-02T13:07:36.993Z</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>sale_1790941037212</v>
+      </c>
+      <c r="B131" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C131" t="str">
+        <v>30474552522</v>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G131" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H131" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>250</v>
+      </c>
+      <c r="K131" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L131" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
+        <v>2026-10-02T11:37:17.212Z</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>sale_1790940354053</v>
+      </c>
+      <c r="B132" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C132" t="str">
+        <v>+92 333 5598645</v>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G132" t="str">
+        <v>alissaturner822@gmail.com</v>
+      </c>
+      <c r="H132" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I132">
+        <v>2</v>
+      </c>
+      <c r="J132">
+        <v>1600</v>
+      </c>
+      <c r="K132" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L132" t="str">
+        <v>2026-11-30</v>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v>2026-10-02T11:25:54.053Z</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>sale_1790939431495</v>
+      </c>
+      <c r="B133" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C133" t="str">
+        <v>+92 301 2553778</v>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G133" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H133" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>1200</v>
+      </c>
+      <c r="K133" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L133" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v>2026-10-02T11:10:31.495Z</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>sale_1790936221232</v>
+      </c>
+      <c r="B134" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C134" t="str">
+        <v>3362088885</v>
+      </c>
+      <c r="D134" t="str">
+        <v/>
+      </c>
+      <c r="E134" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G134" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H134" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134">
+        <v>250</v>
+      </c>
+      <c r="K134" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L134" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v>2026-10-02T10:17:01.232Z</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>sale_1790934821042_1qpo</v>
+      </c>
+      <c r="B135" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C135" t="str">
+        <v>3362088885</v>
+      </c>
+      <c r="D135" t="str">
+        <v/>
+      </c>
+      <c r="E135" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G135" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H135" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135">
+        <v>250</v>
+      </c>
+      <c r="K135" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L135" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v>2026-10-02T09:53:41.042Z</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>sale_1790934819273</v>
+      </c>
+      <c r="B136" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C136" t="str">
+        <v>3362088885</v>
+      </c>
+      <c r="D136" t="str">
+        <v/>
+      </c>
+      <c r="E136" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G136" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H136" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>250</v>
+      </c>
+      <c r="K136" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L136" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v>2026-10-02T09:53:39.274Z</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>sale_1790934132194</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C137" t="str">
+        <v>3171626906</v>
+      </c>
+      <c r="D137" t="str">
+        <v/>
+      </c>
+      <c r="E137" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G137" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H137" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>250</v>
+      </c>
+      <c r="K137" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L137" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v>2026-10-02T09:42:12.194Z</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>sale_1790929984076</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C138" t="str">
+        <v>3425091286</v>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+      <c r="E138" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G138" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H138" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>250</v>
+      </c>
+      <c r="K138" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L138" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v>2026-10-02T08:33:04.076Z</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>sale_1790928896570</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C139" t="str">
+        <v>+92 335 9333443</v>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+      <c r="E139" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G139" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H139" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>1500</v>
+      </c>
+      <c r="K139" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L139" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v>2026-10-02T08:14:56.570Z</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>sale_1790927823366</v>
+      </c>
+      <c r="B140" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C140" t="str">
+        <v>3424112890 - 178132</v>
+      </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
+      <c r="E140" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G140" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H140" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
+        <v>200</v>
+      </c>
+      <c r="K140" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L140" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v>2026-10-02T07:57:03.366Z</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>sale_1790927720999</v>
+      </c>
+      <c r="B141" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C141" t="str">
+        <v>3355060692</v>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+      <c r="E141" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F141" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G141" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H141" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+      <c r="J141">
+        <v>250</v>
+      </c>
+      <c r="K141" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L141" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v>2026-10-02T07:55:20.999Z</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>sale_1790927520048</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C142" t="str">
+        <v>3237432065</v>
+      </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
+      <c r="E142" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G142" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H142" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I142">
+        <v>2</v>
+      </c>
+      <c r="J142">
+        <v>400</v>
+      </c>
+      <c r="K142" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L142" t="str">
+        <v>2026-11-30</v>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v>2026-10-02T07:52:00.048Z</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>sale_1790927399372</v>
+      </c>
+      <c r="B143" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C143" t="str">
+        <v>3226763778</v>
+      </c>
+      <c r="D143" t="str">
+        <v/>
+      </c>
+      <c r="E143" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G143" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H143" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143">
+        <v>250</v>
+      </c>
+      <c r="K143" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L143" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v>2026-10-02T07:49:59.372Z</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>sale_1790927194315</v>
+      </c>
+      <c r="B144" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C144" t="str">
+        <v>3087182016</v>
+      </c>
+      <c r="D144" t="str">
+        <v/>
+      </c>
+      <c r="E144" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F144" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G144" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H144" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I144">
+        <v>1</v>
+      </c>
+      <c r="J144">
+        <v>250</v>
+      </c>
+      <c r="K144" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L144" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v>2026-10-02T07:46:34.315Z</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>sale_1790926790421</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C145" t="str">
+        <v>3424112890 - 161547</v>
+      </c>
+      <c r="D145" t="str">
+        <v/>
+      </c>
+      <c r="E145" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F145" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G145" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H145" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+      <c r="J145">
+        <v>200</v>
+      </c>
+      <c r="K145" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L145" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v>2026-10-02T07:39:50.422Z</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>sale_1790890878620</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C146" t="str">
+        <v>3336677666</v>
+      </c>
+      <c r="D146" t="str">
+        <v/>
+      </c>
+      <c r="E146" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G146" t="str">
+        <v>abd150@kuromee.com</v>
+      </c>
+      <c r="H146" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146">
+        <v>250</v>
+      </c>
+      <c r="K146" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L146" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v>2026-10-01T21:41:18.621Z</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>sale_1790889330982</v>
+      </c>
+      <c r="B147" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C147" t="str">
+        <v>+92 333 7180888</v>
+      </c>
+      <c r="D147" t="str">
+        <v/>
+      </c>
+      <c r="E147" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F147" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G147" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H147" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>1000</v>
+      </c>
+      <c r="K147" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L147" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v>2026-10-01T21:15:30.982Z</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>sale_1790889019841</v>
+      </c>
+      <c r="B148" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C148" t="str">
+        <v>+92 324 3715759</v>
+      </c>
+      <c r="D148" t="str">
+        <v/>
+      </c>
+      <c r="E148" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F148" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G148" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H148" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148">
+        <v>1000</v>
+      </c>
+      <c r="K148" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L148" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v>2026-10-01T21:10:19.841Z</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>sale_1790889206450</v>
+      </c>
+      <c r="B149" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C149" t="str">
+        <v>447348556756 - 2 Devices</v>
+      </c>
+      <c r="D149" t="str">
+        <v/>
+      </c>
+      <c r="E149" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G149" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H149" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>500</v>
+      </c>
+      <c r="K149" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L149" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v>2026-10-01T21:13:26.450Z</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>sale_1790889149110</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C150" t="str">
+        <v>3716928959</v>
+      </c>
+      <c r="D150" t="str">
+        <v/>
+      </c>
+      <c r="E150" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F150" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G150" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H150" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+      <c r="J150">
+        <v>400</v>
+      </c>
+      <c r="K150" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L150" t="str">
+        <v>2026-11-29</v>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v>2026-10-01T21:12:29.110Z</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>sale_1790888980587</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C151" t="str">
+        <v>+92 337 8569003</v>
+      </c>
+      <c r="D151" t="str">
+        <v/>
+      </c>
+      <c r="E151" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G151" t="str">
+        <v>padmahastuti3@akunku.site|masuk123</v>
+      </c>
+      <c r="H151" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="J151">
+        <v>750</v>
+      </c>
+      <c r="K151" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L151" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v>2026-10-01T21:09:40.587Z</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>sale_1790888790593</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C152" t="str">
+        <v>+92 318 8934627</v>
+      </c>
+      <c r="D152" t="str">
+        <v/>
+      </c>
+      <c r="E152" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F152" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G152" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H152" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152">
+        <v>1200</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L152" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v>2026-10-01T21:06:30.593Z</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>sale_1790888748366</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C153" t="str">
+        <v>3121600439</v>
+      </c>
+      <c r="D153" t="str">
+        <v/>
+      </c>
+      <c r="E153" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G153" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H153" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
+      <c r="J153">
+        <v>250</v>
+      </c>
+      <c r="K153" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L153" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v>2026-10-01T21:05:48.366Z</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>sale_1790888549930</v>
+      </c>
+      <c r="B154" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C154" t="str">
+        <v>3148646368</v>
+      </c>
+      <c r="D154" t="str">
+        <v/>
+      </c>
+      <c r="E154" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G154" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H154" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154">
+        <v>200</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L154" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v>2026-10-01T21:02:29.930Z</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>sale_1790888489800</v>
+      </c>
+      <c r="B155" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C155" t="str">
+        <v>3043943233 - 2 devices</v>
+      </c>
+      <c r="D155" t="str">
+        <v/>
+      </c>
+      <c r="E155" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G155" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H155" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I155">
+        <v>3</v>
+      </c>
+      <c r="J155">
+        <v>1000</v>
+      </c>
+      <c r="K155" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L155" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M155" t="str">
+        <v>Payment 5 Oct</v>
+      </c>
+      <c r="N155" t="str">
+        <v>2026-10-01T21:01:29.800Z</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>sale_1790888426010</v>
+      </c>
+      <c r="B156" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C156" t="str">
+        <v>3125698180</v>
+      </c>
+      <c r="D156" t="str">
+        <v/>
+      </c>
+      <c r="E156" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G156" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H156" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I156">
+        <v>2</v>
+      </c>
+      <c r="J156">
+        <v>400</v>
+      </c>
+      <c r="K156" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L156" t="str">
+        <v>2026-11-29</v>
+      </c>
+      <c r="M156" t="str">
+        <v>Payment Sunday 4 Oct</v>
+      </c>
+      <c r="N156" t="str">
+        <v>2026-10-01T21:00:26.011Z</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>sale_1790888378017</v>
+      </c>
+      <c r="B157" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C157" t="str">
+        <v>3208546164</v>
+      </c>
+      <c r="D157" t="str">
+        <v/>
+      </c>
+      <c r="E157" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G157" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H157" t="str">
+        <v>2 Months (60 Days)</v>
+      </c>
+      <c r="I157">
+        <v>2</v>
+      </c>
+      <c r="J157">
+        <v>400</v>
+      </c>
+      <c r="K157" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L157" t="str">
+        <v>2026-11-29</v>
+      </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v>2026-10-01T20:59:38.017Z</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>sale_1790888324786</v>
+      </c>
+      <c r="B158" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C158" t="str">
+        <v>3424112890 - 232013</v>
+      </c>
+      <c r="D158" t="str">
+        <v/>
+      </c>
+      <c r="E158" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G158" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H158" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158">
+        <v>250</v>
+      </c>
+      <c r="K158" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L158" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
+      <c r="N158" t="str">
+        <v>2026-10-01T20:58:44.786Z</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>sale_1790871288858</v>
+      </c>
+      <c r="B159" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C159" t="str">
+        <v>+92 336 6331621</v>
+      </c>
+      <c r="D159" t="str">
+        <v/>
+      </c>
+      <c r="E159" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G159" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H159" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>1200</v>
+      </c>
+      <c r="K159" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L159" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159" t="str">
+        <v>2026-10-01T16:14:48.858Z</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>sale_1790871264002</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C160" t="str">
+        <v>+98 901 603 6081</v>
+      </c>
+      <c r="D160" t="str">
+        <v/>
+      </c>
+      <c r="E160" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G160" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H160" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I160">
+        <v>3</v>
+      </c>
+      <c r="J160">
+        <v>500</v>
+      </c>
+      <c r="K160" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L160" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160" t="str">
+        <v>2026-10-01T16:14:24.002Z</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>sale_1790868862060</v>
+      </c>
+      <c r="B161" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C161" t="str">
+        <v>+92 341 9010662</v>
+      </c>
+      <c r="D161" t="str">
+        <v/>
+      </c>
+      <c r="E161" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G161" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H161" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+      <c r="J161">
+        <v>1000</v>
+      </c>
+      <c r="K161" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L161" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
+      <c r="N161" t="str">
+        <v>2026-10-01T15:34:22.075Z</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>sale_1790864924575</v>
+      </c>
+      <c r="B162" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C162" t="str">
+        <v>+92 313 6762957</v>
+      </c>
+      <c r="D162" t="str">
+        <v/>
+      </c>
+      <c r="E162" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F162" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G162" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H162" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I162">
+        <v>3</v>
+      </c>
+      <c r="J162">
+        <v>500</v>
+      </c>
+      <c r="K162" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L162" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162" t="str">
+        <v>2026-10-01T14:28:44.576Z</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>sale_1790864890520</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C163" t="str">
+        <v>3166729551</v>
+      </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
+      <c r="E163" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G163" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H163" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I163">
+        <v>3</v>
+      </c>
+      <c r="J163">
+        <v>600</v>
+      </c>
+      <c r="K163" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L163" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v>2026-10-01T14:28:10.520Z</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>sale_1790862744178</v>
+      </c>
+      <c r="B164" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C164" t="str">
+        <v>+92 317 0295905</v>
+      </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
+      <c r="E164" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F164" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G164" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H164" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I164">
+        <v>3</v>
+      </c>
+      <c r="J164">
+        <v>600</v>
+      </c>
+      <c r="K164" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L164" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" t="str">
+        <v>2026-10-01T13:52:24.178Z</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>sale_1790861118501</v>
+      </c>
+      <c r="B165" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C165" t="str">
+        <v>+92 344 4643148</v>
+      </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
+      <c r="E165" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F165" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G165" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H165" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I165">
+        <v>3</v>
+      </c>
+      <c r="J165">
+        <v>500</v>
+      </c>
+      <c r="K165" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L165" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" t="str">
+        <v>2026-10-01T13:25:18.501Z</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>sale_1790853314445</v>
+      </c>
+      <c r="B166" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C166" t="str">
+        <v>+92 302 7283125</v>
+      </c>
+      <c r="D166" t="str">
+        <v/>
+      </c>
+      <c r="E166" t="str">
+        <v>CapCut</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G166" t="str">
+        <v>NA</v>
+      </c>
+      <c r="H166" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166">
+        <v>750</v>
+      </c>
+      <c r="K166" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L166" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M166" t="str">
+        <v>vukdsas@apricity.tech  masuk123</v>
+      </c>
+      <c r="N166" t="str">
+        <v>2026-10-01T11:15:14.445Z</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>sale_1790852538710</v>
+      </c>
+      <c r="B167" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C167" t="str">
+        <v>+92 325 1501138</v>
+      </c>
+      <c r="D167" t="str">
+        <v/>
+      </c>
+      <c r="E167" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G167" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H167" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>1000</v>
+      </c>
+      <c r="K167" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L167" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
+      <c r="N167" t="str">
+        <v>2026-10-01T11:02:18.710Z</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>sale_1790852373016</v>
+      </c>
+      <c r="B168" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C168" t="str">
+        <v>+92 301 7890066</v>
+      </c>
+      <c r="D168" t="str">
+        <v/>
+      </c>
+      <c r="E168" t="str">
+        <v>Muse AI</v>
+      </c>
+      <c r="F168" t="str">
+        <v>Private</v>
+      </c>
+      <c r="G168" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H168" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168">
+        <v>1500</v>
+      </c>
+      <c r="K168" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L168" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
+        <v>2026-10-01T10:59:33.016Z</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>sale_1790850006978</v>
+      </c>
+      <c r="B169" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C169" t="str">
+        <v>+92 342 4112890-534389</v>
+      </c>
+      <c r="D169" t="str">
+        <v/>
+      </c>
+      <c r="E169" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G169" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H169" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169">
+        <v>200</v>
+      </c>
+      <c r="K169" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L169" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
+      <c r="N169" t="str">
+        <v>2026-10-01T10:20:06.978Z</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>sale_1790849948623</v>
+      </c>
+      <c r="B170" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C170" t="str">
+        <v>+92 349 6363398</v>
+      </c>
+      <c r="D170" t="str">
+        <v/>
+      </c>
+      <c r="E170" t="str">
+        <v>Surfshark</v>
+      </c>
+      <c r="F170" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G170" t="str">
+        <v>abd149@kuromee.com</v>
+      </c>
+      <c r="H170" t="str">
+        <v>1 Month (30 Days)</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>250</v>
+      </c>
+      <c r="K170" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L170" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
+      <c r="N170" t="str">
+        <v>2026-10-01T10:19:08.625Z</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>sale_1790844774858</v>
+      </c>
+      <c r="B171" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C171" t="str">
+        <v>03035587360</v>
+      </c>
+      <c r="D171" t="str">
+        <v/>
+      </c>
+      <c r="E171" t="str">
+        <v>Gemini Pro</v>
+      </c>
+      <c r="F171" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G171" t="str">
+        <v>Not applicable</v>
+      </c>
+      <c r="H171" t="str">
+        <v>18 Months (540 Days)</v>
+      </c>
+      <c r="I171">
+        <v>18</v>
+      </c>
+      <c r="J171">
+        <v>500</v>
+      </c>
+      <c r="K171" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L171" t="str">
+        <v>2028-03-23</v>
+      </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v>2026-10-01T08:52:54.860Z</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>sale_1790841917101</v>
+      </c>
+      <c r="B172" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C172" t="str">
+        <v>+92 340 7317084</v>
+      </c>
+      <c r="D172" t="str">
+        <v/>
+      </c>
+      <c r="E172" t="str">
+        <v>Nord</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G172" t="str">
+        <v>nord9@kuromee.com</v>
+      </c>
+      <c r="H172" t="str">
+        <v>3 Months (90 Days)</v>
+      </c>
+      <c r="I172">
+        <v>3</v>
+      </c>
+      <c r="J172">
+        <v>500</v>
+      </c>
+      <c r="K172" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L172" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
+      <c r="N172" t="str">
+        <v>2026-10-01T08:05:17.101Z</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
         <v>sale_1790839031379</v>
       </c>
-      <c r="B89" t="str">
+      <c r="B173" t="str">
         <v>2026-10-01</v>
       </c>
-      <c r="C89" t="str">
+      <c r="C173" t="str">
         <v>+92 340 7317084</v>
       </c>
-      <c r="D89" t="str">
-        <v/>
-      </c>
-      <c r="E89" t="str">
+      <c r="D173" t="str">
+        <v/>
+      </c>
+      <c r="E173" t="str">
         <v>Nord</v>
       </c>
-      <c r="F89" t="str">
-        <v>Shared</v>
-      </c>
-      <c r="G89" t="str">
+      <c r="F173" t="str">
+        <v>Shared</v>
+      </c>
+      <c r="G173" t="str">
         <v>Nord9@kuromee.com</v>
       </c>
-      <c r="H89" t="str">
+      <c r="H173" t="str">
         <v>3 Months (90 Days)</v>
       </c>
-      <c r="I89">
+      <c r="I173">
         <v>3</v>
       </c>
-      <c r="J89">
+      <c r="J173">
         <v>500</v>
       </c>
-      <c r="K89" t="str">
-        <v>Paid</v>
-      </c>
-      <c r="L89" t="str">
+      <c r="K173" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="L173" t="str">
         <v>2026-12-29</v>
       </c>
-      <c r="M89" t="str">
-        <v/>
-      </c>
-      <c r="N89" t="str">
+      <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
         <v>2026-10-01T07:17:11.379Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N173"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4350,187 +8046,287 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>exp_1791205545999</v>
+        <v>exp_1791623409478</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-10</v>
       </c>
       <c r="C2" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D2" t="str">
-        <v>baktionopradana64@akunku.site|masuk123 qaoyxh@apricity.tech:masuk123</v>
+        <v>yxddgm871@capcut.space|masuk123</v>
       </c>
       <c r="E2">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-10-05T13:05:45.999Z</v>
+        <v>2026-10-10T09:10:09.478Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>exp_1791035398823</v>
+        <v>exp_1791545987060</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-09</v>
       </c>
       <c r="C3" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D3" t="str">
-        <v>arthurwestbrook00q61@klingaii.com Capcut#1122</v>
+        <v>Nord Purchased Telegram</v>
       </c>
       <c r="E3">
-        <v>380</v>
+        <v>750</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-10-03T13:49:58.823Z</v>
+        <v>2026-10-09T11:39:47.060Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>exp_1791035383336</v>
+        <v>exp_1791388363781</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-07</v>
       </c>
       <c r="C4" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D4" t="str">
-        <v>jinawidamanik6@ccpro.id|masuk123</v>
+        <v>Capcut</v>
       </c>
       <c r="E4">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-10-03T13:49:43.337Z</v>
+        <v>2026-10-07T15:52:43.781Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>exp_1791018590950</v>
+        <v>exp_1791305606523</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C5" t="str">
-        <v>Meta Ads</v>
+        <v>Vendor Purchasing</v>
       </c>
       <c r="D5" t="str">
-        <v>Meta Ads</v>
+        <v>Capcut 3x</v>
       </c>
       <c r="E5">
-        <v>2000</v>
+        <v>1050</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-10-03T09:09:50.950Z</v>
+        <v>2026-10-06T16:53:26.523Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>exp_1790940392222</v>
+        <v>exp_1791284990702</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-06</v>
       </c>
       <c r="C6" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D6" t="str">
-        <v>alissaturner822@gmail.com   Surfshark Private Payment</v>
+        <v>Telegram 5x Gemini</v>
       </c>
       <c r="E6">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-10-02T11:26:32.222Z</v>
+        <v>2026-10-06T11:09:50.702Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>exp_1790889252470</v>
+        <v>exp_1791205545999</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-05</v>
       </c>
       <c r="C7" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D7" t="str">
-        <v>Surfshark/Nord Paid</v>
+        <v>baktionopradana64@akunku.site|masuk123 qaoyxh@apricity.tech:masuk123</v>
       </c>
       <c r="E7">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-10-01T21:14:12.470Z</v>
+        <v>2026-10-05T13:05:45.999Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>exp_1790888895390</v>
+        <v>exp_1791035398823</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C8" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D8" t="str">
-        <v>Capcut padmahastuti3@akunku.site|masuk123</v>
+        <v>arthurwestbrook00q61@klingaii.com Capcut#1122</v>
       </c>
       <c r="E8">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-10-01T21:08:15.390Z</v>
+        <v>2026-10-03T13:49:58.823Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>exp_1790865001001</v>
+        <v>exp_1791035383336</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="C9" t="str">
         <v>Vendor Purchasing</v>
       </c>
       <c r="D9" t="str">
-        <v>Capcut Account For Luxury online Store   vukdsas@apricity.tech:masuk123</v>
+        <v>jinawidamanik6@ccpro.id|masuk123</v>
       </c>
       <c r="E9">
         <v>350</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-10-01T14:30:01.001Z</v>
+        <v>2026-10-03T13:49:43.337Z</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>exp_1790810881227_1bq9</v>
+        <v>exp_1791018590950</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C10" t="str">
         <v>Meta Ads</v>
       </c>
       <c r="D10" t="str">
+        <v>Meta Ads</v>
+      </c>
+      <c r="E10">
+        <v>2000</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-10-03T09:09:50.950Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>exp_1790940392222</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D11" t="str">
+        <v>alissaturner822@gmail.com   Surfshark Private Payment</v>
+      </c>
+      <c r="E11">
+        <v>750</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-10-02T11:26:32.222Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>exp_1790889252470</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Surfshark/Nord Paid</v>
+      </c>
+      <c r="E12">
+        <v>1600</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-10-01T21:14:12.470Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>exp_1790888895390</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Capcut padmahastuti3@akunku.site|masuk123</v>
+      </c>
+      <c r="E13">
+        <v>350</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-10-01T21:08:15.390Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>exp_1790865001001</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Vendor Purchasing</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Capcut Account For Luxury online Store   vukdsas@apricity.tech:masuk123</v>
+      </c>
+      <c r="E14">
+        <v>350</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-10-01T14:30:01.001Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>exp_1790810881227_1bq9</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Meta Ads</v>
+      </c>
+      <c r="D15" t="str">
         <v>Meta Ads Campaign</v>
       </c>
-      <c r="E10">
+      <c r="E15">
         <v>500</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F15" t="str">
         <v>2026-09-30T23:28:01.227Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4876,7 +8672,7 @@
         <v>1 Month (25 Days)</v>
       </c>
       <c r="E20">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
